--- a/research/traditional_assets/database/data/ireland/ireland_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_electrical_equipment.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -599,40 +599,40 @@
         <v>0.121</v>
       </c>
       <c r="G2">
-        <v>0.2297500508026824</v>
+        <v>0.2251818443147812</v>
       </c>
       <c r="H2">
-        <v>0.1974801869538712</v>
+        <v>0.1930157894481849</v>
       </c>
       <c r="I2">
-        <v>0.1854319768964816</v>
+        <v>0.1821008425051368</v>
       </c>
       <c r="J2">
-        <v>0.1559248604480555</v>
+        <v>0.1724418274580625</v>
       </c>
       <c r="K2">
-        <v>3768</v>
+        <v>3665.3</v>
       </c>
       <c r="L2">
-        <v>0.1531396057711847</v>
+        <v>0.1479826747263857</v>
       </c>
       <c r="M2">
         <v>3156</v>
       </c>
       <c r="N2">
-        <v>0.02406313140940109</v>
+        <v>0.02391587069607157</v>
       </c>
       <c r="O2">
-        <v>0.8375796178343949</v>
+        <v>0.8610482088778544</v>
       </c>
       <c r="P2">
         <v>1474</v>
       </c>
       <c r="Q2">
-        <v>0.01123861080401052</v>
+        <v>0.01116983314512341</v>
       </c>
       <c r="R2">
-        <v>0.3911889596602973</v>
+        <v>0.4021498922325594</v>
       </c>
       <c r="S2">
         <v>1682</v>
@@ -641,73 +641,73 @@
         <v>0.5329531051964512</v>
       </c>
       <c r="U2">
-        <v>473</v>
+        <v>498.84</v>
       </c>
       <c r="V2">
-        <v>0.003606419884869048</v>
+        <v>0.003780162527892377</v>
       </c>
       <c r="W2">
-        <v>0.2049719849861285</v>
+        <v>-1.331632653061224</v>
       </c>
       <c r="X2">
-        <v>0.1060866903590911</v>
+        <v>0.1060585358803303</v>
       </c>
       <c r="Y2">
-        <v>0.09888529462703738</v>
+        <v>-1.437691188941555</v>
       </c>
       <c r="Z2">
-        <v>1.888301129895957</v>
+        <v>1.888316100704492</v>
       </c>
       <c r="AA2">
-        <v>0.2944330901629327</v>
+        <v>-0.5275862068965518</v>
       </c>
       <c r="AB2">
-        <v>0.1023586721065301</v>
+        <v>0.102490237636068</v>
       </c>
       <c r="AC2">
-        <v>0.1920744180564026</v>
+        <v>-0.6300764445326198</v>
       </c>
       <c r="AD2">
-        <v>9397</v>
+        <v>9418.57</v>
       </c>
       <c r="AE2">
         <v>627.2310423103443</v>
       </c>
       <c r="AF2">
-        <v>10024.23104231034</v>
+        <v>10045.80104231034</v>
       </c>
       <c r="AG2">
-        <v>9551.231042310344</v>
+        <v>9546.961042310344</v>
       </c>
       <c r="AH2">
-        <v>0.07100358153463918</v>
+        <v>0.07074090253389533</v>
       </c>
       <c r="AI2">
-        <v>0.3434575374867189</v>
+        <v>0.3439426304845963</v>
       </c>
       <c r="AJ2">
-        <v>0.06788065440711216</v>
+        <v>0.06746514031485602</v>
       </c>
       <c r="AK2">
-        <v>0.3326421546999061</v>
+        <v>0.3325431275309086</v>
       </c>
       <c r="AL2">
-        <v>130</v>
+        <v>164.434</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>161.185</v>
       </c>
       <c r="AN2">
-        <v>1.676239743132358</v>
+        <v>1.694048347062844</v>
       </c>
       <c r="AO2">
-        <v>34.86153846153846</v>
+        <v>27.24375737377915</v>
       </c>
       <c r="AP2">
-        <v>1.70375152377994</v>
+        <v>1.71714109182171</v>
       </c>
       <c r="AQ2">
-        <v>34.86153846153846</v>
+        <v>27.79290876942644</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.2049719849861285</v>
       </c>
       <c r="X3">
-        <v>0.1060866903590911</v>
+        <v>0.1060585358803303</v>
       </c>
       <c r="Y3">
-        <v>0.09888529462703738</v>
+        <v>0.09891344910579816</v>
       </c>
       <c r="Z3">
         <v>1.888301129895957</v>
@@ -799,10 +799,10 @@
         <v>0.2944330901629327</v>
       </c>
       <c r="AB3">
-        <v>0.1023586721065301</v>
+        <v>0.1023325166965976</v>
       </c>
       <c r="AC3">
-        <v>0.1920744180564026</v>
+        <v>0.1921005734663352</v>
       </c>
       <c r="AD3">
         <v>9397</v>
@@ -845,6 +845,256 @@
       </c>
       <c r="AQ3">
         <v>34.86153846153846</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADS-TEC Energy PLC (NasdaqCM:ADSE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.2793522012578616</v>
+      </c>
+      <c r="H4">
+        <v>-0.2767295597484277</v>
+      </c>
+      <c r="I4">
+        <v>-0.1924528301886793</v>
+      </c>
+      <c r="J4">
+        <v>-0.1924528301886793</v>
+      </c>
+      <c r="K4">
+        <v>-76.59999999999999</v>
+      </c>
+      <c r="L4">
+        <v>-0.4817610062893081</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>25.4</v>
+      </c>
+      <c r="V4">
+        <v>0.03183755327149661</v>
+      </c>
+      <c r="W4">
+        <v>-1.336823734729494</v>
+      </c>
+      <c r="X4">
+        <v>0.1035387791509138</v>
+      </c>
+      <c r="Y4">
+        <v>-1.440362513880407</v>
+      </c>
+      <c r="Z4">
+        <v>2.741379310344827</v>
+      </c>
+      <c r="AA4">
+        <v>-0.5275862068965518</v>
+      </c>
+      <c r="AB4">
+        <v>0.102490237636068</v>
+      </c>
+      <c r="AC4">
+        <v>-0.6300764445326198</v>
+      </c>
+      <c r="AD4">
+        <v>20.3</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>20.3</v>
+      </c>
+      <c r="AG4">
+        <v>-5.099999999999998</v>
+      </c>
+      <c r="AH4">
+        <v>0.02481359247035815</v>
+      </c>
+      <c r="AI4">
+        <v>1.109896118097321</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.006433707581682854</v>
+      </c>
+      <c r="AK4">
+        <v>0.7172995780590716</v>
+      </c>
+      <c r="AL4">
+        <v>33.8</v>
+      </c>
+      <c r="AM4">
+        <v>33.721</v>
+      </c>
+      <c r="AN4">
+        <v>-0.8023715415019763</v>
+      </c>
+      <c r="AO4">
+        <v>-0.9053254437869823</v>
+      </c>
+      <c r="AP4">
+        <v>0.2015810276679841</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.9074463983867621</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fusion Fuel Green PLC (NasdaqGM:HTOO)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-7.022522522522521</v>
+      </c>
+      <c r="H5">
+        <v>-7.725225225225224</v>
+      </c>
+      <c r="I5">
+        <v>-4.864864864864865</v>
+      </c>
+      <c r="J5">
+        <v>-4.864864864864865</v>
+      </c>
+      <c r="K5">
+        <v>-26.1</v>
+      </c>
+      <c r="L5">
+        <v>-5.878378378378378</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.44</v>
+      </c>
+      <c r="V5">
+        <v>0.04498977505112475</v>
+      </c>
+      <c r="W5">
+        <v>-1.331632653061224</v>
+      </c>
+      <c r="X5">
+        <v>0.1086989292728003</v>
+      </c>
+      <c r="Y5">
+        <v>-1.440331582334025</v>
+      </c>
+      <c r="Z5">
+        <v>0.1560632688927944</v>
+      </c>
+      <c r="AA5">
+        <v>-0.7592267135325133</v>
+      </c>
+      <c r="AB5">
+        <v>0.1026156419506088</v>
+      </c>
+      <c r="AC5">
+        <v>-0.861842355483122</v>
+      </c>
+      <c r="AD5">
+        <v>1.27</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1.27</v>
+      </c>
+      <c r="AG5">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.1149321266968326</v>
+      </c>
+      <c r="AI5">
+        <v>0.3895705521472393</v>
+      </c>
+      <c r="AJ5">
+        <v>0.07822808671065035</v>
+      </c>
+      <c r="AK5">
+        <v>0.2943262411347518</v>
+      </c>
+      <c r="AL5">
+        <v>0.634</v>
+      </c>
+      <c r="AM5">
+        <v>-2.536</v>
+      </c>
+      <c r="AN5">
+        <v>-0.06076555023923445</v>
+      </c>
+      <c r="AO5">
+        <v>-34.06940063091483</v>
+      </c>
+      <c r="AP5">
+        <v>-0.03971291866028709</v>
+      </c>
+      <c r="AQ5">
+        <v>8.517350157728707</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1389,7 @@
         <v>36.0615384615385</v>
       </c>
       <c r="F2">
-        <v>9.60211849834034</v>
+        <v>9.841161433272671</v>
       </c>
       <c r="G2">
         <v>1.78812540890302</v>
@@ -1157,13 +1407,13 @@
         <v>131155</v>
       </c>
       <c r="L2">
-        <v>133200.052281884</v>
+        <v>133384.830776618</v>
       </c>
       <c r="M2">
         <v>140706.23104231</v>
       </c>
       <c r="N2">
-        <v>141197.806144423</v>
+        <v>141382.584639156</v>
       </c>
       <c r="O2">
         <v>10024.2310423103</v>
@@ -1172,16 +1422,16 @@
         <v>8470.753862538621</v>
       </c>
       <c r="Q2">
-        <v>0.10235867210653</v>
+        <v>0.102332516696598</v>
       </c>
       <c r="R2">
-        <v>0.102161765116434</v>
+        <v>0.102062073408946</v>
       </c>
       <c r="S2">
         <v>0.0535820395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1444,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.106086690359091</v>
+        <v>0.10605853588033</v>
       </c>
       <c r="X2">
-        <v>0.105463662491118</v>
+        <v>0.105435798972514</v>
       </c>
       <c r="Y2">
         <v>1.17455102346149</v>
@@ -1236,7 +1486,7 @@
         <v>131155</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183672</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1023076501175322</v>
+        <v>0.1022812604878216</v>
       </c>
       <c r="C2">
-        <v>141306.2777653158</v>
+        <v>141306.9206138974</v>
       </c>
       <c r="D2">
-        <v>140833.2777653158</v>
+        <v>140833.9206138974</v>
       </c>
       <c r="E2">
         <v>-10024.23104231034</v>
@@ -1475,19 +1725,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1023076501175322</v>
+        <v>0.1022812604878216</v>
       </c>
       <c r="T2">
         <v>1.100924895422504</v>
       </c>
       <c r="U2">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1756,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1022833359506825</v>
+        <v>0.102244729308009</v>
       </c>
       <c r="C3">
-        <v>139955.1094204562</v>
+        <v>139986.2763936633</v>
       </c>
       <c r="D3">
-        <v>140893.9017308793</v>
+        <v>140925.0687040864</v>
       </c>
       <c r="E3">
         <v>-8612.438731887241</v>
@@ -1539,37 +1789,37 @@
         <v>4688</v>
       </c>
       <c r="M3">
-        <v>81.37093220296973</v>
+        <v>79.39442296837738</v>
       </c>
       <c r="N3">
-        <v>4606.62906779703</v>
+        <v>4608.605577031622</v>
       </c>
       <c r="O3">
-        <v>575.8286334746288</v>
+        <v>576.0756971289528</v>
       </c>
       <c r="P3">
-        <v>4030.800434322401</v>
+        <v>4032.52987990267</v>
       </c>
       <c r="Q3">
-        <v>4948.800434322401</v>
+        <v>4950.52987990267</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1028070864190761</v>
+        <v>0.1027804635476887</v>
       </c>
       <c r="T3">
         <v>1.110655292225481</v>
       </c>
       <c r="U3">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>57.61271099004204</v>
+        <v>59.04696859963602</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1838,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1022590217838327</v>
+        <v>0.1022081981281964</v>
       </c>
       <c r="C4">
-        <v>138603.9932912094</v>
+        <v>138665.7502324129</v>
       </c>
       <c r="D4">
-        <v>140954.5779120556</v>
+        <v>141016.3348532591</v>
       </c>
       <c r="E4">
         <v>-7200.646421464138</v>
@@ -1621,37 +1871,37 @@
         <v>4688</v>
       </c>
       <c r="M4">
-        <v>162.7418644059395</v>
+        <v>158.7888459367548</v>
       </c>
       <c r="N4">
-        <v>4525.25813559406</v>
+        <v>4529.211154063245</v>
       </c>
       <c r="O4">
-        <v>565.6572669492575</v>
+        <v>566.1513942579056</v>
       </c>
       <c r="P4">
-        <v>3959.600868644803</v>
+        <v>3963.059759805339</v>
       </c>
       <c r="Q4">
-        <v>4877.600868644802</v>
+        <v>4881.059759805339</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1033167152982024</v>
+        <v>0.1032898544251041</v>
       </c>
       <c r="T4">
         <v>1.120584268555049</v>
       </c>
       <c r="U4">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>28.80635549502102</v>
+        <v>29.52348429981801</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1920,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.102234707616983</v>
+        <v>0.1021716669483838</v>
       </c>
       <c r="C5">
-        <v>137252.9294450649</v>
+        <v>137345.3423596676</v>
       </c>
       <c r="D5">
-        <v>141015.3063763342</v>
+        <v>141107.7192909369</v>
       </c>
       <c r="E5">
         <v>-5788.854111041034</v>
@@ -1703,37 +1953,37 @@
         <v>4688</v>
       </c>
       <c r="M5">
-        <v>244.1127966089092</v>
+        <v>238.1832689051322</v>
       </c>
       <c r="N5">
-        <v>4443.887203391091</v>
+        <v>4449.816731094867</v>
       </c>
       <c r="O5">
-        <v>555.4859004238864</v>
+        <v>556.2270913868584</v>
       </c>
       <c r="P5">
-        <v>3888.401302967205</v>
+        <v>3893.589639708009</v>
       </c>
       <c r="Q5">
-        <v>4806.401302967204</v>
+        <v>4811.589639708009</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1038368519892695</v>
+        <v>0.1038097482072085</v>
       </c>
       <c r="T5">
         <v>1.130717966046051</v>
       </c>
       <c r="U5">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>19.20423699668068</v>
+        <v>19.68232286654534</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +2002,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1022103934501332</v>
+        <v>0.1021351357685712</v>
       </c>
       <c r="C6">
-        <v>135901.9179496282</v>
+        <v>136025.0530055441</v>
       </c>
       <c r="D6">
-        <v>141076.0871913206</v>
+        <v>141199.2222472365</v>
       </c>
       <c r="E6">
         <v>-4377.061800617931</v>
@@ -1785,37 +2035,37 @@
         <v>4688</v>
       </c>
       <c r="M6">
-        <v>325.4837288118789</v>
+        <v>317.5776918735095</v>
       </c>
       <c r="N6">
-        <v>4362.516271188121</v>
+        <v>4370.422308126491</v>
       </c>
       <c r="O6">
-        <v>545.3145338985152</v>
+        <v>546.3027885158114</v>
       </c>
       <c r="P6">
-        <v>3817.201737289606</v>
+        <v>3824.11951961068</v>
       </c>
       <c r="Q6">
-        <v>4735.201737289606</v>
+        <v>4742.11951961068</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1043678248614006</v>
+        <v>0.1043404731097734</v>
       </c>
       <c r="T6">
         <v>1.141062782234783</v>
       </c>
       <c r="U6">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>14.40317774751051</v>
+        <v>14.76174214990901</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +2084,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1021860792832835</v>
+        <v>0.1020986045887586</v>
       </c>
       <c r="C7">
-        <v>134550.9588726216</v>
+        <v>134704.8824007564</v>
       </c>
       <c r="D7">
-        <v>141136.9204247371</v>
+        <v>141290.8439528719</v>
       </c>
       <c r="E7">
         <v>-2965.269490194827</v>
@@ -1867,37 +2117,37 @@
         <v>4688</v>
       </c>
       <c r="M7">
-        <v>406.8546610148487</v>
+        <v>396.972114841887</v>
       </c>
       <c r="N7">
-        <v>4281.145338985151</v>
+        <v>4291.027885158113</v>
       </c>
       <c r="O7">
-        <v>535.1431673731439</v>
+        <v>536.3784856447642</v>
       </c>
       <c r="P7">
-        <v>3746.002171612007</v>
+        <v>3754.649399513349</v>
       </c>
       <c r="Q7">
-        <v>4664.002171612007</v>
+        <v>4672.64939951335</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.104909976109787</v>
+        <v>0.1048823711681818</v>
       </c>
       <c r="T7">
         <v>1.151625384027488</v>
       </c>
       <c r="U7">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2155,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>11.52254219800841</v>
+        <v>11.8093937199272</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2166,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1021617651164338</v>
+        <v>0.1020620734089459</v>
       </c>
       <c r="C8">
-        <v>133200.052281884</v>
+        <v>133384.8307766176</v>
       </c>
       <c r="D8">
-        <v>141197.8061444226</v>
+        <v>141382.5846391562</v>
       </c>
       <c r="E8">
         <v>-1553.477179771724</v>
@@ -1949,37 +2199,37 @@
         <v>4688</v>
       </c>
       <c r="M8">
-        <v>488.2255932178184</v>
+        <v>476.3665378102643</v>
       </c>
       <c r="N8">
-        <v>4199.774406782181</v>
+        <v>4211.633462189736</v>
       </c>
       <c r="O8">
-        <v>524.9718008477727</v>
+        <v>526.454182773717</v>
       </c>
       <c r="P8">
-        <v>3674.802605934409</v>
+        <v>3685.179279416019</v>
       </c>
       <c r="Q8">
-        <v>4592.802605934408</v>
+        <v>4603.179279416019</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1054636624911178</v>
+        <v>0.1054357989725137</v>
       </c>
       <c r="T8">
         <v>1.162412722028549</v>
       </c>
       <c r="U8">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2237,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>9.602118498340339</v>
+        <v>9.841161433272669</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2248,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.102204825949584</v>
+        <v>0.1021174172291334</v>
       </c>
       <c r="C9">
-        <v>131680.4660891254</v>
+        <v>131834.1000573171</v>
       </c>
       <c r="D9">
-        <v>141090.0122620871</v>
+        <v>141243.6462302789</v>
       </c>
       <c r="E9">
         <v>-141.6848693486209</v>
@@ -2031,37 +2281,37 @@
         <v>4688</v>
       </c>
       <c r="M9">
-        <v>580.467326211046</v>
+        <v>570.5847800380843</v>
       </c>
       <c r="N9">
-        <v>4107.532673788954</v>
+        <v>4117.415219961916</v>
       </c>
       <c r="O9">
-        <v>513.4415842236192</v>
+        <v>514.6769024952395</v>
       </c>
       <c r="P9">
-        <v>3594.091089565334</v>
+        <v>3602.738317466676</v>
       </c>
       <c r="Q9">
-        <v>4512.091089565334</v>
+        <v>4520.738317466676</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1060292561064557</v>
+        <v>0.1060011284500572</v>
       </c>
       <c r="T9">
         <v>1.173432045793073</v>
       </c>
       <c r="U9">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2319,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.076251303584208</v>
+        <v>8.216132227864708</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2330,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1021901367827343</v>
+        <v>0.1020940110493208</v>
       </c>
       <c r="C10">
-        <v>130305.426566498</v>
+        <v>130481.034672182</v>
       </c>
       <c r="D10">
-        <v>141126.7650498828</v>
+        <v>141302.3731555668</v>
       </c>
       <c r="E10">
         <v>1270.107441074482</v>
@@ -2113,37 +2363,37 @@
         <v>4688</v>
       </c>
       <c r="M10">
-        <v>663.3912299554812</v>
+        <v>652.0968914720963</v>
       </c>
       <c r="N10">
-        <v>4024.608770044519</v>
+        <v>4035.903108527904</v>
       </c>
       <c r="O10">
-        <v>503.0760962555648</v>
+        <v>504.487888565988</v>
       </c>
       <c r="P10">
-        <v>3521.532673788954</v>
+        <v>3531.415219961916</v>
       </c>
       <c r="Q10">
-        <v>4439.532673788954</v>
+        <v>4449.415219961916</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1066071452351705</v>
+        <v>0.1065787476988515</v>
       </c>
       <c r="T10">
         <v>1.184690920074217</v>
       </c>
       <c r="U10">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2401,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.066719890636181</v>
+        <v>7.18911569938162</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2412,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1023486976158845</v>
+        <v>0.1022044798695081</v>
       </c>
       <c r="C11">
-        <v>128497.9190868572</v>
+        <v>128792.5000446896</v>
       </c>
       <c r="D11">
-        <v>140731.0498806651</v>
+        <v>141025.6308384976</v>
       </c>
       <c r="E11">
         <v>2681.899751497585</v>
@@ -2195,37 +2445,37 @@
         <v>4688</v>
       </c>
       <c r="M11">
-        <v>774.2686214462938</v>
+        <v>755.2094252555819</v>
       </c>
       <c r="N11">
-        <v>3913.731378553706</v>
+        <v>3932.790574744418</v>
       </c>
       <c r="O11">
-        <v>489.2164223192133</v>
+        <v>491.5988218430523</v>
       </c>
       <c r="P11">
-        <v>3424.514956234493</v>
+        <v>3441.191752901366</v>
       </c>
       <c r="Q11">
-        <v>4342.514956234493</v>
+        <v>4359.191752901366</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1071977352238571</v>
+        <v>0.1071690618761908</v>
       </c>
       <c r="T11">
         <v>1.196197242141759</v>
       </c>
       <c r="U11">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05331953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2483,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>6.054746208419319</v>
+        <v>6.207549645468822</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2494,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1024845084490348</v>
+        <v>0.1021959486896956</v>
       </c>
       <c r="C12">
-        <v>126748.9482128837</v>
+        <v>127402.0410931836</v>
       </c>
       <c r="D12">
-        <v>140393.8713171148</v>
+        <v>141046.9641974146</v>
       </c>
       <c r="E12">
         <v>4093.69206192069</v>
@@ -2277,45 +2527,45 @@
         <v>4688</v>
       </c>
       <c r="M12">
-        <v>881.4753529300065</v>
+        <v>839.1215836173133</v>
       </c>
       <c r="N12">
-        <v>3806.524647069994</v>
+        <v>3848.878416382687</v>
       </c>
       <c r="O12">
-        <v>475.8155808837492</v>
+        <v>481.1098020478358</v>
       </c>
       <c r="P12">
-        <v>3330.709066186244</v>
+        <v>3367.768614334851</v>
       </c>
       <c r="Q12">
-        <v>4248.709066186244</v>
+        <v>4285.768614334851</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1078014494345145</v>
+        <v>0.1077724941463598</v>
       </c>
       <c r="T12">
         <v>1.207959260255248</v>
       </c>
       <c r="U12">
-        <v>0.06243661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05463203957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.318356303913866</v>
+        <v>5.58679468092194</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2576,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1025021942821851</v>
+        <v>0.102264417509883</v>
       </c>
       <c r="C13">
-        <v>125293.3660171684</v>
+        <v>125819.2150653238</v>
       </c>
       <c r="D13">
-        <v>140350.0814318226</v>
+        <v>140875.9304799779</v>
       </c>
       <c r="E13">
         <v>5505.484372343792</v>
@@ -2359,37 +2609,37 @@
         <v>4688</v>
       </c>
       <c r="M13">
-        <v>969.622888223007</v>
+        <v>935.4575143107678</v>
       </c>
       <c r="N13">
-        <v>3718.377111776993</v>
+        <v>3752.542485689232</v>
       </c>
       <c r="O13">
-        <v>464.7971389721241</v>
+        <v>469.067810711154</v>
       </c>
       <c r="P13">
-        <v>3253.579972804869</v>
+        <v>3283.474674978078</v>
       </c>
       <c r="Q13">
-        <v>4171.579972804869</v>
+        <v>4201.474674978079</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1084187302566474</v>
+        <v>0.108389486692263</v>
       </c>
       <c r="T13">
         <v>1.219985593382523</v>
       </c>
       <c r="U13">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2647,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>4.834869367194425</v>
+        <v>5.011451539254622</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2658,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1025198801153353</v>
+        <v>0.1022628863300703</v>
       </c>
       <c r="C14">
-        <v>123837.8111297127</v>
+        <v>124411.2430764404</v>
       </c>
       <c r="D14">
-        <v>140306.3188547899</v>
+        <v>140879.7508015176</v>
       </c>
       <c r="E14">
         <v>6917.276682766897</v>
@@ -2441,37 +2691,37 @@
         <v>4688</v>
       </c>
       <c r="M14">
-        <v>1057.770423516008</v>
+        <v>1020.499106520838</v>
       </c>
       <c r="N14">
-        <v>3630.229576483992</v>
+        <v>3667.500893479162</v>
       </c>
       <c r="O14">
-        <v>453.778697060499</v>
+        <v>458.4376116848953</v>
       </c>
       <c r="P14">
-        <v>3176.450879423493</v>
+        <v>3209.063281794267</v>
       </c>
       <c r="Q14">
-        <v>4094.450879423493</v>
+        <v>4127.063281794267</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1090500401883741</v>
+        <v>0.1090205017960276</v>
       </c>
       <c r="T14">
         <v>1.23228525226269</v>
       </c>
       <c r="U14">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2729,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.431963586594889</v>
+        <v>4.59383057765007</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2740,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1026968159484856</v>
+        <v>0.1023751051502577</v>
       </c>
       <c r="C15">
-        <v>121989.6988774972</v>
+        <v>122720.0105532018</v>
       </c>
       <c r="D15">
-        <v>139869.9989129975</v>
+        <v>140600.3105887022</v>
       </c>
       <c r="E15">
         <v>8329.068993189998</v>
@@ -2523,37 +2773,37 @@
         <v>4688</v>
       </c>
       <c r="M15">
-        <v>1171.612578858709</v>
+        <v>1123.893998766408</v>
       </c>
       <c r="N15">
-        <v>3516.387421141291</v>
+        <v>3564.106001233592</v>
       </c>
       <c r="O15">
-        <v>439.5484276426614</v>
+        <v>445.513250154199</v>
       </c>
       <c r="P15">
-        <v>3076.83899349863</v>
+        <v>3118.592751079393</v>
       </c>
       <c r="Q15">
-        <v>3994.83899349863</v>
+        <v>4036.592751079393</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1096958629920946</v>
+        <v>0.1096660229941316</v>
       </c>
       <c r="T15">
         <v>1.244867661921711</v>
       </c>
       <c r="U15">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.001322693689986</v>
+        <v>4.171211880431406</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2822,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1027267517816358</v>
+        <v>0.1023823239704452</v>
       </c>
       <c r="C16">
-        <v>120504.3537150468</v>
+        <v>121290.2803376307</v>
       </c>
       <c r="D16">
-        <v>139796.4460609703</v>
+        <v>140582.3726835542</v>
       </c>
       <c r="E16">
         <v>9740.861303613103</v>
@@ -2605,37 +2855,37 @@
         <v>4688</v>
       </c>
       <c r="M16">
-        <v>1261.736623386302</v>
+        <v>1210.347383286901</v>
       </c>
       <c r="N16">
-        <v>3426.263376613698</v>
+        <v>3477.652616713099</v>
       </c>
       <c r="O16">
-        <v>428.2829220767123</v>
+        <v>434.7065770891374</v>
       </c>
       <c r="P16">
-        <v>2997.980454536986</v>
+        <v>3042.946039623962</v>
       </c>
       <c r="Q16">
-        <v>3915.980454536986</v>
+        <v>3960.946039623962</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1103567049307853</v>
+        <v>0.1103265563131218</v>
       </c>
       <c r="T16">
         <v>1.25774268575885</v>
       </c>
       <c r="U16">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2893,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>3.715513929854987</v>
+        <v>3.873268174686305</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2904,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1027566876147861</v>
+        <v>0.1023895427906325</v>
       </c>
       <c r="C17">
-        <v>119019.0858698001</v>
+        <v>119860.5546985417</v>
       </c>
       <c r="D17">
-        <v>139722.9705261466</v>
+        <v>140564.4393548883</v>
       </c>
       <c r="E17">
         <v>11152.6536140362</v>
@@ -2687,37 +2937,37 @@
         <v>4688</v>
       </c>
       <c r="M17">
-        <v>1351.860667913895</v>
+        <v>1296.800767807394</v>
       </c>
       <c r="N17">
-        <v>3336.139332086105</v>
+        <v>3391.199232192606</v>
       </c>
       <c r="O17">
-        <v>417.0174165107632</v>
+        <v>423.8999040240758</v>
       </c>
       <c r="P17">
-        <v>2919.121915575342</v>
+        <v>2967.29932816853</v>
       </c>
       <c r="Q17">
-        <v>3837.121915575342</v>
+        <v>3885.29932816853</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1110330960915629</v>
+        <v>0.1110026315925587</v>
       </c>
       <c r="T17">
         <v>1.270920651333332</v>
       </c>
       <c r="U17">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2975,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.467813001197988</v>
+        <v>3.615050296373885</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2986,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1027866234479363</v>
+        <v>0.1023967616108199</v>
       </c>
       <c r="C18">
-        <v>117533.8952199096</v>
+        <v>118430.8336341835</v>
       </c>
       <c r="D18">
-        <v>139649.5721866793</v>
+        <v>140546.5106009531</v>
       </c>
       <c r="E18">
         <v>12564.44592445931</v>
@@ -2769,37 +3019,37 @@
         <v>4688</v>
       </c>
       <c r="M18">
-        <v>1441.984712441488</v>
+        <v>1383.254152327887</v>
       </c>
       <c r="N18">
-        <v>3246.015287558512</v>
+        <v>3304.745847672113</v>
       </c>
       <c r="O18">
-        <v>405.751910944814</v>
+        <v>413.0932309590141</v>
       </c>
       <c r="P18">
-        <v>2840.263376613698</v>
+        <v>2891.652616713099</v>
       </c>
       <c r="Q18">
-        <v>3758.263376613698</v>
+        <v>3809.652616713099</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1117255918037876</v>
+        <v>0.1116948039024585</v>
       </c>
       <c r="T18">
         <v>1.284412377992922</v>
       </c>
       <c r="U18">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.251074688623114</v>
+        <v>3.389109652850517</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +3068,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1028165592810866</v>
+        <v>0.1024039804310073</v>
       </c>
       <c r="C19">
-        <v>116048.7816437841</v>
+        <v>117001.1171428059</v>
       </c>
       <c r="D19">
-        <v>139576.2509209769</v>
+        <v>140528.5864199986</v>
       </c>
       <c r="E19">
         <v>13976.23823488241</v>
@@ -2851,37 +3101,37 @@
         <v>4688</v>
       </c>
       <c r="M19">
-        <v>1532.108756969081</v>
+        <v>1469.70753684838</v>
       </c>
       <c r="N19">
-        <v>3155.891243030919</v>
+        <v>3218.292463151621</v>
       </c>
       <c r="O19">
-        <v>394.4864053788649</v>
+        <v>402.2865578939526</v>
       </c>
       <c r="P19">
-        <v>2761.404837652054</v>
+        <v>2816.005905257668</v>
       </c>
       <c r="Q19">
-        <v>3679.404837652054</v>
+        <v>3734.005905257668</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1124347741596803</v>
+        <v>0.1124036550631992</v>
       </c>
       <c r="T19">
         <v>1.29822920649973</v>
       </c>
       <c r="U19">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +3139,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.059835001057048</v>
+        <v>3.189750261506369</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3150,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1032559951142369</v>
+        <v>0.1024111992511947</v>
       </c>
       <c r="C20">
-        <v>113569.4800858143</v>
+        <v>115571.4052226594</v>
       </c>
       <c r="D20">
-        <v>138508.7416734301</v>
+        <v>140510.6668102752</v>
       </c>
       <c r="E20">
         <v>15388.03054530552</v>
@@ -2933,45 +3183,45 @@
         <v>4688</v>
       </c>
       <c r="M20">
-        <v>1688.304681624475</v>
+        <v>1556.160921368872</v>
       </c>
       <c r="N20">
-        <v>2999.695318375525</v>
+        <v>3131.839078631127</v>
       </c>
       <c r="O20">
-        <v>374.9619147969406</v>
+        <v>391.4798848288909</v>
       </c>
       <c r="P20">
-        <v>2624.733403578584</v>
+        <v>2740.359193802236</v>
       </c>
       <c r="Q20">
-        <v>3542.733403578584</v>
+        <v>3658.359193802236</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1131612536462046</v>
+        <v>0.113129795276641</v>
       </c>
       <c r="T20">
         <v>1.312383030823778</v>
       </c>
       <c r="U20">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.776749985369489</v>
+        <v>3.012541913644904</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3232,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1033086809473871</v>
+        <v>0.1028340430713821</v>
       </c>
       <c r="C21">
-        <v>112030.7947857861</v>
+        <v>113117.8830272134</v>
       </c>
       <c r="D21">
-        <v>138381.8486838251</v>
+        <v>139468.9369252524</v>
       </c>
       <c r="E21">
         <v>16799.82285572862</v>
@@ -3015,37 +3265,37 @@
         <v>4688</v>
       </c>
       <c r="M21">
-        <v>1782.099386159168</v>
+        <v>1709.674440634463</v>
       </c>
       <c r="N21">
-        <v>2905.900613840832</v>
+        <v>2978.325559365537</v>
       </c>
       <c r="O21">
-        <v>363.237576730104</v>
+        <v>372.2906949206921</v>
       </c>
       <c r="P21">
-        <v>2542.663037110728</v>
+        <v>2606.034864444845</v>
       </c>
       <c r="Q21">
-        <v>3460.663037110728</v>
+        <v>3524.034864444845</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1139056708978282</v>
+        <v>0.1138738648780689</v>
       </c>
       <c r="T21">
         <v>1.326886332291629</v>
       </c>
       <c r="U21">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3303,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.63060524929741</v>
+        <v>2.742042513228586</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3314,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1038338667805374</v>
+        <v>0.1028631368915695</v>
       </c>
       <c r="C22">
-        <v>109366.6960114714</v>
+        <v>111634.9820397413</v>
       </c>
       <c r="D22">
-        <v>137129.5422199335</v>
+        <v>139397.8282482033</v>
       </c>
       <c r="E22">
         <v>18211.61516615173</v>
@@ -3097,45 +3347,45 @@
         <v>4688</v>
       </c>
       <c r="M22">
-        <v>1952.130875456709</v>
+        <v>1799.657305931014</v>
       </c>
       <c r="N22">
-        <v>2735.869124543291</v>
+        <v>2888.342694068986</v>
       </c>
       <c r="O22">
-        <v>341.9836405679114</v>
+        <v>361.0428367586233</v>
       </c>
       <c r="P22">
-        <v>2393.885483975379</v>
+        <v>2527.299857310363</v>
       </c>
       <c r="Q22">
-        <v>3311.885483975379</v>
+        <v>3445.299857310363</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1146686985807424</v>
+        <v>0.1146365362195326</v>
       </c>
       <c r="T22">
         <v>1.341752216296177</v>
       </c>
       <c r="U22">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.401478332697967</v>
+        <v>2.604940387567157</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3396,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1039101776136876</v>
+        <v>0.1035353557117569</v>
       </c>
       <c r="C23">
-        <v>107774.8238932411</v>
+        <v>108600.1661506722</v>
       </c>
       <c r="D23">
-        <v>136949.4624121263</v>
+        <v>137774.8046695574</v>
       </c>
       <c r="E23">
         <v>19623.40747657482</v>
@@ -3179,37 +3429,37 @@
         <v>4688</v>
       </c>
       <c r="M23">
-        <v>2049.737419229544</v>
+        <v>1993.406906043662</v>
       </c>
       <c r="N23">
-        <v>2638.262580770456</v>
+        <v>2694.593093956338</v>
       </c>
       <c r="O23">
-        <v>329.782822596307</v>
+        <v>336.8241367445423</v>
       </c>
       <c r="P23">
-        <v>2308.479758174149</v>
+        <v>2357.768957211796</v>
       </c>
       <c r="Q23">
-        <v>3226.479758174149</v>
+        <v>3275.768957211796</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1154510434201861</v>
+        <v>0.1154185156962231</v>
       </c>
       <c r="T23">
         <v>1.356994451794511</v>
       </c>
       <c r="U23">
-        <v>0.06913661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3467,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.287122221617112</v>
+        <v>2.351752663135059</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3478,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1048912384468379</v>
+        <v>0.1041340745319443</v>
       </c>
       <c r="C24">
-        <v>104089.3315009625</v>
+        <v>105774.3054905723</v>
       </c>
       <c r="D24">
-        <v>134675.7623302708</v>
+        <v>136360.7363198806</v>
       </c>
       <c r="E24">
         <v>21035.19978699793</v>
@@ -3261,37 +3511,37 @@
         <v>4688</v>
       </c>
       <c r="M24">
-        <v>2293.323287900128</v>
+        <v>2175.297450748757</v>
       </c>
       <c r="N24">
-        <v>2394.676712099872</v>
+        <v>2512.702549251243</v>
       </c>
       <c r="O24">
-        <v>299.3345890124839</v>
+        <v>314.0878186564054</v>
       </c>
       <c r="P24">
-        <v>2095.342123087388</v>
+        <v>2198.614730594838</v>
       </c>
       <c r="Q24">
-        <v>3013.342123087388</v>
+        <v>3116.614730594838</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.116253448383718</v>
+        <v>0.1162205459287263</v>
       </c>
       <c r="T24">
         <v>1.372627513844084</v>
       </c>
       <c r="U24">
-        <v>0.07383661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3549,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.044195000650147</v>
+        <v>2.15510756857015</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3560,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1078261742799881</v>
+        <v>0.1042182933521317</v>
       </c>
       <c r="C25">
-        <v>96304.99203108212</v>
+        <v>104165.928520212</v>
       </c>
       <c r="D25">
-        <v>128303.2151708135</v>
+        <v>136164.1516599434</v>
       </c>
       <c r="E25">
         <v>22446.99209742103</v>
@@ -3343,45 +3593,45 @@
         <v>4688</v>
       </c>
       <c r="M25">
-        <v>2852.162379488192</v>
+        <v>2274.174607600973</v>
       </c>
       <c r="N25">
-        <v>1835.837620511808</v>
+        <v>2413.825392399027</v>
       </c>
       <c r="O25">
-        <v>229.479702563976</v>
+        <v>301.7281740498784</v>
       </c>
       <c r="P25">
-        <v>1606.357917947832</v>
+        <v>2112.097218349149</v>
       </c>
       <c r="Q25">
-        <v>2524.357917947832</v>
+        <v>3030.097218349149</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1170766950346145</v>
+        <v>0.1170434081153204</v>
       </c>
       <c r="T25">
         <v>1.388666629453386</v>
       </c>
       <c r="U25">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>1.643665183200839</v>
+        <v>2.061407239501883</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3642,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1080661101131384</v>
+        <v>0.1059405121723191</v>
       </c>
       <c r="C26">
-        <v>94398.7969263953</v>
+        <v>98854.86006209522</v>
       </c>
       <c r="D26">
-        <v>127808.8123765498</v>
+        <v>132264.8755122497</v>
       </c>
       <c r="E26">
         <v>23858.78440784414</v>
@@ -3425,45 +3675,45 @@
         <v>4688</v>
       </c>
       <c r="M26">
-        <v>2976.169439465939</v>
+        <v>2637.339284964394</v>
       </c>
       <c r="N26">
-        <v>1711.830560534061</v>
+        <v>2050.660715035606</v>
       </c>
       <c r="O26">
-        <v>213.9788200667576</v>
+        <v>256.3325893794507</v>
       </c>
       <c r="P26">
-        <v>1497.851740467303</v>
+        <v>1794.328125656155</v>
       </c>
       <c r="Q26">
-        <v>2415.851740467303</v>
+        <v>2712.328125656155</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1179216060710608</v>
+        <v>0.1178879245699828</v>
       </c>
       <c r="T26">
         <v>1.405127827052407</v>
       </c>
       <c r="U26">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971732</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.575179133900804</v>
+        <v>1.777549072554497</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3724,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1083060459462886</v>
+        <v>0.1069461059925065</v>
       </c>
       <c r="C27">
-        <v>92496.39745282094</v>
+        <v>95267.87213971815</v>
       </c>
       <c r="D27">
-        <v>127318.2052133985</v>
+        <v>130089.6799002957</v>
       </c>
       <c r="E27">
         <v>25270.57671826724</v>
@@ -3507,37 +3757,37 @@
         <v>4688</v>
       </c>
       <c r="M27">
-        <v>3100.176499443686</v>
+        <v>2884.878172104163</v>
       </c>
       <c r="N27">
-        <v>1587.823500556314</v>
+        <v>1803.121827895837</v>
       </c>
       <c r="O27">
-        <v>198.4779375695392</v>
+        <v>225.3902284869796</v>
       </c>
       <c r="P27">
-        <v>1389.345562986774</v>
+        <v>1577.731599408857</v>
       </c>
       <c r="Q27">
-        <v>2307.345562986774</v>
+        <v>2495.731599408857</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1187890480684791</v>
+        <v>0.1187549614634362</v>
       </c>
       <c r="T27">
         <v>1.422027989920735</v>
       </c>
       <c r="U27">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3795,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.512171968544772</v>
+        <v>1.62502529407704</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3806,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1201123357658796</v>
+        <v>0.1071326998126939</v>
       </c>
       <c r="C28">
-        <v>70857.06667832355</v>
+        <v>93460.30513792019</v>
       </c>
       <c r="D28">
-        <v>107090.6667493242</v>
+        <v>129693.9052089209</v>
       </c>
       <c r="E28">
         <v>26682.36902869034</v>
@@ -3589,45 +3839,45 @@
         <v>4688</v>
       </c>
       <c r="M28">
-        <v>5022.806962900467</v>
+        <v>3000.27329898833</v>
       </c>
       <c r="N28">
-        <v>-334.8069629004667</v>
+        <v>1687.72670101167</v>
       </c>
       <c r="O28">
-        <v>-41.85087036255834</v>
+        <v>210.9658376264588</v>
       </c>
       <c r="P28">
-        <v>-292.9560925379084</v>
+        <v>1476.760863385211</v>
       </c>
       <c r="Q28">
-        <v>625.0439074620916</v>
+        <v>2394.760863385211</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1198453616302685</v>
+        <v>0.1196454317864424</v>
       </c>
       <c r="T28">
-        <v>1.442607891847777</v>
+        <v>1.439384913947666</v>
       </c>
       <c r="U28">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V28">
-        <v>0.1166678322157953</v>
+        <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.1208721852287725</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.9333426577263624</v>
+        <v>1.562524321227923</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3888,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1210227019325049</v>
+        <v>0.1073192936328813</v>
       </c>
       <c r="C29">
-        <v>68149.23318265546</v>
+        <v>91655.13898006038</v>
       </c>
       <c r="D29">
-        <v>105794.6255640793</v>
+        <v>129300.5313614842</v>
       </c>
       <c r="E29">
         <v>28094.16133911345</v>
@@ -3671,45 +3921,45 @@
         <v>4688</v>
       </c>
       <c r="M29">
-        <v>5215.991846088947</v>
+        <v>3115.668425872497</v>
       </c>
       <c r="N29">
-        <v>-527.9918460889467</v>
+        <v>1572.331574127503</v>
       </c>
       <c r="O29">
-        <v>-65.99898076111833</v>
+        <v>196.5414467659379</v>
       </c>
       <c r="P29">
-        <v>-461.9928653278283</v>
+        <v>1375.790127361565</v>
       </c>
       <c r="Q29">
-        <v>456.0071346721717</v>
+        <v>2293.790127361565</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.120859681652601</v>
+        <v>0.1205602985566543</v>
       </c>
       <c r="T29">
-        <v>1.462369643790897</v>
+        <v>1.457217370139719</v>
       </c>
       <c r="U29">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V29">
-        <v>0.1123468013929881</v>
+        <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.1214634604670599</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.8987744111439044</v>
+        <v>1.504653050071333</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3970,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1219330680991302</v>
+        <v>0.1182942647238389</v>
       </c>
       <c r="C30">
-        <v>65472.3946823306</v>
+        <v>70668.42444449876</v>
       </c>
       <c r="D30">
-        <v>104529.5793741775</v>
+        <v>109725.6091363457</v>
       </c>
       <c r="E30">
         <v>29505.95364953655</v>
@@ -3753,37 +4003,37 @@
         <v>4688</v>
       </c>
       <c r="M30">
-        <v>5409.176729277427</v>
+        <v>4922.95545756771</v>
       </c>
       <c r="N30">
-        <v>-721.1767292774266</v>
+        <v>-234.9554575677103</v>
       </c>
       <c r="O30">
-        <v>-90.14709115967833</v>
+        <v>-29.36943219596378</v>
       </c>
       <c r="P30">
-        <v>-631.0296381177483</v>
+        <v>-205.5860253717465</v>
       </c>
       <c r="Q30">
-        <v>286.9703618822517</v>
+        <v>712.4139746282535</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1219021772311093</v>
+        <v>0.1216316169876492</v>
       </c>
       <c r="T30">
-        <v>1.482680333287993</v>
+        <v>1.478099360403758</v>
       </c>
       <c r="U30">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V30">
-        <v>0.1083344156289528</v>
+        <v>0.1190341868925878</v>
       </c>
       <c r="W30">
-        <v>0.1220125017597554</v>
+        <v>0.1097125017597554</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.866675325031622</v>
+        <v>0.9522734951407026</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +4052,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1228434342657556</v>
+        <v>0.1190816308904643</v>
       </c>
       <c r="C31">
-        <v>62825.45244147241</v>
+        <v>68077.6977790877</v>
       </c>
       <c r="D31">
-        <v>103294.4294437424</v>
+        <v>108546.6747813577</v>
       </c>
       <c r="E31">
         <v>30917.74595995965</v>
@@ -3835,37 +4085,37 @@
         <v>4688</v>
       </c>
       <c r="M31">
-        <v>5602.361612465906</v>
+        <v>5098.775295337986</v>
       </c>
       <c r="N31">
-        <v>-914.3616124659056</v>
+        <v>-410.7752953379859</v>
       </c>
       <c r="O31">
-        <v>-114.2952015582382</v>
+        <v>-51.34691191724824</v>
       </c>
       <c r="P31">
-        <v>-800.0664109076674</v>
+        <v>-359.4283834207376</v>
       </c>
       <c r="Q31">
-        <v>117.9335890923326</v>
+        <v>558.5716165792624</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1229740388822517</v>
+        <v>0.1226996679311372</v>
       </c>
       <c r="T31">
-        <v>1.503563154883598</v>
+        <v>1.498917661254515</v>
       </c>
       <c r="U31">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V31">
-        <v>0.1045987461245061</v>
+        <v>0.1149295597583607</v>
       </c>
       <c r="W31">
-        <v>0.1225236781357133</v>
+        <v>0.1102236781357133</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4123,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.836789968996049</v>
+        <v>0.9194364780668851</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4134,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1237538004323809</v>
+        <v>0.1198689970570896</v>
       </c>
       <c r="C32">
-        <v>60207.35904957709</v>
+        <v>65512.0356632364</v>
       </c>
       <c r="D32">
-        <v>102088.1283622702</v>
+        <v>107392.8049759295</v>
       </c>
       <c r="E32">
         <v>32329.53827038275</v>
@@ -3917,37 +4167,37 @@
         <v>4688</v>
       </c>
       <c r="M32">
-        <v>5795.546495654385</v>
+        <v>5274.595133108261</v>
       </c>
       <c r="N32">
-        <v>-1107.546495654385</v>
+        <v>-586.5951331082606</v>
       </c>
       <c r="O32">
-        <v>-138.4433119567981</v>
+        <v>-73.32439163853257</v>
       </c>
       <c r="P32">
-        <v>-969.1031836975866</v>
+        <v>-513.270741469728</v>
       </c>
       <c r="Q32">
-        <v>-51.10318369758659</v>
+        <v>404.729258530272</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1240765251519982</v>
+        <v>0.1237982346158678</v>
       </c>
       <c r="T32">
-        <v>1.525042628524792</v>
+        <v>1.520330770701008</v>
       </c>
       <c r="U32">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V32">
-        <v>0.1011121212536893</v>
+        <v>0.111098574433082</v>
       </c>
       <c r="W32">
-        <v>0.1230007760866073</v>
+        <v>0.1107007760866073</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +4205,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8088969700295141</v>
+        <v>0.8887885954646557</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4216,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1516394659842211</v>
+        <v>0.120656363223715</v>
       </c>
       <c r="C33">
-        <v>31898.27112403811</v>
+        <v>62970.64718308846</v>
       </c>
       <c r="D33">
-        <v>75190.83274715432</v>
+        <v>106263.2088062047</v>
       </c>
       <c r="E33">
         <v>33741.33058080586</v>
@@ -3999,45 +4249,45 @@
         <v>4688</v>
       </c>
       <c r="M33">
-        <v>9704.427560645432</v>
+        <v>5450.414970878536</v>
       </c>
       <c r="N33">
-        <v>-5016.427560645432</v>
+        <v>-762.4149708785362</v>
       </c>
       <c r="O33">
-        <v>-627.053445080679</v>
+        <v>-95.30187135981703</v>
       </c>
       <c r="P33">
-        <v>-4389.374115564753</v>
+        <v>-667.1130995187192</v>
       </c>
       <c r="Q33">
-        <v>-3471.374115564753</v>
+        <v>250.8869004812808</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1261621260748022</v>
+        <v>0.1249286438131992</v>
       </c>
       <c r="T33">
-        <v>1.565675887438504</v>
+        <v>1.542364549986529</v>
       </c>
       <c r="U33">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V33">
-        <v>0.06038480851528204</v>
+        <v>0.1075147494513696</v>
       </c>
       <c r="W33">
-        <v>0.2083470935245405</v>
+        <v>0.1111470935245405</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.4830784681222563</v>
+        <v>0.8601179956109571</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4298,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1533988321508464</v>
+        <v>0.1214437293903403</v>
       </c>
       <c r="C34">
-        <v>29257.02116494584</v>
+        <v>60452.7743548831</v>
       </c>
       <c r="D34">
-        <v>73961.37509848515</v>
+        <v>105157.1282884224</v>
       </c>
       <c r="E34">
         <v>35153.12289122897</v>
@@ -4081,45 +4331,45 @@
         <v>4688</v>
       </c>
       <c r="M34">
-        <v>10017.47361098883</v>
+        <v>5626.234808648812</v>
       </c>
       <c r="N34">
-        <v>-5329.473610988833</v>
+        <v>-938.2348086488118</v>
       </c>
       <c r="O34">
-        <v>-666.1842013736041</v>
+        <v>-117.2793510811015</v>
       </c>
       <c r="P34">
-        <v>-4663.289409615229</v>
+        <v>-820.9554575677104</v>
       </c>
       <c r="Q34">
-        <v>-3745.289409615229</v>
+        <v>97.04454243228963</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1273439220464905</v>
+        <v>0.1260923003398638</v>
       </c>
       <c r="T34">
-        <v>1.588700532842012</v>
+        <v>1.565046381603978</v>
       </c>
       <c r="U34">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.05849778324917948</v>
+        <v>0.1041549135310143</v>
       </c>
       <c r="W34">
-        <v>0.2087655161226028</v>
+        <v>0.1115655161226028</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.4679822659934358</v>
+        <v>0.8332393082481147</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4380,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1551581983174718</v>
+        <v>0.1222310955569657</v>
       </c>
       <c r="C35">
-        <v>26655.33049310677</v>
+        <v>57957.69042878406</v>
       </c>
       <c r="D35">
-        <v>72771.47673706918</v>
+        <v>104073.8366727465</v>
       </c>
       <c r="E35">
         <v>36564.91520165207</v>
@@ -4163,45 +4413,45 @@
         <v>4688</v>
       </c>
       <c r="M35">
-        <v>10330.51966133224</v>
+        <v>5802.054646419087</v>
       </c>
       <c r="N35">
-        <v>-5642.519661332235</v>
+        <v>-1114.054646419087</v>
       </c>
       <c r="O35">
-        <v>-705.3149576665294</v>
+        <v>-139.2568308023859</v>
       </c>
       <c r="P35">
-        <v>-4937.204703665706</v>
+        <v>-974.7978156167015</v>
       </c>
       <c r="Q35">
-        <v>-4019.204703665706</v>
+        <v>-56.79781561670154</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.128560995509871</v>
+        <v>0.1272906928822499</v>
       </c>
       <c r="T35">
-        <v>1.612412481093385</v>
+        <v>1.588405282821949</v>
       </c>
       <c r="U35">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V35">
-        <v>0.05672512315071949</v>
+        <v>0.1009987040300745</v>
       </c>
       <c r="W35">
-        <v>0.209158579775328</v>
+        <v>0.111958579775328</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.4538009852057558</v>
+        <v>0.8079896322405961</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4462,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1569175644840971</v>
+        <v>0.1517149560870955</v>
       </c>
       <c r="C36">
-        <v>24091.32003732568</v>
+        <v>27574.55546141365</v>
       </c>
       <c r="D36">
-        <v>71619.2585917112</v>
+        <v>75102.49401579917</v>
       </c>
       <c r="E36">
         <v>37976.70751207517</v>
@@ -4245,37 +4495,37 @@
         <v>4688</v>
       </c>
       <c r="M36">
-        <v>10643.56571167564</v>
+        <v>9923.551633359852</v>
       </c>
       <c r="N36">
-        <v>-5955.565711675636</v>
+        <v>-5235.551633359852</v>
       </c>
       <c r="O36">
-        <v>-744.4457139594545</v>
+        <v>-654.4439541699815</v>
       </c>
       <c r="P36">
-        <v>-5211.119997716181</v>
+        <v>-4581.10767918987</v>
       </c>
       <c r="Q36">
-        <v>-4293.119997716181</v>
+        <v>-3663.10767918987</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1298149499872932</v>
+        <v>0.129659482719109</v>
       </c>
       <c r="T36">
-        <v>1.636842973231164</v>
+        <v>1.634577405768538</v>
       </c>
       <c r="U36">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V36">
-        <v>0.05505673717569833</v>
+        <v>0.05905143860289423</v>
       </c>
       <c r="W36">
-        <v>0.2095285220367164</v>
+        <v>0.1945285220367164</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4404538974055866</v>
+        <v>0.4724115088231539</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4544,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1586769306507225</v>
+        <v>0.1533243222537209</v>
       </c>
       <c r="C37">
-        <v>21563.22787963842</v>
+        <v>25038.6694541895</v>
       </c>
       <c r="D37">
-        <v>70502.95874444704</v>
+        <v>73978.40031899812</v>
       </c>
       <c r="E37">
         <v>39388.49982249827</v>
@@ -4327,37 +4577,37 @@
         <v>4688</v>
       </c>
       <c r="M37">
-        <v>10956.61176201904</v>
+        <v>10215.42079904691</v>
       </c>
       <c r="N37">
-        <v>-6268.611762019036</v>
+        <v>-5527.420799046906</v>
       </c>
       <c r="O37">
-        <v>-783.5764702523795</v>
+        <v>-690.9275998808632</v>
       </c>
       <c r="P37">
-        <v>-5485.035291766657</v>
+        <v>-4836.493199166042</v>
       </c>
       <c r="Q37">
-        <v>-4567.035291766657</v>
+        <v>-3918.493199166042</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1311074876794054</v>
+        <v>0.1309496286070953</v>
       </c>
       <c r="T37">
-        <v>1.662025172819335</v>
+        <v>1.659724750472669</v>
       </c>
       <c r="U37">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V37">
-        <v>0.05348368754210695</v>
+        <v>0.05736425464281154</v>
       </c>
       <c r="W37">
-        <v>0.2098773247403112</v>
+        <v>0.1948773247403112</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4278695003368556</v>
+        <v>0.4589140371424922</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4626,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1604362968173478</v>
+        <v>0.1549336884203462</v>
       </c>
       <c r="C38">
-        <v>19069.40026533947</v>
+        <v>22535.93688271806</v>
       </c>
       <c r="D38">
-        <v>69420.92344057119</v>
+        <v>72887.46005794978</v>
       </c>
       <c r="E38">
         <v>40800.29213292137</v>
@@ -4409,37 +4659,37 @@
         <v>4688</v>
       </c>
       <c r="M38">
-        <v>11269.65781236244</v>
+        <v>10507.28996473396</v>
       </c>
       <c r="N38">
-        <v>-6581.657812362437</v>
+        <v>-5819.28996473396</v>
       </c>
       <c r="O38">
-        <v>-822.7072265453046</v>
+        <v>-727.411245591745</v>
       </c>
       <c r="P38">
-        <v>-5758.950585817132</v>
+        <v>-5091.878719142215</v>
       </c>
       <c r="Q38">
-        <v>-4840.950585817132</v>
+        <v>-4173.878719142215</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1324404171743961</v>
+        <v>0.1322800915540812</v>
       </c>
       <c r="T38">
-        <v>1.687994316144638</v>
+        <v>1.685657949698804</v>
       </c>
       <c r="U38">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V38">
-        <v>0.0519980295548262</v>
+        <v>0.05577080312495566</v>
       </c>
       <c r="W38">
-        <v>0.2102067495159285</v>
+        <v>0.1952067495159285</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4159842364386096</v>
+        <v>0.4461664249996453</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4708,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1621956629839731</v>
+        <v>0.1565430545869715</v>
       </c>
       <c r="C39">
-        <v>16608.28342833115</v>
+        <v>20064.91234661713</v>
       </c>
       <c r="D39">
-        <v>68371.59891398597</v>
+        <v>71828.22783227195</v>
       </c>
       <c r="E39">
         <v>42212.08444334447</v>
@@ -4491,37 +4741,37 @@
         <v>4688</v>
       </c>
       <c r="M39">
-        <v>11582.70386270584</v>
+        <v>10799.15913042101</v>
       </c>
       <c r="N39">
-        <v>-6894.703862705837</v>
+        <v>-6111.159130421014</v>
       </c>
       <c r="O39">
-        <v>-861.8379828382297</v>
+        <v>-763.8948913026268</v>
       </c>
       <c r="P39">
-        <v>-6032.865879867608</v>
+        <v>-5347.264239118387</v>
       </c>
       <c r="Q39">
-        <v>-5114.865879867608</v>
+        <v>-4429.264239118387</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1338156618914501</v>
+        <v>0.133652791420019</v>
       </c>
       <c r="T39">
-        <v>1.714787876718362</v>
+        <v>1.712414425090849</v>
       </c>
       <c r="U39">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.05059267740469577</v>
+        <v>0.05426348412157848</v>
       </c>
       <c r="W39">
-        <v>0.2105183675469178</v>
+        <v>0.1955183675469178</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4047414192375661</v>
+        <v>0.4341078729726279</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4790,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1639550291505985</v>
+        <v>0.1581524207535969</v>
       </c>
       <c r="C40">
-        <v>14178.41614681204</v>
+        <v>17624.23326271331</v>
       </c>
       <c r="D40">
-        <v>67353.52394288997</v>
+        <v>70799.34105879124</v>
       </c>
       <c r="E40">
         <v>43623.87675376759</v>
@@ -4573,37 +4823,37 @@
         <v>4688</v>
       </c>
       <c r="M40">
-        <v>11895.74991304924</v>
+        <v>11091.02829610807</v>
       </c>
       <c r="N40">
-        <v>-7207.74991304924</v>
+        <v>-6403.02829610807</v>
       </c>
       <c r="O40">
-        <v>-900.968739131155</v>
+        <v>-800.3785370135088</v>
       </c>
       <c r="P40">
-        <v>-6306.781173918085</v>
+        <v>-5602.649759094562</v>
       </c>
       <c r="Q40">
-        <v>-5388.781173918085</v>
+        <v>-4684.649759094562</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1352352693413121</v>
+        <v>0.1350697719267935</v>
       </c>
       <c r="T40">
-        <v>1.74244574569769</v>
+        <v>1.740034012592314</v>
       </c>
       <c r="U40">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.04926129115720377</v>
+        <v>0.05283549769732641</v>
       </c>
       <c r="W40">
-        <v>0.2108135846289077</v>
+        <v>0.1958135846289077</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3940903292576301</v>
+        <v>0.4226839815786113</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4872,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1657143953172238</v>
+        <v>0.1597617869202222</v>
       </c>
       <c r="C41">
-        <v>11778.42295429607</v>
+        <v>15212.6140173269</v>
       </c>
       <c r="D41">
-        <v>66365.32306079711</v>
+        <v>69799.51412382793</v>
       </c>
       <c r="E41">
         <v>45035.66906419069</v>
@@ -4655,37 +4905,37 @@
         <v>4688</v>
       </c>
       <c r="M41">
-        <v>12208.79596339264</v>
+        <v>11382.89746179512</v>
       </c>
       <c r="N41">
-        <v>-7520.79596339264</v>
+        <v>-6694.897461795124</v>
       </c>
       <c r="O41">
-        <v>-940.09949542408</v>
+        <v>-836.8621827243905</v>
       </c>
       <c r="P41">
-        <v>-6580.696467968561</v>
+        <v>-5858.035279070734</v>
       </c>
       <c r="Q41">
-        <v>-5662.696467968561</v>
+        <v>-4940.035279070734</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1367014212977271</v>
+        <v>0.1365332108108393</v>
       </c>
       <c r="T41">
-        <v>1.77101043005339</v>
+        <v>1.768559160339729</v>
       </c>
       <c r="U41">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.04799818112753187</v>
+        <v>0.05148074134611291</v>
       </c>
       <c r="W41">
-        <v>0.2110936623733597</v>
+        <v>0.1960936623733597</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4943,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.383985449020255</v>
+        <v>0.4118459307689033</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4954,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1674737614838492</v>
+        <v>0.1613711530868476</v>
       </c>
       <c r="C42">
-        <v>9407.007939631803</v>
+        <v>12828.84060714474</v>
       </c>
       <c r="D42">
-        <v>65405.70035655594</v>
+        <v>68827.53302406888</v>
       </c>
       <c r="E42">
         <v>46447.46137461379</v>
@@ -4737,37 +4987,37 @@
         <v>4688</v>
       </c>
       <c r="M42">
-        <v>12521.84201373604</v>
+        <v>11674.76662748218</v>
       </c>
       <c r="N42">
-        <v>-7833.842013736043</v>
+        <v>-6986.766627482179</v>
       </c>
       <c r="O42">
-        <v>-979.2302517170053</v>
+        <v>-873.3458284352723</v>
       </c>
       <c r="P42">
-        <v>-6854.611762019037</v>
+        <v>-6113.420799046906</v>
       </c>
       <c r="Q42">
-        <v>-5936.611762019037</v>
+        <v>-5195.420799046906</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1382164449860226</v>
+        <v>0.1380454309910199</v>
       </c>
       <c r="T42">
-        <v>1.80052727055428</v>
+        <v>1.798035146345392</v>
       </c>
       <c r="U42">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.04679822659934357</v>
+        <v>0.0501937228124601</v>
       </c>
       <c r="W42">
-        <v>0.211359736230589</v>
+        <v>0.1963597362305891</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +5025,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3743858127947486</v>
+        <v>0.4015497824996808</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +5036,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1692331276504745</v>
+        <v>0.1629805192534729</v>
       </c>
       <c r="C43">
-        <v>7062.949077253448</v>
+        <v>10471.76572170915</v>
       </c>
       <c r="D43">
-        <v>64473.43380460069</v>
+        <v>67882.25044905639</v>
       </c>
       <c r="E43">
         <v>47859.25368503689</v>
@@ -4819,37 +5069,37 @@
         <v>4688</v>
       </c>
       <c r="M43">
-        <v>12834.88806407944</v>
+        <v>11966.63579316923</v>
       </c>
       <c r="N43">
-        <v>-8146.888064079443</v>
+        <v>-7278.635793169233</v>
       </c>
       <c r="O43">
-        <v>-1018.36100800993</v>
+        <v>-909.8294741461541</v>
       </c>
       <c r="P43">
-        <v>-7128.527056069513</v>
+        <v>-6368.806319023079</v>
       </c>
       <c r="Q43">
-        <v>-6210.527056069513</v>
+        <v>-5450.806319023079</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1397828254095145</v>
+        <v>0.1396089128722237</v>
       </c>
       <c r="T43">
-        <v>1.831044681919607</v>
+        <v>1.828510318317347</v>
       </c>
       <c r="U43">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.04565680643838398</v>
+        <v>0.04896948567069277</v>
       </c>
       <c r="W43">
-        <v>0.2116128308752706</v>
+        <v>0.1966128308752706</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +5107,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3652544515070718</v>
+        <v>0.3917558853655422</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +5118,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1709924938170999</v>
+        <v>0.1645898854200983</v>
       </c>
       <c r="C44">
-        <v>4745.093035503989</v>
+        <v>8140.304225641601</v>
       </c>
       <c r="D44">
-        <v>63567.37007327432</v>
+        <v>66962.58126341194</v>
       </c>
       <c r="E44">
         <v>49271.04599545999</v>
@@ -4901,37 +5151,37 @@
         <v>4688</v>
       </c>
       <c r="M44">
-        <v>13147.93411442284</v>
+        <v>12258.50495885629</v>
       </c>
       <c r="N44">
-        <v>-8459.934114422842</v>
+        <v>-7570.504958856285</v>
       </c>
       <c r="O44">
-        <v>-1057.491764302855</v>
+        <v>-946.3131198570356</v>
       </c>
       <c r="P44">
-        <v>-7402.442350119987</v>
+        <v>-6624.19183899925</v>
       </c>
       <c r="Q44">
-        <v>-6484.442350119987</v>
+        <v>-5706.19183899925</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1414032189510578</v>
+        <v>0.1412263079217447</v>
       </c>
       <c r="T44">
-        <v>1.862614417814772</v>
+        <v>1.860036358288336</v>
       </c>
       <c r="U44">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.04456973961842246</v>
+        <v>0.04780354553567628</v>
       </c>
       <c r="W44">
-        <v>0.211853873394015</v>
+        <v>0.196853873394015</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +5189,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3565579169473797</v>
+        <v>0.3824283642854103</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5200,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1727518599837252</v>
+        <v>0.1661992515867236</v>
       </c>
       <c r="C45">
-        <v>2452.350416652116</v>
+        <v>5833.429003198791</v>
       </c>
       <c r="D45">
-        <v>62686.41976484556</v>
+        <v>66067.49835139223</v>
       </c>
       <c r="E45">
         <v>50682.8383058831</v>
@@ -4983,37 +5233,37 @@
         <v>4688</v>
       </c>
       <c r="M45">
-        <v>13460.98016476624</v>
+        <v>12550.37412454334</v>
       </c>
       <c r="N45">
-        <v>-8772.980164766244</v>
+        <v>-7862.374124543341</v>
       </c>
       <c r="O45">
-        <v>-1096.622520595781</v>
+        <v>-982.7967655679176</v>
       </c>
       <c r="P45">
-        <v>-7676.357644170464</v>
+        <v>-6879.577358975424</v>
       </c>
       <c r="Q45">
-        <v>-6758.357644170464</v>
+        <v>-5961.577358975424</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1430804684063395</v>
+        <v>0.1429004536747578</v>
       </c>
       <c r="T45">
-        <v>1.895291863741347</v>
+        <v>1.892668575100412</v>
       </c>
       <c r="U45">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.04353323404590101</v>
+        <v>0.04669183517438148</v>
       </c>
       <c r="W45">
-        <v>0.2120837046328178</v>
+        <v>0.1970837046328178</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3482658723672081</v>
+        <v>0.3735346813950519</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5282,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1745112261503505</v>
+        <v>0.1678086177533489</v>
       </c>
       <c r="C46">
-        <v>183.6913872971709</v>
+        <v>3550.167131705399</v>
       </c>
       <c r="D46">
-        <v>61829.55304591372</v>
+        <v>65196.02879032194</v>
       </c>
       <c r="E46">
         <v>52094.6306163062</v>
@@ -5065,37 +5315,37 @@
         <v>4688</v>
       </c>
       <c r="M46">
-        <v>13774.02621510964</v>
+        <v>12842.2432902304</v>
       </c>
       <c r="N46">
-        <v>-9086.026215109645</v>
+        <v>-8154.243290230395</v>
       </c>
       <c r="O46">
-        <v>-1135.753276888706</v>
+        <v>-1019.280411278799</v>
       </c>
       <c r="P46">
-        <v>-7950.272938220939</v>
+        <v>-7134.962878951595</v>
       </c>
       <c r="Q46">
-        <v>-7032.272938220939</v>
+        <v>-6216.962878951595</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1448176196278813</v>
+        <v>0.1446343903475213</v>
       </c>
       <c r="T46">
-        <v>1.929136361308157</v>
+        <v>1.926466228227205</v>
       </c>
       <c r="U46">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.04254384236303962</v>
+        <v>0.04563065710223645</v>
       </c>
       <c r="W46">
-        <v>0.2123030889971295</v>
+        <v>0.1973030889971295</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5353,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.340350738904317</v>
+        <v>0.3650452568178916</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5364,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1762705923169759</v>
+        <v>0.1694179839199743</v>
       </c>
       <c r="C47">
-        <v>-2061.858337687736</v>
+        <v>1289.596353891975</v>
       </c>
       <c r="D47">
-        <v>60995.79563135192</v>
+        <v>64347.25032293163</v>
       </c>
       <c r="E47">
         <v>53506.42292672931</v>
@@ -5147,37 +5397,37 @@
         <v>4688</v>
       </c>
       <c r="M47">
-        <v>14087.07226545305</v>
+        <v>13134.11245591745</v>
       </c>
       <c r="N47">
-        <v>-9399.072265453047</v>
+        <v>-8446.112455917451</v>
       </c>
       <c r="O47">
-        <v>-1174.884033181631</v>
+        <v>-1055.764056989681</v>
       </c>
       <c r="P47">
-        <v>-8224.188232271415</v>
+        <v>-7390.34839892777</v>
       </c>
       <c r="Q47">
-        <v>-7306.188232271415</v>
+        <v>-6472.34839892777</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1466179399847519</v>
+        <v>0.1464313792629308</v>
       </c>
       <c r="T47">
-        <v>1.964211567877396</v>
+        <v>1.961492886922245</v>
       </c>
       <c r="U47">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.04159842364386096</v>
+        <v>0.04461664249996453</v>
       </c>
       <c r="W47">
-        <v>0.2125127229452496</v>
+        <v>0.1975127229452496</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3327873891508877</v>
+        <v>0.3569331399997162</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5446,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1780299584836012</v>
+        <v>0.1710273500865996</v>
       </c>
       <c r="C48">
-        <v>-4285.221190602562</v>
+        <v>-949.158177751051</v>
       </c>
       <c r="D48">
-        <v>60184.22508886019</v>
+        <v>63520.2881017117</v>
       </c>
       <c r="E48">
         <v>54918.21523715241</v>
@@ -5229,37 +5479,37 @@
         <v>4688</v>
       </c>
       <c r="M48">
-        <v>14400.11831579645</v>
+        <v>13425.98162160451</v>
       </c>
       <c r="N48">
-        <v>-9712.118315796448</v>
+        <v>-8737.981621604506</v>
       </c>
       <c r="O48">
-        <v>-1214.014789474556</v>
+        <v>-1092.247702700563</v>
       </c>
       <c r="P48">
-        <v>-8498.103526321891</v>
+        <v>-7645.733918903942</v>
       </c>
       <c r="Q48">
-        <v>-7580.103526321891</v>
+        <v>-6727.733918903942</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1484849388733584</v>
+        <v>0.1482949233233555</v>
       </c>
       <c r="T48">
-        <v>2.000585856171422</v>
+        <v>1.997816829272657</v>
       </c>
       <c r="U48">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.04069411008638572</v>
+        <v>0.04364671548909573</v>
       </c>
       <c r="W48">
-        <v>0.2127132423738863</v>
+        <v>0.1977132423738862</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3255528806910858</v>
+        <v>0.3491737239127658</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5528,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1797893246502266</v>
+        <v>0.172636716253225</v>
       </c>
       <c r="C49">
-        <v>-6487.27115522547</v>
+        <v>-3166.926908764348</v>
       </c>
       <c r="D49">
-        <v>59393.96743466039</v>
+        <v>62714.31168112151</v>
       </c>
       <c r="E49">
         <v>56330.00754757551</v>
@@ -5311,37 +5561,37 @@
         <v>4688</v>
       </c>
       <c r="M49">
-        <v>14713.16436613985</v>
+        <v>13717.85078729156</v>
       </c>
       <c r="N49">
-        <v>-10025.16436613985</v>
+        <v>-9029.85078729156</v>
       </c>
       <c r="O49">
-        <v>-1253.145545767481</v>
+        <v>-1128.731348411445</v>
       </c>
       <c r="P49">
-        <v>-8772.018820372368</v>
+        <v>-7901.119438880115</v>
       </c>
       <c r="Q49">
-        <v>-7854.018820372368</v>
+        <v>-6983.119438880115</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1504223905502142</v>
+        <v>0.1502287898011546</v>
       </c>
       <c r="T49">
-        <v>2.038332759118053</v>
+        <v>2.035511486428745</v>
       </c>
       <c r="U49">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.03982827795688815</v>
+        <v>0.04271806196805114</v>
       </c>
       <c r="W49">
-        <v>0.2129052290608787</v>
+        <v>0.1979052290608787</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5599,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3186262236551052</v>
+        <v>0.3417444957444091</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5610,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1815486908168519</v>
+        <v>0.1742460824198503</v>
       </c>
       <c r="C50">
-        <v>-8668.836906389661</v>
+        <v>-5364.498664393737</v>
       </c>
       <c r="D50">
-        <v>58624.1939939193</v>
+        <v>61928.53223591523</v>
       </c>
       <c r="E50">
         <v>57741.79985799862</v>
@@ -5393,37 +5643,37 @@
         <v>4688</v>
       </c>
       <c r="M50">
-        <v>15026.21041648325</v>
+        <v>14009.71995297861</v>
       </c>
       <c r="N50">
-        <v>-10338.21041648325</v>
+        <v>-9321.719952978614</v>
       </c>
       <c r="O50">
-        <v>-1292.276302060406</v>
+        <v>-1165.214994122327</v>
       </c>
       <c r="P50">
-        <v>-9045.934114422844</v>
+        <v>-8156.504958856287</v>
       </c>
       <c r="Q50">
-        <v>-8127.934114422844</v>
+        <v>-7238.504958856287</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1524343595992568</v>
+        <v>0.1522370357588692</v>
       </c>
       <c r="T50">
-        <v>2.077531466024169</v>
+        <v>2.074655938090836</v>
       </c>
       <c r="U50">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.03899852216611965</v>
+        <v>0.04182810234371674</v>
       </c>
       <c r="W50">
-        <v>0.2130892163025799</v>
+        <v>0.1980892163025799</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3119881773289572</v>
+        <v>0.3346248187497339</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5692,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1833080569834772</v>
+        <v>0.1758554485864756</v>
       </c>
       <c r="C51">
-        <v>-10830.70470854177</v>
+        <v>-7542.623224733914</v>
       </c>
       <c r="D51">
-        <v>57874.1185021903</v>
+        <v>61162.19998599815</v>
       </c>
       <c r="E51">
         <v>59153.59216842172</v>
@@ -5475,37 +5725,37 @@
         <v>4688</v>
       </c>
       <c r="M51">
-        <v>15339.25646682665</v>
+        <v>14301.58911866567</v>
       </c>
       <c r="N51">
-        <v>-10651.25646682665</v>
+        <v>-9613.589118665668</v>
       </c>
       <c r="O51">
-        <v>-1331.407058353331</v>
+        <v>-1201.698639833209</v>
       </c>
       <c r="P51">
-        <v>-9319.849408473319</v>
+        <v>-8411.89047883246</v>
       </c>
       <c r="Q51">
-        <v>-8401.849408473319</v>
+        <v>-7493.89047883246</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1545252293953206</v>
+        <v>0.1543240364600234</v>
       </c>
       <c r="T51">
-        <v>2.118267377122682</v>
+        <v>2.115335466288696</v>
       </c>
       <c r="U51">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.03820263395864782</v>
+        <v>0.04097446760200824</v>
       </c>
       <c r="W51">
-        <v>0.2132656938609463</v>
+        <v>0.1982656938609463</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3056210716691825</v>
+        <v>0.3277957408160659</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5774,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1850674231501026</v>
+        <v>0.177464814753101</v>
       </c>
       <c r="C52">
-        <v>-12973.62109459508</v>
+        <v>-9702.013711013045</v>
       </c>
       <c r="D52">
-        <v>57142.99442656009</v>
+        <v>60414.60181014212</v>
       </c>
       <c r="E52">
         <v>60565.38447884482</v>
@@ -5557,37 +5807,37 @@
         <v>4688</v>
       </c>
       <c r="M52">
-        <v>15652.30251717005</v>
+        <v>14593.45828435272</v>
       </c>
       <c r="N52">
-        <v>-10964.30251717005</v>
+        <v>-9905.458284352722</v>
       </c>
       <c r="O52">
-        <v>-1370.537814646256</v>
+        <v>-1238.18228554409</v>
       </c>
       <c r="P52">
-        <v>-9593.764702523795</v>
+        <v>-8667.275998808633</v>
       </c>
       <c r="Q52">
-        <v>-8675.764702523795</v>
+        <v>-7749.275998808633</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1566997339832271</v>
+        <v>0.1564945171892239</v>
       </c>
       <c r="T52">
-        <v>2.160632724665136</v>
+        <v>2.15764217561447</v>
       </c>
       <c r="U52">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.03743858127947487</v>
+        <v>0.04015497824996807</v>
       </c>
       <c r="W52">
-        <v>0.2134351123169781</v>
+        <v>0.1984351123169781</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2995086502357989</v>
+        <v>0.3212398259997447</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5856,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1868267893167279</v>
+        <v>0.1790741809197263</v>
       </c>
       <c r="C53">
-        <v>-15098.29534426422</v>
+        <v>-11843.34879898244</v>
       </c>
       <c r="D53">
-        <v>56430.11248731405</v>
+        <v>59685.05903259583</v>
       </c>
       <c r="E53">
         <v>61977.17678926792</v>
@@ -5639,37 +5889,37 @@
         <v>4688</v>
       </c>
       <c r="M53">
-        <v>15965.34856751345</v>
+        <v>14885.32745003978</v>
       </c>
       <c r="N53">
-        <v>-11277.34856751345</v>
+        <v>-10197.32745003978</v>
       </c>
       <c r="O53">
-        <v>-1409.668570939182</v>
+        <v>-1274.665931254972</v>
       </c>
       <c r="P53">
-        <v>-9867.67999657427</v>
+        <v>-8922.661518784804</v>
       </c>
       <c r="Q53">
-        <v>-8949.67999657427</v>
+        <v>-8004.661518784804</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1589629938604358</v>
+        <v>0.1587535889685958</v>
       </c>
       <c r="T53">
-        <v>2.204727270066465</v>
+        <v>2.20167568940252</v>
       </c>
       <c r="U53">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.03670449145046555</v>
+        <v>0.03936762573526282</v>
       </c>
       <c r="W53">
-        <v>0.213597886911989</v>
+        <v>0.1985978869119889</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2936359316037245</v>
+        <v>0.3149410058821026</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5938,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1885861554833533</v>
+        <v>0.1806835470863516</v>
       </c>
       <c r="C54">
-        <v>-17205.40177917622</v>
+        <v>-13967.27477385166</v>
       </c>
       <c r="D54">
-        <v>55734.79836282515</v>
+        <v>58972.92536814971</v>
       </c>
       <c r="E54">
         <v>63388.96909969102</v>
@@ -5721,37 +5971,37 @@
         <v>4688</v>
       </c>
       <c r="M54">
-        <v>16278.39461785685</v>
+        <v>15177.19661572683</v>
       </c>
       <c r="N54">
-        <v>-11590.39461785685</v>
+        <v>-10489.19661572683</v>
       </c>
       <c r="O54">
-        <v>-1448.799327232107</v>
+        <v>-1311.149576965854</v>
       </c>
       <c r="P54">
-        <v>-10141.59529062475</v>
+        <v>-9178.047038760977</v>
       </c>
       <c r="Q54">
-        <v>-9223.595290624746</v>
+        <v>-8260.047038760977</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1613205562325282</v>
+        <v>0.1611067887387749</v>
       </c>
       <c r="T54">
-        <v>2.25065908819285</v>
+        <v>2.247543932931739</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.03599863584564891</v>
+        <v>0.03861055600958469</v>
       </c>
       <c r="W54">
-        <v>0.2137544009456533</v>
+        <v>0.1987544009456533</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +6009,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2879890867651913</v>
+        <v>0.3088844480766775</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +6020,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1903455216499786</v>
+        <v>0.182292913252977</v>
       </c>
       <c r="C55">
-        <v>-19295.58189036905</v>
+        <v>-16074.40743984705</v>
       </c>
       <c r="D55">
-        <v>55056.41056205543</v>
+        <v>58277.58501257743</v>
       </c>
       <c r="E55">
         <v>64800.76141011414</v>
@@ -5803,37 +6053,37 @@
         <v>4688</v>
       </c>
       <c r="M55">
-        <v>16591.44066820026</v>
+        <v>15469.06578141389</v>
       </c>
       <c r="N55">
-        <v>-11903.44066820026</v>
+        <v>-10781.06578141389</v>
       </c>
       <c r="O55">
-        <v>-1487.930083525032</v>
+        <v>-1347.633222676736</v>
       </c>
       <c r="P55">
-        <v>-10415.51058467522</v>
+        <v>-9433.432558737153</v>
       </c>
       <c r="Q55">
-        <v>-9497.510584675223</v>
+        <v>-8515.432558737153</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1637784404076884</v>
+        <v>0.1635601246693871</v>
       </c>
       <c r="T55">
-        <v>2.298545451771422</v>
+        <v>2.295364016611138</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.03531941630139138</v>
+        <v>0.03788205495280007</v>
       </c>
       <c r="W55">
-        <v>0.213905008789368</v>
+        <v>0.198905008789368</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +6091,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.282555330411131</v>
+        <v>0.3030564396224005</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +6102,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1921048878166039</v>
+        <v>0.1839022794196024</v>
       </c>
       <c r="C56">
-        <v>-21369.4463122867</v>
+        <v>-18165.33389625271</v>
       </c>
       <c r="D56">
-        <v>54394.33845056088</v>
+        <v>57598.45086659487</v>
       </c>
       <c r="E56">
         <v>66212.55372053724</v>
@@ -5885,37 +6135,37 @@
         <v>4688</v>
       </c>
       <c r="M56">
-        <v>16904.48671854366</v>
+        <v>15760.93494710094</v>
       </c>
       <c r="N56">
-        <v>-12216.48671854366</v>
+        <v>-11072.93494710094</v>
       </c>
       <c r="O56">
-        <v>-1527.060839817957</v>
+        <v>-1384.116868387618</v>
       </c>
       <c r="P56">
-        <v>-10689.4258787257</v>
+        <v>-9688.818078713324</v>
       </c>
       <c r="Q56">
-        <v>-9771.425878725699</v>
+        <v>-8770.818078713324</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1663431891122033</v>
+        <v>0.1661201273795912</v>
       </c>
       <c r="T56">
-        <v>2.348513831157756</v>
+        <v>2.345263234363554</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.0346653530365508</v>
+        <v>0.03718053541663711</v>
       </c>
       <c r="W56">
-        <v>0.214050038564797</v>
+        <v>0.199050038564797</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2773228242924064</v>
+        <v>0.2974442833330968</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6184,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1938642539832293</v>
+        <v>0.1855116455862277</v>
       </c>
       <c r="C57">
-        <v>-23427.57665603906</v>
+        <v>-20240.61419070016</v>
       </c>
       <c r="D57">
-        <v>53748.00041723163</v>
+        <v>56934.96288257053</v>
       </c>
       <c r="E57">
         <v>67624.34603096034</v>
@@ -5967,37 +6217,37 @@
         <v>4688</v>
       </c>
       <c r="M57">
-        <v>17217.53276888706</v>
+        <v>16052.804112788</v>
       </c>
       <c r="N57">
-        <v>-12529.53276888706</v>
+        <v>-11364.804112788</v>
       </c>
       <c r="O57">
-        <v>-1566.191596110882</v>
+        <v>-1420.600514098499</v>
       </c>
       <c r="P57">
-        <v>-10963.34117277617</v>
+        <v>-9944.203598689495</v>
       </c>
       <c r="Q57">
-        <v>-10045.34117277617</v>
+        <v>-9026.203598689495</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1690219266480301</v>
+        <v>0.1687939079880266</v>
       </c>
       <c r="T57">
-        <v>2.400703027405707</v>
+        <v>2.397380195127189</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.03403507389043169</v>
+        <v>0.03650452568178916</v>
       </c>
       <c r="W57">
-        <v>0.2141897945302104</v>
+        <v>0.1991897945302104</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2722805911234536</v>
+        <v>0.2920362054543133</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6266,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1956236201498546</v>
+        <v>0.1871210117528531</v>
       </c>
       <c r="C58">
-        <v>-25470.52721349466</v>
+        <v>-22300.78285949187</v>
       </c>
       <c r="D58">
-        <v>53116.84217019913</v>
+        <v>56286.58652420192</v>
       </c>
       <c r="E58">
         <v>69036.13834138344</v>
@@ -6049,37 +6299,37 @@
         <v>4688</v>
       </c>
       <c r="M58">
-        <v>17530.57881923046</v>
+        <v>16344.67327847505</v>
       </c>
       <c r="N58">
-        <v>-12842.57881923046</v>
+        <v>-11656.67327847505</v>
       </c>
       <c r="O58">
-        <v>-1605.322352403807</v>
+        <v>-1457.084159809381</v>
       </c>
       <c r="P58">
-        <v>-11237.25646682665</v>
+        <v>-10199.58911866567</v>
       </c>
       <c r="Q58">
-        <v>-10319.25646682665</v>
+        <v>-9281.589118665668</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1718224249809399</v>
+        <v>0.1715892240786636</v>
       </c>
       <c r="T58">
-        <v>2.455264459846746</v>
+        <v>2.451866108652807</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.03342730471381684</v>
+        <v>0.03585265915175721</v>
       </c>
       <c r="W58">
-        <v>0.2143245592111448</v>
+        <v>0.1993245592111448</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6337,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2674184377105348</v>
+        <v>0.2868212732140577</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6348,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.19738298631648</v>
+        <v>0.1887303779194784</v>
       </c>
       <c r="C59">
-        <v>-27498.82654270097</v>
+        <v>-24346.35036386228</v>
       </c>
       <c r="D59">
-        <v>52500.33515141594</v>
+        <v>55652.81133025463</v>
       </c>
       <c r="E59">
         <v>70447.93065180656</v>
@@ -6131,37 +6381,37 @@
         <v>4688</v>
       </c>
       <c r="M59">
-        <v>17843.62486957386</v>
+        <v>16636.54244416211</v>
       </c>
       <c r="N59">
-        <v>-13155.62486957386</v>
+        <v>-11948.54244416211</v>
       </c>
       <c r="O59">
-        <v>-1644.453108696733</v>
+        <v>-1493.567805520263</v>
       </c>
       <c r="P59">
-        <v>-11511.17176087713</v>
+        <v>-10454.97463864184</v>
       </c>
       <c r="Q59">
-        <v>-10593.17176087713</v>
+        <v>-9536.974638641845</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1747531790502641</v>
+        <v>0.1745145548711906</v>
       </c>
       <c r="T59">
-        <v>2.512363633331554</v>
+        <v>2.5088862507145</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.03284086077146917</v>
+        <v>0.03522366513155094</v>
       </c>
       <c r="W59">
-        <v>0.2144545953067832</v>
+        <v>0.1994545953067832</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2627268861717534</v>
+        <v>0.2817893210524075</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6430,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1991423524831053</v>
+        <v>0.1903397440861037</v>
       </c>
       <c r="C60">
-        <v>-29512.97894416327</v>
+        <v>-26377.80443028748</v>
       </c>
       <c r="D60">
-        <v>51897.97506037672</v>
+        <v>55033.14957425251</v>
       </c>
       <c r="E60">
         <v>71859.72296222964</v>
@@ -6213,37 +6463,37 @@
         <v>4688</v>
       </c>
       <c r="M60">
-        <v>18156.67091991726</v>
+        <v>16928.41160984916</v>
       </c>
       <c r="N60">
-        <v>-13468.67091991726</v>
+        <v>-12240.41160984916</v>
       </c>
       <c r="O60">
-        <v>-1683.583864989657</v>
+        <v>-1530.051451231145</v>
       </c>
       <c r="P60">
-        <v>-11785.0870549276</v>
+        <v>-10710.36015861801</v>
       </c>
       <c r="Q60">
-        <v>-10867.0870549276</v>
+        <v>-9792.360158618012</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1778234928371751</v>
+        <v>0.1775791871300284</v>
       </c>
       <c r="T60">
-        <v>2.572181815077543</v>
+        <v>2.568621637636273</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.03227463903403006</v>
+        <v>0.03461636056031731</v>
       </c>
       <c r="W60">
-        <v>0.2145801473991237</v>
+        <v>0.1995801473991237</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2581971122722405</v>
+        <v>0.2769308844825384</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6512,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2009017186497306</v>
+        <v>0.191949110252729</v>
       </c>
       <c r="C61">
-        <v>-31513.46583664832</v>
+        <v>-28395.61130223941</v>
       </c>
       <c r="D61">
-        <v>51309.28047831477</v>
+        <v>54427.13501272369</v>
       </c>
       <c r="E61">
         <v>73271.51527265274</v>
@@ -6295,37 +6545,37 @@
         <v>4688</v>
       </c>
       <c r="M61">
-        <v>18469.71697026066</v>
+        <v>17220.28077553621</v>
       </c>
       <c r="N61">
-        <v>-13781.71697026066</v>
+        <v>-12532.28077553621</v>
       </c>
       <c r="O61">
-        <v>-1722.714621282582</v>
+        <v>-1566.535096942026</v>
       </c>
       <c r="P61">
-        <v>-12059.00234897808</v>
+        <v>-10965.74567859418</v>
       </c>
       <c r="Q61">
-        <v>-11141.00234897808</v>
+        <v>-10047.74567859418</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1810435780283257</v>
+        <v>0.180793313645395</v>
       </c>
       <c r="T61">
-        <v>2.634917956908702</v>
+        <v>2.631270945871304</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.03172761125379226</v>
+        <v>0.03402964258471871</v>
       </c>
       <c r="W61">
-        <v>0.2147014434883341</v>
+        <v>0.199701443488334</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2538208900303381</v>
+        <v>0.2722371406777496</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6594,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.202661084816356</v>
+        <v>0.1935584764193544</v>
       </c>
       <c r="C62">
-        <v>-33500.74704040097</v>
+        <v>-30400.2169101361</v>
       </c>
       <c r="D62">
-        <v>50733.79158498522</v>
+        <v>53834.32171525009</v>
       </c>
       <c r="E62">
         <v>74683.30758307585</v>
@@ -6377,37 +6627,37 @@
         <v>4688</v>
       </c>
       <c r="M62">
-        <v>18782.76302060406</v>
+        <v>17512.14994122327</v>
       </c>
       <c r="N62">
-        <v>-14094.76302060406</v>
+        <v>-12824.14994122327</v>
       </c>
       <c r="O62">
-        <v>-1761.845377575507</v>
+        <v>-1603.018742652908</v>
       </c>
       <c r="P62">
-        <v>-12332.91764302855</v>
+        <v>-11221.13119857036</v>
       </c>
       <c r="Q62">
-        <v>-11414.91764302855</v>
+        <v>-10303.13119857036</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1844246674790338</v>
+        <v>0.1841681464865299</v>
       </c>
       <c r="T62">
-        <v>2.70079090583142</v>
+        <v>2.697052719518087</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.03119881773289572</v>
+        <v>0.0334624818749734</v>
       </c>
       <c r="W62">
-        <v>0.2148186963745707</v>
+        <v>0.1998186963745707</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2495905418631658</v>
+        <v>0.2676998549997872</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6676,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2044204509829813</v>
+        <v>0.1951678425859797</v>
       </c>
       <c r="C63">
-        <v>-35475.261974963</v>
+        <v>-32392.04796565838</v>
       </c>
       <c r="D63">
-        <v>50171.06896084629</v>
+        <v>53254.28297015091</v>
       </c>
       <c r="E63">
         <v>76095.09989349895</v>
@@ -6459,37 +6709,37 @@
         <v>4688</v>
       </c>
       <c r="M63">
-        <v>19095.80907094746</v>
+        <v>17804.01910691032</v>
       </c>
       <c r="N63">
-        <v>-14407.80907094746</v>
+        <v>-13116.01910691032</v>
       </c>
       <c r="O63">
-        <v>-1800.976133868432</v>
+        <v>-1639.50238836379</v>
       </c>
       <c r="P63">
-        <v>-12606.83293707903</v>
+        <v>-11476.51671854653</v>
       </c>
       <c r="Q63">
-        <v>-11688.83293707903</v>
+        <v>-10558.51671854653</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1879791461323424</v>
+        <v>0.1877160476784922</v>
       </c>
       <c r="T63">
-        <v>2.770041954698892</v>
+        <v>2.766207917454448</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.0306873617044876</v>
+        <v>0.03291391659833449</v>
       </c>
       <c r="W63">
-        <v>0.2149321049038816</v>
+        <v>0.1999321049038816</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2454988936359008</v>
+        <v>0.263311332786676</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6758,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2061798171496066</v>
+        <v>0.1967772087526051</v>
       </c>
       <c r="C64">
-        <v>-37437.43077815141</v>
+        <v>-34371.51298607638</v>
       </c>
       <c r="D64">
-        <v>49620.692468081</v>
+        <v>52686.61026015603</v>
       </c>
       <c r="E64">
         <v>77506.89220392206</v>
@@ -6541,37 +6791,37 @@
         <v>4688</v>
       </c>
       <c r="M64">
-        <v>19408.85512129086</v>
+        <v>18095.88827259738</v>
       </c>
       <c r="N64">
-        <v>-14720.85512129086</v>
+        <v>-13407.88827259738</v>
       </c>
       <c r="O64">
-        <v>-1840.106890161358</v>
+        <v>-1675.986034074672</v>
       </c>
       <c r="P64">
-        <v>-12880.74823112951</v>
+        <v>-11731.90223852271</v>
       </c>
       <c r="Q64">
-        <v>-11962.74823112951</v>
+        <v>-10813.90223852271</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1917207026095093</v>
+        <v>0.1914506805121367</v>
       </c>
       <c r="T64">
-        <v>2.842937795612021</v>
+        <v>2.839002862650618</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.03019240425764102</v>
+        <v>0.0323830469757807</v>
       </c>
       <c r="W64">
-        <v>0.2150418550935373</v>
+        <v>0.2000418550935373</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6829,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2415392340611282</v>
+        <v>0.2590643758062456</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6840,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.207939183316232</v>
+        <v>0.1983865749192304</v>
       </c>
       <c r="C65">
-        <v>-39387.65535218469</v>
+        <v>-36339.00325375263</v>
       </c>
       <c r="D65">
-        <v>49082.26020447083</v>
+        <v>52130.91230290289</v>
       </c>
       <c r="E65">
         <v>78918.68451434516</v>
@@ -6623,37 +6873,37 @@
         <v>4688</v>
       </c>
       <c r="M65">
-        <v>19721.90117163426</v>
+        <v>18387.75743828443</v>
       </c>
       <c r="N65">
-        <v>-15033.90117163426</v>
+        <v>-13699.75743828443</v>
       </c>
       <c r="O65">
-        <v>-1879.237646454283</v>
+        <v>-1712.469679785554</v>
       </c>
       <c r="P65">
-        <v>-13154.66352517998</v>
+        <v>-11987.28775849888</v>
       </c>
       <c r="Q65">
-        <v>-12236.66352517998</v>
+        <v>-11069.28775849888</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1956645053827392</v>
+        <v>0.1953871853908431</v>
       </c>
       <c r="T65">
-        <v>2.919773952250183</v>
+        <v>2.915732669749283</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.02971315974561497</v>
+        <v>0.03186903035711752</v>
       </c>
       <c r="W65">
-        <v>0.2151481211501881</v>
+        <v>0.200148121150188</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2377052779649198</v>
+        <v>0.2549522428569402</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6922,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2096985494828573</v>
+        <v>0.1999959410858557</v>
       </c>
       <c r="C66">
-        <v>-41326.32034243147</v>
+        <v>-38294.89371555892</v>
       </c>
       <c r="D66">
-        <v>48555.38752464714</v>
+        <v>51586.8141515197</v>
       </c>
       <c r="E66">
         <v>80330.47682476827</v>
@@ -6705,37 +6955,37 @@
         <v>4688</v>
       </c>
       <c r="M66">
-        <v>20034.94722197767</v>
+        <v>18679.62660397149</v>
       </c>
       <c r="N66">
-        <v>-15346.94722197767</v>
+        <v>-13991.62660397149</v>
       </c>
       <c r="O66">
-        <v>-1918.368402747208</v>
+        <v>-1748.953325496436</v>
       </c>
       <c r="P66">
-        <v>-13428.57881923046</v>
+        <v>-12242.67327847505</v>
       </c>
       <c r="Q66">
-        <v>-12510.57881923046</v>
+        <v>-11324.67327847505</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1998274083100376</v>
+        <v>0.1995423849850332</v>
       </c>
       <c r="T66">
-        <v>3.000878784257133</v>
+        <v>2.996725243908986</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.02924889162458974</v>
+        <v>0.03137107675778756</v>
       </c>
       <c r="W66">
-        <v>0.2152510663925684</v>
+        <v>0.2002510663925684</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2339911329967179</v>
+        <v>0.2509686140623004</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +7004,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2114579156494827</v>
+        <v>0.2016053072524811</v>
       </c>
       <c r="C67">
-        <v>-43253.79405379046</v>
+        <v>-40239.54382655044</v>
       </c>
       <c r="D67">
-        <v>48039.70612371126</v>
+        <v>51053.95635095127</v>
       </c>
       <c r="E67">
         <v>81742.26913519137</v>
@@ -6787,37 +7037,37 @@
         <v>4688</v>
       </c>
       <c r="M67">
-        <v>20347.99327232107</v>
+        <v>18971.49576965854</v>
       </c>
       <c r="N67">
-        <v>-15659.99327232107</v>
+        <v>-14283.49576965854</v>
       </c>
       <c r="O67">
-        <v>-1957.499159040133</v>
+        <v>-1785.436971207318</v>
       </c>
       <c r="P67">
-        <v>-13702.49411328093</v>
+        <v>-12498.05879845122</v>
       </c>
       <c r="Q67">
-        <v>-12784.49411328093</v>
+        <v>-11580.05879845122</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2042281914046101</v>
+        <v>0.2039350245560342</v>
       </c>
       <c r="T67">
-        <v>3.086618178093052</v>
+        <v>3.082345965163529</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.02879890867651913</v>
+        <v>0.03088844480766775</v>
       </c>
       <c r="W67">
-        <v>0.2153508440890295</v>
+        <v>0.2003508440890295</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +7075,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.230391269412153</v>
+        <v>0.247107558461342</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +7086,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.213217281816108</v>
+        <v>0.2032146734191064</v>
       </c>
       <c r="C68">
-        <v>-45170.42930928971</v>
+        <v>-42173.29834188714</v>
       </c>
       <c r="D68">
-        <v>47534.86317863513</v>
+        <v>50531.99414603769</v>
       </c>
       <c r="E68">
         <v>83154.06144561448</v>
@@ -6869,37 +7119,37 @@
         <v>4688</v>
       </c>
       <c r="M68">
-        <v>20661.03932266447</v>
+        <v>19263.36493534559</v>
       </c>
       <c r="N68">
-        <v>-15973.03932266447</v>
+        <v>-14575.36493534559</v>
       </c>
       <c r="O68">
-        <v>-1996.629915333059</v>
+        <v>-1821.920616918199</v>
       </c>
       <c r="P68">
-        <v>-13976.40940733141</v>
+        <v>-12753.4443184274</v>
       </c>
       <c r="Q68">
-        <v>-13058.40940733141</v>
+        <v>-11835.4443184274</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.208887844092981</v>
+        <v>0.2085860546900352</v>
       </c>
       <c r="T68">
-        <v>3.177401065684023</v>
+        <v>3.173003199433044</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.02836256157535974</v>
+        <v>0.03042043806815763</v>
       </c>
       <c r="W68">
-        <v>0.215447598218931</v>
+        <v>0.200447598218931</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2269004926028779</v>
+        <v>0.243363504545261</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7168,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2149766479827334</v>
+        <v>0.2048240395857318</v>
       </c>
       <c r="C69">
-        <v>-47076.56425511123</v>
+        <v>-44096.48806066813</v>
       </c>
       <c r="D69">
-        <v>47040.52054323671</v>
+        <v>50020.59673767981</v>
       </c>
       <c r="E69">
         <v>84565.85375603758</v>
@@ -6951,37 +7201,37 @@
         <v>4688</v>
       </c>
       <c r="M69">
-        <v>20974.08537300787</v>
+        <v>19555.23410103265</v>
       </c>
       <c r="N69">
-        <v>-16286.08537300787</v>
+        <v>-14867.23410103265</v>
       </c>
       <c r="O69">
-        <v>-2035.760671625984</v>
+        <v>-1858.404262629081</v>
       </c>
       <c r="P69">
-        <v>-14250.32470138189</v>
+        <v>-13008.82983840357</v>
       </c>
       <c r="Q69">
-        <v>-13332.32470138189</v>
+        <v>-12090.82983840357</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2138298999745865</v>
+        <v>0.2135189654382181</v>
       </c>
       <c r="T69">
-        <v>3.273685946462328</v>
+        <v>3.269154811537076</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.02793923976080214</v>
+        <v>0.02996640167908065</v>
       </c>
       <c r="W69">
-        <v>0.2155414641658505</v>
+        <v>0.2005414641658505</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +7239,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2235139180864171</v>
+        <v>0.2397312134326453</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7250,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2167360141493587</v>
+        <v>0.2064334057523571</v>
       </c>
       <c r="C70">
-        <v>-48972.52311590154</v>
+        <v>-46009.43052505196</v>
       </c>
       <c r="D70">
-        <v>46556.3539928695</v>
+        <v>49519.44658371907</v>
       </c>
       <c r="E70">
         <v>85977.64606646069</v>
@@ -7033,37 +7283,37 @@
         <v>4688</v>
       </c>
       <c r="M70">
-        <v>21287.13142335127</v>
+        <v>19847.1032667197</v>
       </c>
       <c r="N70">
-        <v>-16599.13142335127</v>
+        <v>-15159.1032667197</v>
       </c>
       <c r="O70">
-        <v>-2074.891427918909</v>
+        <v>-1894.887908339963</v>
       </c>
       <c r="P70">
-        <v>-14524.23999543236</v>
+        <v>-13264.21535837974</v>
       </c>
       <c r="Q70">
-        <v>-13606.23999543236</v>
+        <v>-12346.21535837974</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2190808343487923</v>
+        <v>0.2187601831081624</v>
       </c>
       <c r="T70">
-        <v>3.375988632289276</v>
+        <v>3.371315899397609</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.02752836858784916</v>
+        <v>0.02952571930144711</v>
       </c>
       <c r="W70">
-        <v>0.2156325693496253</v>
+        <v>0.2006325693496253</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2202269487027934</v>
+        <v>0.2362057544115769</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7332,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.218495380315984</v>
+        <v>0.2080427719189825</v>
       </c>
       <c r="C71">
-        <v>-50858.61690391259</v>
+        <v>-47912.43067776738</v>
       </c>
       <c r="D71">
-        <v>46082.05251528155</v>
+        <v>49028.23874142676</v>
       </c>
       <c r="E71">
         <v>87389.43837688379</v>
@@ -7115,37 +7365,37 @@
         <v>4688</v>
       </c>
       <c r="M71">
-        <v>21600.17747369467</v>
+        <v>20138.97243240676</v>
       </c>
       <c r="N71">
-        <v>-16912.17747369467</v>
+        <v>-15450.97243240676</v>
       </c>
       <c r="O71">
-        <v>-2114.022184211834</v>
+        <v>-1931.371554050845</v>
       </c>
       <c r="P71">
-        <v>-14798.15528948284</v>
+        <v>-13519.60087835591</v>
       </c>
       <c r="Q71">
-        <v>-13880.15528948284</v>
+        <v>-12601.60087835591</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2246705386826243</v>
+        <v>0.224339543853587</v>
       </c>
       <c r="T71">
-        <v>3.484891491395381</v>
+        <v>3.48006802518463</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.02712940672425715</v>
+        <v>0.02909781032606382</v>
       </c>
       <c r="W71">
-        <v>0.2157210338034355</v>
+        <v>0.2007210338034355</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7403,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2170352537940572</v>
+        <v>0.2327824826085105</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7414,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2202547464826094</v>
+        <v>0.2096521380856078</v>
       </c>
       <c r="C72">
-        <v>-52735.14408523312</v>
+        <v>-49805.78148087525</v>
       </c>
       <c r="D72">
-        <v>45617.31764438411</v>
+        <v>48546.68024874198</v>
       </c>
       <c r="E72">
         <v>88801.23068730689</v>
@@ -7197,37 +7447,37 @@
         <v>4688</v>
       </c>
       <c r="M72">
-        <v>21913.22352403807</v>
+        <v>20430.84159809381</v>
       </c>
       <c r="N72">
-        <v>-17225.22352403807</v>
+        <v>-15742.84159809381</v>
       </c>
       <c r="O72">
-        <v>-2153.152940504759</v>
+        <v>-1967.855199761726</v>
       </c>
       <c r="P72">
-        <v>-15072.07058353331</v>
+        <v>-13774.98639833208</v>
       </c>
       <c r="Q72">
-        <v>-14154.07058353331</v>
+        <v>-12856.98639833208</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2306328899720451</v>
+        <v>0.2302908619820399</v>
       </c>
       <c r="T72">
-        <v>3.601054541108561</v>
+        <v>3.596070292690784</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.02674184377105348</v>
+        <v>0.02868212732140577</v>
       </c>
       <c r="W72">
-        <v>0.2158069707014227</v>
+        <v>0.2008069707014226</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2139347501684278</v>
+        <v>0.2294570185712461</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7496,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2220141126492347</v>
+        <v>0.2112615042522331</v>
       </c>
       <c r="C73">
-        <v>-54602.39120610883</v>
+        <v>-51689.76449842016</v>
       </c>
       <c r="D73">
-        <v>45161.86283393151</v>
+        <v>48074.48954162018</v>
       </c>
       <c r="E73">
         <v>90213.02299772999</v>
@@ -7279,37 +7529,37 @@
         <v>4688</v>
       </c>
       <c r="M73">
-        <v>22226.26957438147</v>
+        <v>20722.71076378087</v>
       </c>
       <c r="N73">
-        <v>-17538.26957438147</v>
+        <v>-16034.71076378087</v>
       </c>
       <c r="O73">
-        <v>-2192.283696797684</v>
+        <v>-2004.338845472608</v>
       </c>
       <c r="P73">
-        <v>-15345.98587758379</v>
+        <v>-14030.37191830826</v>
       </c>
       <c r="Q73">
-        <v>-14427.98587758379</v>
+        <v>-13112.37191830826</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2370064379021156</v>
+        <v>0.2366526158434895</v>
       </c>
       <c r="T73">
-        <v>3.725228835629545</v>
+        <v>3.720072716576671</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.02636519808413723</v>
+        <v>0.02827815369716062</v>
       </c>
       <c r="W73">
-        <v>0.21589048684172</v>
+        <v>0.20089048684172</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2109215846730979</v>
+        <v>0.226225229577285</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7578,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2237734788158601</v>
+        <v>0.2128708704188585</v>
       </c>
       <c r="C74">
-        <v>-56460.6334821136</v>
+        <v>-53564.65044540659</v>
       </c>
       <c r="D74">
-        <v>44715.41286834983</v>
+        <v>47611.39590505685</v>
       </c>
       <c r="E74">
         <v>91624.81530815309</v>
@@ -7361,37 +7611,37 @@
         <v>4688</v>
       </c>
       <c r="M74">
-        <v>22539.31562472487</v>
+        <v>21014.57992946792</v>
       </c>
       <c r="N74">
-        <v>-17851.31562472487</v>
+        <v>-16326.57992946792</v>
       </c>
       <c r="O74">
-        <v>-2231.414453090609</v>
+        <v>-2040.82249118349</v>
       </c>
       <c r="P74">
-        <v>-15619.90117163426</v>
+        <v>-14285.75743828443</v>
       </c>
       <c r="Q74">
-        <v>-14701.90117163426</v>
+        <v>-13367.75743828443</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2438352392557626</v>
+        <v>0.2434687806950427</v>
       </c>
       <c r="T74">
-        <v>3.858272722616314</v>
+        <v>3.85293245645441</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.0259990147774131</v>
+        <v>0.02788540156247783</v>
       </c>
       <c r="W74">
-        <v>0.2159716830892313</v>
+        <v>0.2009716830892313</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2079921182193049</v>
+        <v>0.2230832124998227</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7660,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2255328449824854</v>
+        <v>0.2144802365854838</v>
       </c>
       <c r="C75">
-        <v>-58310.13535271712</v>
+        <v>-55430.69970534833</v>
       </c>
       <c r="D75">
-        <v>44277.70330816942</v>
+        <v>47157.13895553821</v>
       </c>
       <c r="E75">
         <v>93036.60761857619</v>
@@ -7443,37 +7693,37 @@
         <v>4688</v>
       </c>
       <c r="M75">
-        <v>22852.36167506827</v>
+        <v>21306.44909515497</v>
       </c>
       <c r="N75">
-        <v>-18164.36167506827</v>
+        <v>-16618.44909515497</v>
       </c>
       <c r="O75">
-        <v>-2270.545209383534</v>
+        <v>-2077.306136894372</v>
       </c>
       <c r="P75">
-        <v>-15893.81646568474</v>
+        <v>-14541.1429582606</v>
       </c>
       <c r="Q75">
-        <v>-14975.81646568474</v>
+        <v>-13623.1429582606</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2511698777467167</v>
+        <v>0.2507898466467109</v>
       </c>
       <c r="T75">
-        <v>4.001171712342844</v>
+        <v>3.995633658545314</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.02564286389005128</v>
+        <v>0.02750340976025211</v>
       </c>
       <c r="W75">
-        <v>0.2160506547820163</v>
+        <v>0.2010506547820163</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2051429111204103</v>
+        <v>0.2200272780820168</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7742,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2272922111491107</v>
+        <v>0.2160896027521091</v>
       </c>
       <c r="C76">
-        <v>-60151.15100359678</v>
+        <v>-57288.16281847082</v>
       </c>
       <c r="D76">
-        <v>43848.47996771286</v>
+        <v>46711.46815283882</v>
       </c>
       <c r="E76">
         <v>94448.39992899929</v>
@@ -7525,37 +7775,37 @@
         <v>4688</v>
       </c>
       <c r="M76">
-        <v>23165.40772541167</v>
+        <v>21598.31826084203</v>
       </c>
       <c r="N76">
-        <v>-18477.40772541167</v>
+        <v>-16910.31826084203</v>
       </c>
       <c r="O76">
-        <v>-2309.675965676459</v>
+        <v>-2113.789782605254</v>
       </c>
       <c r="P76">
-        <v>-16167.73175973522</v>
+        <v>-14796.52847823677</v>
       </c>
       <c r="Q76">
-        <v>-15249.73175973522</v>
+        <v>-13878.52847823677</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2590687191985135</v>
+        <v>0.2586740715177382</v>
       </c>
       <c r="T76">
-        <v>4.155062932048338</v>
+        <v>4.149311876181672</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.02529633870234788</v>
+        <v>0.02713174206078924</v>
       </c>
       <c r="W76">
-        <v>0.216127492104726</v>
+        <v>0.2011274921047259</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7813,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2023707096187831</v>
+        <v>0.2170539364863139</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7824,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2516776356309636</v>
+        <v>0.2176989689187345</v>
       </c>
       <c r="C77">
-        <v>-66756.62932862595</v>
+        <v>-59137.2809424892</v>
       </c>
       <c r="D77">
-        <v>38654.79395310679</v>
+        <v>46274.14233924354</v>
       </c>
       <c r="E77">
         <v>95860.19223942239</v>
@@ -7607,45 +7857,45 @@
         <v>4688</v>
       </c>
       <c r="M77">
-        <v>26654.98647420706</v>
+        <v>21890.18742652908</v>
       </c>
       <c r="N77">
-        <v>-21966.98647420706</v>
+        <v>-17202.18742652908</v>
       </c>
       <c r="O77">
-        <v>-2745.873309275882</v>
+        <v>-2150.273428316135</v>
       </c>
       <c r="P77">
-        <v>-19221.11316493118</v>
+        <v>-15051.91399821295</v>
       </c>
       <c r="Q77">
-        <v>-18303.11316493118</v>
+        <v>-14133.91399821295</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2681037012273643</v>
+        <v>0.2671890343784478</v>
       </c>
       <c r="T77">
-        <v>4.331089304133673</v>
+        <v>4.315284351228939</v>
       </c>
       <c r="U77">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.02198462942635699</v>
+        <v>0.02676998549997872</v>
       </c>
       <c r="W77">
-        <v>0.2462022804321634</v>
+        <v>0.2012022804321634</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.1758770354108559</v>
+        <v>0.2141598839998298</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7906,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.253737001797589</v>
+        <v>0.2193083350853599</v>
       </c>
       <c r="C78">
-        <v>-68551.25092944343</v>
+        <v>-60978.28628774288</v>
       </c>
       <c r="D78">
-        <v>38271.96466271244</v>
+        <v>45844.92930441298</v>
       </c>
       <c r="E78">
         <v>97271.98454984551</v>
@@ -7689,45 +7939,45 @@
         <v>4688</v>
       </c>
       <c r="M78">
-        <v>27010.38629386315</v>
+        <v>22182.05659221614</v>
       </c>
       <c r="N78">
-        <v>-22322.38629386315</v>
+        <v>-17494.05659221614</v>
       </c>
       <c r="O78">
-        <v>-2790.298286732894</v>
+        <v>-2186.757074027018</v>
       </c>
       <c r="P78">
-        <v>-19532.08800713026</v>
+        <v>-15307.29951818912</v>
       </c>
       <c r="Q78">
-        <v>-18614.08800713026</v>
+        <v>-14389.29951818912</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2773663554451711</v>
+        <v>0.2764135774775498</v>
       </c>
       <c r="T78">
-        <v>4.511551358472577</v>
+        <v>4.495087865863479</v>
       </c>
       <c r="U78">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.0216953579865365</v>
+        <v>0.0264177488486632</v>
       </c>
       <c r="W78">
-        <v>0.2462751006457209</v>
+        <v>0.2012751006457209</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.173562863892292</v>
+        <v>0.2113419907893056</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7988,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2557963679642143</v>
+        <v>0.2209177012519852</v>
       </c>
       <c r="C79">
-        <v>-70338.36396527119</v>
+        <v>-62811.40252833615</v>
       </c>
       <c r="D79">
-        <v>37896.64393730777</v>
+        <v>45423.60537424281</v>
       </c>
       <c r="E79">
         <v>98683.77686026861</v>
@@ -7771,45 +8021,45 @@
         <v>4688</v>
       </c>
       <c r="M79">
-        <v>27365.78611351925</v>
+        <v>22473.92575790319</v>
       </c>
       <c r="N79">
-        <v>-22677.78611351925</v>
+        <v>-17785.92575790319</v>
       </c>
       <c r="O79">
-        <v>-2834.723264189906</v>
+        <v>-2223.240719737899</v>
       </c>
       <c r="P79">
-        <v>-19843.06284932934</v>
+        <v>-15562.68503816529</v>
       </c>
       <c r="Q79">
-        <v>-18925.06284932934</v>
+        <v>-14644.68503816529</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2874344578558308</v>
+        <v>0.2864402547591824</v>
       </c>
       <c r="T79">
-        <v>4.707705765362689</v>
+        <v>4.690526468727109</v>
       </c>
       <c r="U79">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.02141360009060746</v>
+        <v>0.02607466120127797</v>
       </c>
       <c r="W79">
-        <v>0.2463460294251601</v>
+        <v>0.20134602942516</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.1713088007248597</v>
+        <v>0.2085972896102237</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +8070,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2578557341308396</v>
+        <v>0.2225270674186105</v>
       </c>
       <c r="C80">
-        <v>-72118.18719300484</v>
+        <v>-64636.84519081477</v>
       </c>
       <c r="D80">
-        <v>37528.61301999722</v>
+        <v>45009.95502218729</v>
       </c>
       <c r="E80">
         <v>100095.5691706917</v>
@@ -7853,45 +8103,45 @@
         <v>4688</v>
       </c>
       <c r="M80">
-        <v>27721.18593317534</v>
+        <v>22765.79492359025</v>
       </c>
       <c r="N80">
-        <v>-23033.18593317534</v>
+        <v>-18077.79492359025</v>
       </c>
       <c r="O80">
-        <v>-2879.148241646918</v>
+        <v>-2259.724365448781</v>
       </c>
       <c r="P80">
-        <v>-20154.03769152842</v>
+        <v>-15818.07055814147</v>
       </c>
       <c r="Q80">
-        <v>-19236.03769152842</v>
+        <v>-14900.07055814147</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.298417842303823</v>
+        <v>0.2973784481573271</v>
       </c>
       <c r="T80">
-        <v>4.921692391060993</v>
+        <v>4.903732217305614</v>
       </c>
       <c r="U80">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.02113906675611249</v>
+        <v>0.02574037067305646</v>
       </c>
       <c r="W80">
-        <v>0.2464151395179469</v>
+        <v>0.2014151395179469</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.1691125340488999</v>
+        <v>0.2059229653844517</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8152,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.259915100297465</v>
+        <v>0.2241364335852359</v>
       </c>
       <c r="C81">
-        <v>-73890.93095349564</v>
+        <v>-66454.82202179695</v>
       </c>
       <c r="D81">
-        <v>37167.66156992953</v>
+        <v>44603.77050162821</v>
       </c>
       <c r="E81">
         <v>101507.3614811148</v>
@@ -7935,45 +8185,45 @@
         <v>4688</v>
       </c>
       <c r="M81">
-        <v>28076.58575283143</v>
+        <v>23057.6640892773</v>
       </c>
       <c r="N81">
-        <v>-23388.58575283143</v>
+        <v>-18369.6640892773</v>
       </c>
       <c r="O81">
-        <v>-2923.573219103929</v>
+        <v>-2296.208011159663</v>
       </c>
       <c r="P81">
-        <v>-20465.01253372751</v>
+        <v>-16073.45607811764</v>
       </c>
       <c r="Q81">
-        <v>-19547.01253372751</v>
+        <v>-15155.45607811764</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3104472633659099</v>
+        <v>0.309358374260057</v>
       </c>
       <c r="T81">
-        <v>5.156058695397232</v>
+        <v>5.137243275272548</v>
       </c>
       <c r="U81">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.0208714836326174</v>
+        <v>0.02541454319618233</v>
       </c>
       <c r="W81">
-        <v>0.2464824999881315</v>
+        <v>0.2014824999881315</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.1669718690609392</v>
+        <v>0.2033163455694585</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8234,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2619744664640903</v>
+        <v>0.2257457997518612</v>
       </c>
       <c r="C82">
-        <v>-75656.79757242367</v>
+        <v>-68265.53333587688</v>
       </c>
       <c r="D82">
-        <v>36813.58726142461</v>
+        <v>44204.85149797139</v>
       </c>
       <c r="E82">
         <v>102919.1537915379</v>
@@ -8017,45 +8267,45 @@
         <v>4688</v>
       </c>
       <c r="M82">
-        <v>28431.98557248753</v>
+        <v>23349.53325496436</v>
       </c>
       <c r="N82">
-        <v>-23743.98557248753</v>
+        <v>-18661.53325496436</v>
       </c>
       <c r="O82">
-        <v>-2967.998196560942</v>
+        <v>-2332.691656870545</v>
       </c>
       <c r="P82">
-        <v>-20775.98737592659</v>
+        <v>-16328.84159809381</v>
       </c>
       <c r="Q82">
-        <v>-19857.98737592659</v>
+        <v>-15410.84159809381</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3236796265342054</v>
+        <v>0.3225362929730598</v>
       </c>
       <c r="T82">
-        <v>5.413861630167093</v>
+        <v>5.394105439036175</v>
       </c>
       <c r="U82">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.02061059008720967</v>
+        <v>0.02509686140623005</v>
       </c>
       <c r="W82">
-        <v>0.2465481764465616</v>
+        <v>0.2015481764465616</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.1648847206976773</v>
+        <v>0.2007748912498404</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8316,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2640338326307157</v>
+        <v>0.2558693531517254</v>
       </c>
       <c r="C83">
-        <v>-77415.98173847428</v>
+        <v>-76016.21889585667</v>
       </c>
       <c r="D83">
-        <v>36466.1954057971</v>
+        <v>37865.95824841471</v>
       </c>
       <c r="E83">
         <v>104330.946101961</v>
@@ -8099,37 +8349,37 @@
         <v>4688</v>
       </c>
       <c r="M83">
-        <v>28787.38539214363</v>
+        <v>27643.83362070091</v>
       </c>
       <c r="N83">
-        <v>-24099.38539214363</v>
+        <v>-22955.83362070091</v>
       </c>
       <c r="O83">
-        <v>-3012.423174017953</v>
+        <v>-2869.479202587614</v>
       </c>
       <c r="P83">
-        <v>-21086.96221812567</v>
+        <v>-20086.3544181133</v>
       </c>
       <c r="Q83">
-        <v>-20168.96221812567</v>
+        <v>-19168.3544181133</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3383048700360057</v>
+        <v>0.3379655043571095</v>
       </c>
       <c r="T83">
-        <v>5.698801715965362</v>
+        <v>5.69484948728735</v>
       </c>
       <c r="U83">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.02035613835773795</v>
+        <v>0.02119821758589871</v>
       </c>
       <c r="W83">
-        <v>0.2466122312640427</v>
+        <v>0.2366122312640427</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1628491068619036</v>
+        <v>0.1695857406871897</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8398,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.266093198797341</v>
+        <v>0.2578287193183507</v>
       </c>
       <c r="C84">
-        <v>-79168.6708603025</v>
+        <v>-77777.93209292811</v>
       </c>
       <c r="D84">
-        <v>36125.29859439198</v>
+        <v>37516.03736176637</v>
       </c>
       <c r="E84">
         <v>105742.7384123841</v>
@@ -8181,37 +8431,37 @@
         <v>4688</v>
       </c>
       <c r="M84">
-        <v>29142.78521179972</v>
+        <v>27985.11551725277</v>
       </c>
       <c r="N84">
-        <v>-24454.78521179972</v>
+        <v>-23297.11551725277</v>
       </c>
       <c r="O84">
-        <v>-3056.848151474965</v>
+        <v>-2912.139439656597</v>
       </c>
       <c r="P84">
-        <v>-21397.93706032476</v>
+        <v>-20384.97607759618</v>
       </c>
       <c r="Q84">
-        <v>-20479.93706032476</v>
+        <v>-19466.97607759618</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3545551405935616</v>
+        <v>0.3541969212658378</v>
       </c>
       <c r="T84">
-        <v>6.015401811296771</v>
+        <v>6.011230014358869</v>
       </c>
       <c r="U84">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.02010789276800944</v>
+        <v>0.02093970273729019</v>
       </c>
       <c r="W84">
-        <v>0.2466747237689024</v>
+        <v>0.2366747237689024</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1608631421440755</v>
+        <v>0.1675176218983215</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8480,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2681525649639663</v>
+        <v>0.2597880854849761</v>
       </c>
       <c r="C85">
-        <v>-80915.04540366086</v>
+        <v>-79533.23724027343</v>
       </c>
       <c r="D85">
-        <v>35790.71636145672</v>
+        <v>37172.52452484415</v>
       </c>
       <c r="E85">
         <v>107154.5307228072</v>
@@ -8263,37 +8513,37 @@
         <v>4688</v>
       </c>
       <c r="M85">
-        <v>29498.18503145581</v>
+        <v>28326.39741380464</v>
       </c>
       <c r="N85">
-        <v>-24810.18503145581</v>
+        <v>-23638.39741380464</v>
       </c>
       <c r="O85">
-        <v>-3101.273128931977</v>
+        <v>-2954.79967672558</v>
       </c>
       <c r="P85">
-        <v>-21708.91190252384</v>
+        <v>-20683.59773707906</v>
       </c>
       <c r="Q85">
-        <v>-20790.91190252384</v>
+        <v>-19765.59773707906</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3727172076873005</v>
+        <v>0.3723379166344165</v>
       </c>
       <c r="T85">
-        <v>6.369248976667169</v>
+        <v>6.364831779909391</v>
       </c>
       <c r="U85">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.01986562899972017</v>
+        <v>0.02068741716214211</v>
       </c>
       <c r="W85">
-        <v>0.2467357104302714</v>
+        <v>0.2367357104302714</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1589250319977613</v>
+        <v>0.165499337297137</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8562,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2702119311305917</v>
+        <v>0.2617474516516014</v>
       </c>
       <c r="C86">
-        <v>-82655.27920996494</v>
+        <v>-81282.30876526923</v>
       </c>
       <c r="D86">
-        <v>35462.27486557574</v>
+        <v>36835.24531027144</v>
       </c>
       <c r="E86">
         <v>108566.3230332303</v>
@@ -8345,37 +8595,37 @@
         <v>4688</v>
       </c>
       <c r="M86">
-        <v>29853.5848511119</v>
+        <v>28667.6793103565</v>
       </c>
       <c r="N86">
-        <v>-25165.5848511119</v>
+        <v>-23979.6793103565</v>
       </c>
       <c r="O86">
-        <v>-3145.698106388988</v>
+        <v>-2997.459913794562</v>
       </c>
       <c r="P86">
-        <v>-22019.88674472292</v>
+        <v>-20982.21939656193</v>
       </c>
       <c r="Q86">
-        <v>-21101.88674472292</v>
+        <v>-20064.21939656193</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3931495331677566</v>
+        <v>0.3927465364240673</v>
       </c>
       <c r="T86">
-        <v>6.767327037708864</v>
+        <v>6.762633766153725</v>
       </c>
       <c r="U86">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.01962913341639017</v>
+        <v>0.02044113838640233</v>
       </c>
       <c r="W86">
-        <v>0.2467952450282745</v>
+        <v>0.2367952450282745</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1570330673311213</v>
+        <v>0.1635291070912186</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8644,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2722712972972171</v>
+        <v>0.2637068178182267</v>
       </c>
       <c r="C87">
-        <v>-84389.53979747789</v>
+        <v>-83025.31482165461</v>
       </c>
       <c r="D87">
-        <v>35139.8065884859</v>
+        <v>36504.03156430918</v>
       </c>
       <c r="E87">
         <v>109978.1153436534</v>
@@ -8427,37 +8677,37 @@
         <v>4688</v>
       </c>
       <c r="M87">
-        <v>30208.984670768</v>
+        <v>29008.96120690836</v>
       </c>
       <c r="N87">
-        <v>-25520.984670768</v>
+        <v>-24320.96120690836</v>
       </c>
       <c r="O87">
-        <v>-3190.123083846</v>
+        <v>-3040.120150863545</v>
       </c>
       <c r="P87">
-        <v>-22330.861586922</v>
+        <v>-21280.84105604482</v>
       </c>
       <c r="Q87">
-        <v>-21412.861586922</v>
+        <v>-20362.84105604482</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4163061687122738</v>
+        <v>0.4158763055190052</v>
       </c>
       <c r="T87">
-        <v>7.218482173556122</v>
+        <v>7.21347601723064</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.01939820243502087</v>
+        <v>0.02020065440538583</v>
       </c>
       <c r="W87">
-        <v>0.246853378812207</v>
+        <v>0.236853378812207</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.155185619480167</v>
+        <v>0.1616052352430867</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8726,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2743306634638424</v>
+        <v>0.2656661839848521</v>
       </c>
       <c r="C88">
-        <v>-86117.98864621072</v>
+        <v>-84762.41756907268</v>
       </c>
       <c r="D88">
-        <v>34823.15005017617</v>
+        <v>36178.7211273142</v>
       </c>
       <c r="E88">
         <v>111389.9076540765</v>
@@ -8509,37 +8759,37 @@
         <v>4688</v>
       </c>
       <c r="M88">
-        <v>30564.38449042409</v>
+        <v>29350.24310346022</v>
       </c>
       <c r="N88">
-        <v>-25876.38449042409</v>
+        <v>-24662.24310346022</v>
       </c>
       <c r="O88">
-        <v>-3234.548061303012</v>
+        <v>-3082.780387932528</v>
       </c>
       <c r="P88">
-        <v>-22641.83642912108</v>
+        <v>-21579.46271552769</v>
       </c>
       <c r="Q88">
-        <v>-21723.83642912108</v>
+        <v>-20661.46271552769</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4427708950488647</v>
+        <v>0.4423103273417913</v>
       </c>
       <c r="T88">
-        <v>7.734088043095845</v>
+        <v>7.728724304175686</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.0191726419415904</v>
+        <v>0.01996576307509065</v>
       </c>
       <c r="W88">
-        <v>0.2469101606476759</v>
+        <v>0.2369101606476759</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8797,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1533811355327231</v>
+        <v>0.1597261046007251</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8808,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2763900296304677</v>
+        <v>0.2676255501514774</v>
       </c>
       <c r="C89">
-        <v>-87840.78146755605</v>
+        <v>-86493.77343779747</v>
       </c>
       <c r="D89">
-        <v>34512.14953925394</v>
+        <v>35859.15756901252</v>
       </c>
       <c r="E89">
         <v>112801.6999644996</v>
@@ -8591,37 +8841,37 @@
         <v>4688</v>
       </c>
       <c r="M89">
-        <v>30919.78431008019</v>
+        <v>29691.52500001209</v>
       </c>
       <c r="N89">
-        <v>-26231.78431008019</v>
+        <v>-25003.52500001209</v>
       </c>
       <c r="O89">
-        <v>-3278.973038760023</v>
+        <v>-3125.440625001511</v>
       </c>
       <c r="P89">
-        <v>-22952.81127132016</v>
+        <v>-21878.08437501058</v>
       </c>
       <c r="Q89">
-        <v>-22034.81127132016</v>
+        <v>-20960.08437501058</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4733071177449313</v>
+        <v>0.4728111217526983</v>
       </c>
       <c r="T89">
-        <v>8.329017892564757</v>
+        <v>8.323241558343046</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.01895226674685947</v>
+        <v>0.0197362715454919</v>
       </c>
       <c r="W89">
-        <v>0.2469656371535938</v>
+        <v>0.2369656371535939</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1516181339748758</v>
+        <v>0.1578901723639352</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8890,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.278449395797093</v>
+        <v>0.2695849163181028</v>
       </c>
       <c r="C90">
-        <v>-89558.06845960146</v>
+        <v>-88219.53337955338</v>
       </c>
       <c r="D90">
-        <v>34206.65485763162</v>
+        <v>35545.1899376797</v>
       </c>
       <c r="E90">
         <v>114213.4922749227</v>
@@ -8673,37 +8923,37 @@
         <v>4688</v>
       </c>
       <c r="M90">
-        <v>31275.18412973628</v>
+        <v>30032.80689656395</v>
       </c>
       <c r="N90">
-        <v>-26587.18412973628</v>
+        <v>-25344.80689656395</v>
       </c>
       <c r="O90">
-        <v>-3323.398016217035</v>
+        <v>-3168.100862070494</v>
       </c>
       <c r="P90">
-        <v>-23263.78611351925</v>
+        <v>-22176.70603449346</v>
       </c>
       <c r="Q90">
-        <v>-22345.78611351925</v>
+        <v>-21258.70603449346</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5089327108903422</v>
+        <v>0.5083953818987565</v>
       </c>
       <c r="T90">
-        <v>9.023102716945154</v>
+        <v>9.016845021538302</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.01873690007928152</v>
+        <v>0.01951199573247495</v>
       </c>
       <c r="W90">
-        <v>0.2470198528298318</v>
+        <v>0.2370198528298318</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1498952006342522</v>
+        <v>0.1560959658597996</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8972,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2805087619637184</v>
+        <v>0.2715442824847281</v>
       </c>
       <c r="C91">
-        <v>-91269.9945490018</v>
+        <v>-89939.84310527304</v>
       </c>
       <c r="D91">
-        <v>33906.5210786544</v>
+        <v>35236.67252238316</v>
       </c>
       <c r="E91">
         <v>115625.2845853459</v>
@@ -8755,37 +9005,37 @@
         <v>4688</v>
       </c>
       <c r="M91">
-        <v>31630.58394939238</v>
+        <v>30374.08879311581</v>
       </c>
       <c r="N91">
-        <v>-26942.58394939238</v>
+        <v>-25686.08879311581</v>
       </c>
       <c r="O91">
-        <v>-3367.822993674047</v>
+        <v>-3210.761099139477</v>
       </c>
       <c r="P91">
-        <v>-23574.76095571833</v>
+        <v>-22475.32769397634</v>
       </c>
       <c r="Q91">
-        <v>-22656.76095571833</v>
+        <v>-21557.32769397634</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.551035684607646</v>
+        <v>0.5504495075259161</v>
       </c>
       <c r="T91">
-        <v>9.843384782121985</v>
+        <v>9.83655820531451</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.01852637311209859</v>
+        <v>0.01929275982536849</v>
       </c>
       <c r="W91">
-        <v>0.2470728501762667</v>
+        <v>0.2370728501762667</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +9043,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1482109848967886</v>
+        <v>0.1543420786029479</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +9054,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2825681281303438</v>
+        <v>0.2735036486513535</v>
       </c>
       <c r="C92">
-        <v>-92976.69962022906</v>
+        <v>-91654.84331057941</v>
       </c>
       <c r="D92">
-        <v>33611.60831785024</v>
+        <v>34933.4646274999</v>
       </c>
       <c r="E92">
         <v>117037.076895769</v>
@@ -8837,37 +9087,37 @@
         <v>4688</v>
       </c>
       <c r="M92">
-        <v>31985.98376904847</v>
+        <v>30715.37068966768</v>
       </c>
       <c r="N92">
-        <v>-27297.98376904847</v>
+        <v>-26027.37068966768</v>
       </c>
       <c r="O92">
-        <v>-3412.247971131059</v>
+        <v>-3253.42133620846</v>
       </c>
       <c r="P92">
-        <v>-23885.73579791741</v>
+        <v>-22773.94935345922</v>
       </c>
       <c r="Q92">
-        <v>-22967.73579791741</v>
+        <v>-21855.94935345922</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6015592530684107</v>
+        <v>0.6009144582785079</v>
       </c>
       <c r="T92">
-        <v>10.82772326033419</v>
+        <v>10.82021402584596</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.01832052452196416</v>
+        <v>0.01907839582730884</v>
       </c>
       <c r="W92">
-        <v>0.2471246698038919</v>
+        <v>0.2371246698038919</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1465641961757133</v>
+        <v>0.1526271666184708</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9136,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.284627494296969</v>
+        <v>0.2754630148179788</v>
       </c>
       <c r="C93">
-        <v>-94678.31873296149</v>
+        <v>-93364.66988972609</v>
       </c>
       <c r="D93">
-        <v>33321.78151554091</v>
+        <v>34635.43035877632</v>
       </c>
       <c r="E93">
         <v>118448.8692061921</v>
@@ -8919,37 +9169,37 @@
         <v>4688</v>
       </c>
       <c r="M93">
-        <v>32341.38358870456</v>
+        <v>31056.65258621954</v>
       </c>
       <c r="N93">
-        <v>-27653.38358870456</v>
+        <v>-26368.65258621954</v>
       </c>
       <c r="O93">
-        <v>-3456.672948588071</v>
+        <v>-3296.081573277443</v>
       </c>
       <c r="P93">
-        <v>-24196.71064011649</v>
+        <v>-23072.5710129421</v>
       </c>
       <c r="Q93">
-        <v>-23278.71064011649</v>
+        <v>-22154.5710129421</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.663310281187123</v>
+        <v>0.6625938425316755</v>
       </c>
       <c r="T93">
-        <v>12.03080362259354</v>
+        <v>12.02246002871774</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.01811920007666785</v>
+        <v>0.01886874312590984</v>
       </c>
       <c r="W93">
-        <v>0.2471753505386022</v>
+        <v>0.2371753505386022</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1449536006133427</v>
+        <v>0.1509499450072788</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9218,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2866868604635944</v>
+        <v>0.2774223809846041</v>
       </c>
       <c r="C94">
-        <v>-96374.98232832193</v>
+        <v>-95069.45413867867</v>
       </c>
       <c r="D94">
-        <v>33036.91023060357</v>
+        <v>34342.43842024683</v>
       </c>
       <c r="E94">
         <v>119860.6615166152</v>
@@ -9001,37 +9251,37 @@
         <v>4688</v>
       </c>
       <c r="M94">
-        <v>32696.78340836066</v>
+        <v>31397.9344827714</v>
       </c>
       <c r="N94">
-        <v>-28008.78340836066</v>
+        <v>-26709.9344827714</v>
       </c>
       <c r="O94">
-        <v>-3501.097926045083</v>
+        <v>-3338.741810346426</v>
       </c>
       <c r="P94">
-        <v>-24507.68548231558</v>
+        <v>-23371.19267242498</v>
       </c>
       <c r="Q94">
-        <v>-23589.68548231558</v>
+        <v>-22453.19267242498</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7404990663355138</v>
+        <v>0.7396930728481351</v>
       </c>
       <c r="T94">
-        <v>13.53465407541774</v>
+        <v>13.52526753230746</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.01792225224974754</v>
+        <v>0.01866364809193256</v>
       </c>
       <c r="W94">
-        <v>0.2472249295182102</v>
+        <v>0.2372249295182102</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1433780179979803</v>
+        <v>0.1493091847354605</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9300,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2887462266302198</v>
+        <v>0.2793817471512295</v>
       </c>
       <c r="C95">
-        <v>-98066.81642462674</v>
+        <v>-96769.32294797513</v>
       </c>
       <c r="D95">
-        <v>32756.86844472188</v>
+        <v>34054.36192137349</v>
       </c>
       <c r="E95">
         <v>121272.4538270383</v>
@@ -9083,37 +9333,37 @@
         <v>4688</v>
       </c>
       <c r="M95">
-        <v>33052.18322801676</v>
+        <v>31739.21637932327</v>
       </c>
       <c r="N95">
-        <v>-28364.18322801676</v>
+        <v>-27051.21637932327</v>
       </c>
       <c r="O95">
-        <v>-3545.522903502095</v>
+        <v>-3381.402047415409</v>
       </c>
       <c r="P95">
-        <v>-24818.66032451466</v>
+        <v>-23669.81433190786</v>
       </c>
       <c r="Q95">
-        <v>-23900.66032451466</v>
+        <v>-22751.81433190786</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8397417900977301</v>
+        <v>0.8388206546835831</v>
       </c>
       <c r="T95">
-        <v>15.4681760861917</v>
+        <v>15.45744860835138</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.01772953985996531</v>
+        <v>0.01846296370384726</v>
       </c>
       <c r="W95">
-        <v>0.2472734422832029</v>
+        <v>0.2372734422832029</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1418363188797225</v>
+        <v>0.1477037096307781</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9382,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2908055927968451</v>
+        <v>0.2813411133178548</v>
       </c>
       <c r="C96">
-        <v>-99753.9428032627</v>
+        <v>-98464.3989859601</v>
       </c>
       <c r="D96">
-        <v>32481.53437650901</v>
+        <v>33771.07819381163</v>
       </c>
       <c r="E96">
         <v>122684.2461374614</v>
@@ -9165,37 +9415,37 @@
         <v>4688</v>
       </c>
       <c r="M96">
-        <v>33407.58304767285</v>
+        <v>32080.49827587513</v>
       </c>
       <c r="N96">
-        <v>-28719.58304767285</v>
+        <v>-27392.49827587513</v>
       </c>
       <c r="O96">
-        <v>-3589.947880959106</v>
+        <v>-3424.062284484392</v>
       </c>
       <c r="P96">
-        <v>-25129.63516671375</v>
+        <v>-23968.43599139074</v>
       </c>
       <c r="Q96">
-        <v>-24211.63516671375</v>
+        <v>-23050.43599139074</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9720654217806853</v>
+        <v>0.9709907637975138</v>
       </c>
       <c r="T96">
-        <v>18.04620543389033</v>
+        <v>18.03369004307662</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.01754092773379547</v>
+        <v>0.01826654919635953</v>
       </c>
       <c r="W96">
-        <v>0.2473209228617064</v>
+        <v>0.2373209228617064</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1403274218703637</v>
+        <v>0.1461323935708762</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9464,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2928649589634705</v>
+        <v>0.2833004794844802</v>
       </c>
       <c r="C97">
-        <v>-101436.479185268</v>
+        <v>-100154.8008729493</v>
       </c>
       <c r="D97">
-        <v>32210.79030492682</v>
+        <v>33492.46861724553</v>
       </c>
       <c r="E97">
         <v>124096.0384478845</v>
@@ -9247,37 +9497,37 @@
         <v>4688</v>
       </c>
       <c r="M97">
-        <v>33762.98286732894</v>
+        <v>32421.780172427</v>
       </c>
       <c r="N97">
-        <v>-29074.98286732894</v>
+        <v>-27733.780172427</v>
       </c>
       <c r="O97">
-        <v>-3634.372858416118</v>
+        <v>-3466.722521553374</v>
       </c>
       <c r="P97">
-        <v>-25440.61000891283</v>
+        <v>-24267.05765087362</v>
       </c>
       <c r="Q97">
-        <v>-24522.61000891283</v>
+        <v>-23349.05765087362</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.157318506136823</v>
+        <v>1.156028916557017</v>
       </c>
       <c r="T97">
-        <v>21.6554465206684</v>
+        <v>21.64042805169195</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.0173562863892292</v>
+        <v>0.01807426973113469</v>
       </c>
       <c r="W97">
-        <v>0.2473674038490836</v>
+        <v>0.2373674038490836</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1388502911138336</v>
+        <v>0.1445941578490775</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9546,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2949243251300958</v>
+        <v>0.2852598456511055</v>
       </c>
       <c r="C98">
-        <v>-103114.5393991549</v>
+        <v>-101840.6433468433</v>
       </c>
       <c r="D98">
-        <v>31944.522401463</v>
+        <v>33218.41845377467</v>
       </c>
       <c r="E98">
         <v>125507.8307583076</v>
@@ -9329,37 +9579,37 @@
         <v>4688</v>
       </c>
       <c r="M98">
-        <v>34118.38268698504</v>
+        <v>32763.06206897886</v>
       </c>
       <c r="N98">
-        <v>-29430.38268698504</v>
+        <v>-28075.06206897886</v>
       </c>
       <c r="O98">
-        <v>-3678.79783587313</v>
+        <v>-3509.382758622357</v>
       </c>
       <c r="P98">
-        <v>-25751.58485111191</v>
+        <v>-24565.6793103565</v>
       </c>
       <c r="Q98">
-        <v>-24833.58485111191</v>
+        <v>-23647.6793103565</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.435198132671026</v>
+        <v>1.433586145696268</v>
       </c>
       <c r="T98">
-        <v>27.06930815083544</v>
+        <v>27.05053506461488</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.01717549173934139</v>
+        <v>0.01788599608810204</v>
       </c>
       <c r="W98">
-        <v>0.247412916482557</v>
+        <v>0.237412916482557</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9617,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1374039339147312</v>
+        <v>0.1430879687048163</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9628,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2969836912967211</v>
+        <v>0.2872192118177308</v>
       </c>
       <c r="C99">
-        <v>-104788.233540477</v>
+        <v>-103522.0374206764</v>
       </c>
       <c r="D99">
-        <v>31682.620570564</v>
+        <v>32948.81669036461</v>
       </c>
       <c r="E99">
         <v>126919.6230687307</v>
@@ -9411,37 +9661,37 @@
         <v>4688</v>
       </c>
       <c r="M99">
-        <v>34473.78250664113</v>
+        <v>33104.34396553072</v>
       </c>
       <c r="N99">
-        <v>-29785.78250664113</v>
+        <v>-28416.34396553072</v>
       </c>
       <c r="O99">
-        <v>-3723.222813330141</v>
+        <v>-3552.04299569134</v>
       </c>
       <c r="P99">
-        <v>-26062.55969331099</v>
+        <v>-24864.30096983938</v>
       </c>
       <c r="Q99">
-        <v>-25144.55969331099</v>
+        <v>-23946.30096983938</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.898330843561367</v>
+        <v>1.896181527595024</v>
       </c>
       <c r="T99">
-        <v>36.09241086778059</v>
+        <v>36.06738008615317</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.01699842481419355</v>
+        <v>0.01770160437585356</v>
       </c>
       <c r="W99">
-        <v>0.2474574907112166</v>
+        <v>0.2374574907112166</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1359873985135484</v>
+        <v>0.1416128350068284</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9710,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2990430574633465</v>
+        <v>0.2891785779843562</v>
       </c>
       <c r="C100">
-        <v>-106457.6681236108</v>
+        <v>-105199.0905325559</v>
       </c>
       <c r="D100">
-        <v>31424.97829785337</v>
+        <v>32683.55588890824</v>
       </c>
       <c r="E100">
         <v>128331.4153791538</v>
@@ -9493,37 +9743,37 @@
         <v>4688</v>
       </c>
       <c r="M100">
-        <v>34829.18232629722</v>
+        <v>33445.62586208258</v>
       </c>
       <c r="N100">
-        <v>-30141.18232629722</v>
+        <v>-28757.62586208258</v>
       </c>
       <c r="O100">
-        <v>-3767.647790787153</v>
+        <v>-3594.703232760323</v>
       </c>
       <c r="P100">
-        <v>-26373.53453551007</v>
+        <v>-25162.92262932226</v>
       </c>
       <c r="Q100">
-        <v>-25455.53453551007</v>
+        <v>-24244.92262932226</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.824596265342051</v>
+        <v>2.821372291392537</v>
       </c>
       <c r="T100">
-        <v>54.13861630167087</v>
+        <v>54.10107012922977</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.016824971499763</v>
+        <v>0.01752097575977342</v>
       </c>
       <c r="W100">
-        <v>0.2475011552617402</v>
+        <v>0.2375011552617402</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9781,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.134599771998104</v>
+        <v>0.1401678060781874</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9792,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3011024236299719</v>
+        <v>0.2911379441509815</v>
       </c>
       <c r="C101">
-        <v>-108122.9462261912</v>
+        <v>-106871.9066884153</v>
       </c>
       <c r="D101">
-        <v>31171.49250569601</v>
+        <v>32422.53204347191</v>
       </c>
       <c r="E101">
         <v>129743.2076895769</v>
@@ -9575,37 +9825,37 @@
         <v>4688</v>
       </c>
       <c r="M101">
-        <v>35184.58214595332</v>
+        <v>33786.90775863444</v>
       </c>
       <c r="N101">
-        <v>-30496.58214595332</v>
+        <v>-29098.90775863444</v>
       </c>
       <c r="O101">
-        <v>-3812.072768244165</v>
+        <v>-3637.363469829305</v>
       </c>
       <c r="P101">
-        <v>-26684.50937770915</v>
+        <v>-25461.54428880514</v>
       </c>
       <c r="Q101">
-        <v>-25766.50937770915</v>
+        <v>-24543.54428880514</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.603392530684102</v>
+        <v>5.596944582785073</v>
       </c>
       <c r="T101">
-        <v>108.2772326033418</v>
+        <v>108.2021402584595</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
-        <v>0.01665502229269469</v>
+        <v>0.0173439962066444</v>
       </c>
       <c r="W101">
-        <v>0.2475439377001321</v>
+        <v>0.237543937700132</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9863,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1332401783415575</v>
+        <v>0.1387519696531552</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_electrical_equipment.xlsx
@@ -1534,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1671,22 +1671,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1022812604878216</v>
+        <v>0.102244729308009</v>
       </c>
       <c r="C2">
-        <v>141306.9206138974</v>
+        <v>139986.2763936633</v>
       </c>
       <c r="D2">
-        <v>140833.9206138974</v>
+        <v>140925.0687040864</v>
       </c>
       <c r="E2">
-        <v>-10024.23104231034</v>
+        <v>-8612.438731887241</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1411.792310423103</v>
       </c>
       <c r="G2">
         <v>473</v>
@@ -1707,28 +1707,28 @@
         <v>4688</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>79.39442296837738</v>
       </c>
       <c r="N2">
-        <v>4688</v>
+        <v>4608.605577031622</v>
       </c>
       <c r="O2">
-        <v>586</v>
+        <v>576.0756971289528</v>
       </c>
       <c r="P2">
-        <v>4102</v>
+        <v>4032.52987990267</v>
       </c>
       <c r="Q2">
-        <v>5020</v>
+        <v>4950.52987990267</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1022812604878216</v>
+        <v>0.1027804635476887</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.110655292225481</v>
       </c>
       <c r="U2">
         <v>0.05623661666253409</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>59.04696859963602</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.102244729308009</v>
+        <v>0.1022081981281964</v>
       </c>
       <c r="C3">
-        <v>139986.2763936633</v>
+        <v>138665.7502324129</v>
       </c>
       <c r="D3">
-        <v>140925.0687040864</v>
+        <v>141016.3348532591</v>
       </c>
       <c r="E3">
-        <v>-8612.438731887241</v>
+        <v>-7200.646421464138</v>
       </c>
       <c r="F3">
-        <v>1411.792310423103</v>
+        <v>2823.584620846207</v>
       </c>
       <c r="G3">
         <v>473</v>
@@ -1789,28 +1789,28 @@
         <v>4688</v>
       </c>
       <c r="M3">
-        <v>79.39442296837738</v>
+        <v>158.7888459367548</v>
       </c>
       <c r="N3">
-        <v>4608.605577031622</v>
+        <v>4529.211154063245</v>
       </c>
       <c r="O3">
-        <v>576.0756971289528</v>
+        <v>566.1513942579056</v>
       </c>
       <c r="P3">
-        <v>4032.52987990267</v>
+        <v>3963.059759805339</v>
       </c>
       <c r="Q3">
-        <v>4950.52987990267</v>
+        <v>4881.059759805339</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1027804635476887</v>
+        <v>0.1032898544251041</v>
       </c>
       <c r="T3">
-        <v>1.110655292225481</v>
+        <v>1.120584268555049</v>
       </c>
       <c r="U3">
         <v>0.05623661666253409</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>59.04696859963602</v>
+        <v>29.52348429981801</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1835,22 +1835,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1022081981281964</v>
+        <v>0.1021716669483838</v>
       </c>
       <c r="C4">
-        <v>138665.7502324129</v>
+        <v>137345.3423596676</v>
       </c>
       <c r="D4">
-        <v>141016.3348532591</v>
+        <v>141107.7192909369</v>
       </c>
       <c r="E4">
-        <v>-7200.646421464138</v>
+        <v>-5788.854111041034</v>
       </c>
       <c r="F4">
-        <v>2823.584620846207</v>
+        <v>4235.37693126931</v>
       </c>
       <c r="G4">
         <v>473</v>
@@ -1871,28 +1871,28 @@
         <v>4688</v>
       </c>
       <c r="M4">
-        <v>158.7888459367548</v>
+        <v>238.1832689051322</v>
       </c>
       <c r="N4">
-        <v>4529.211154063245</v>
+        <v>4449.816731094867</v>
       </c>
       <c r="O4">
-        <v>566.1513942579056</v>
+        <v>556.2270913868584</v>
       </c>
       <c r="P4">
-        <v>3963.059759805339</v>
+        <v>3893.589639708009</v>
       </c>
       <c r="Q4">
-        <v>4881.059759805339</v>
+        <v>4811.589639708009</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1032898544251041</v>
+        <v>0.1038097482072085</v>
       </c>
       <c r="T4">
-        <v>1.120584268555049</v>
+        <v>1.130717966046051</v>
       </c>
       <c r="U4">
         <v>0.05623661666253409</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>29.52348429981801</v>
+        <v>19.68232286654534</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1021716669483838</v>
+        <v>0.1021351357685712</v>
       </c>
       <c r="C5">
-        <v>137345.3423596676</v>
+        <v>136025.0530055441</v>
       </c>
       <c r="D5">
-        <v>141107.7192909369</v>
+        <v>141199.2222472365</v>
       </c>
       <c r="E5">
-        <v>-5788.854111041034</v>
+        <v>-4377.061800617931</v>
       </c>
       <c r="F5">
-        <v>4235.37693126931</v>
+        <v>5647.169241692413</v>
       </c>
       <c r="G5">
         <v>473</v>
@@ -1953,28 +1953,28 @@
         <v>4688</v>
       </c>
       <c r="M5">
-        <v>238.1832689051322</v>
+        <v>317.5776918735095</v>
       </c>
       <c r="N5">
-        <v>4449.816731094867</v>
+        <v>4370.422308126491</v>
       </c>
       <c r="O5">
-        <v>556.2270913868584</v>
+        <v>546.3027885158114</v>
       </c>
       <c r="P5">
-        <v>3893.589639708009</v>
+        <v>3824.11951961068</v>
       </c>
       <c r="Q5">
-        <v>4811.589639708009</v>
+        <v>4742.11951961068</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1038097482072085</v>
+        <v>0.1043404731097734</v>
       </c>
       <c r="T5">
-        <v>1.130717966046051</v>
+        <v>1.141062782234783</v>
       </c>
       <c r="U5">
         <v>0.05623661666253409</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>19.68232286654534</v>
+        <v>14.76174214990901</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1999,22 +1999,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1021351357685712</v>
+        <v>0.1020986045887586</v>
       </c>
       <c r="C6">
-        <v>136025.0530055441</v>
+        <v>134704.8824007564</v>
       </c>
       <c r="D6">
-        <v>141199.2222472365</v>
+        <v>141290.8439528719</v>
       </c>
       <c r="E6">
-        <v>-4377.061800617931</v>
+        <v>-2965.269490194827</v>
       </c>
       <c r="F6">
-        <v>5647.169241692413</v>
+        <v>7058.961552115517</v>
       </c>
       <c r="G6">
         <v>473</v>
@@ -2035,28 +2035,28 @@
         <v>4688</v>
       </c>
       <c r="M6">
-        <v>317.5776918735095</v>
+        <v>396.972114841887</v>
       </c>
       <c r="N6">
-        <v>4370.422308126491</v>
+        <v>4291.027885158113</v>
       </c>
       <c r="O6">
-        <v>546.3027885158114</v>
+        <v>536.3784856447642</v>
       </c>
       <c r="P6">
-        <v>3824.11951961068</v>
+        <v>3754.649399513349</v>
       </c>
       <c r="Q6">
-        <v>4742.11951961068</v>
+        <v>4672.64939951335</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1043404731097734</v>
+        <v>0.1048823711681818</v>
       </c>
       <c r="T6">
-        <v>1.141062782234783</v>
+        <v>1.151625384027488</v>
       </c>
       <c r="U6">
         <v>0.05623661666253409</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>14.76174214990901</v>
+        <v>11.8093937199272</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1020986045887586</v>
+        <v>0.1020620734089459</v>
       </c>
       <c r="C7">
-        <v>134704.8824007564</v>
+        <v>133384.8307766176</v>
       </c>
       <c r="D7">
-        <v>141290.8439528719</v>
+        <v>141382.5846391562</v>
       </c>
       <c r="E7">
-        <v>-2965.269490194827</v>
+        <v>-1553.477179771724</v>
       </c>
       <c r="F7">
-        <v>7058.961552115517</v>
+        <v>8470.753862538621</v>
       </c>
       <c r="G7">
         <v>473</v>
@@ -2117,28 +2117,28 @@
         <v>4688</v>
       </c>
       <c r="M7">
-        <v>396.972114841887</v>
+        <v>476.3665378102643</v>
       </c>
       <c r="N7">
-        <v>4291.027885158113</v>
+        <v>4211.633462189736</v>
       </c>
       <c r="O7">
-        <v>536.3784856447642</v>
+        <v>526.454182773717</v>
       </c>
       <c r="P7">
-        <v>3754.649399513349</v>
+        <v>3685.179279416019</v>
       </c>
       <c r="Q7">
-        <v>4672.64939951335</v>
+        <v>4603.179279416019</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1048823711681818</v>
+        <v>0.1054357989725137</v>
       </c>
       <c r="T7">
-        <v>1.151625384027488</v>
+        <v>1.162412722028549</v>
       </c>
       <c r="U7">
         <v>0.05623661666253409</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>11.8093937199272</v>
+        <v>9.841161433272669</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1020620734089459</v>
+        <v>0.1021174172291334</v>
       </c>
       <c r="C8">
-        <v>133384.8307766176</v>
+        <v>131834.1000573171</v>
       </c>
       <c r="D8">
-        <v>141382.5846391562</v>
+        <v>141243.6462302788</v>
       </c>
       <c r="E8">
-        <v>-1553.477179771724</v>
+        <v>-141.6848693486227</v>
       </c>
       <c r="F8">
-        <v>8470.753862538621</v>
+        <v>9882.546172961722</v>
       </c>
       <c r="G8">
         <v>473</v>
@@ -2199,45 +2199,45 @@
         <v>4688</v>
       </c>
       <c r="M8">
-        <v>476.3665378102643</v>
+        <v>570.5847800380842</v>
       </c>
       <c r="N8">
-        <v>4211.633462189736</v>
+        <v>4117.415219961916</v>
       </c>
       <c r="O8">
-        <v>526.454182773717</v>
+        <v>514.6769024952395</v>
       </c>
       <c r="P8">
-        <v>3685.179279416019</v>
+        <v>3602.738317466676</v>
       </c>
       <c r="Q8">
-        <v>4603.179279416019</v>
+        <v>4520.738317466676</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1054357989725137</v>
+        <v>0.1060011284500572</v>
       </c>
       <c r="T8">
-        <v>1.162412722028549</v>
+        <v>1.173432045793073</v>
       </c>
       <c r="U8">
-        <v>0.05623661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.04920703957971732</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>9.841161433272669</v>
+        <v>8.216132227864708</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1021174172291334</v>
+        <v>0.1020940110493208</v>
       </c>
       <c r="C9">
-        <v>131834.1000573171</v>
+        <v>130481.034672182</v>
       </c>
       <c r="D9">
-        <v>141243.6462302789</v>
+        <v>141302.3731555668</v>
       </c>
       <c r="E9">
-        <v>-141.6848693486209</v>
+        <v>1270.107441074482</v>
       </c>
       <c r="F9">
-        <v>9882.546172961724</v>
+        <v>11294.33848338483</v>
       </c>
       <c r="G9">
         <v>473</v>
@@ -2281,28 +2281,28 @@
         <v>4688</v>
       </c>
       <c r="M9">
-        <v>570.5847800380843</v>
+        <v>652.0968914720963</v>
       </c>
       <c r="N9">
-        <v>4117.415219961916</v>
+        <v>4035.903108527904</v>
       </c>
       <c r="O9">
-        <v>514.6769024952395</v>
+        <v>504.487888565988</v>
       </c>
       <c r="P9">
-        <v>3602.738317466676</v>
+        <v>3531.415219961916</v>
       </c>
       <c r="Q9">
-        <v>4520.738317466676</v>
+        <v>4449.415219961916</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1060011284500572</v>
+        <v>0.1065787476988515</v>
       </c>
       <c r="T9">
-        <v>1.173432045793073</v>
+        <v>1.184690920074217</v>
       </c>
       <c r="U9">
         <v>0.05773661666253409</v>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.216132227864708</v>
+        <v>7.18911569938162</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2327,22 +2327,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1020940110493208</v>
+        <v>0.1022044798695081</v>
       </c>
       <c r="C10">
-        <v>130481.034672182</v>
+        <v>128792.5000446896</v>
       </c>
       <c r="D10">
-        <v>141302.3731555668</v>
+        <v>141025.6308384976</v>
       </c>
       <c r="E10">
-        <v>1270.107441074482</v>
+        <v>2681.899751497585</v>
       </c>
       <c r="F10">
-        <v>11294.33848338483</v>
+        <v>12706.13079380793</v>
       </c>
       <c r="G10">
         <v>473</v>
@@ -2363,45 +2363,45 @@
         <v>4688</v>
       </c>
       <c r="M10">
-        <v>652.0968914720963</v>
+        <v>755.2094252555819</v>
       </c>
       <c r="N10">
-        <v>4035.903108527904</v>
+        <v>3932.790574744418</v>
       </c>
       <c r="O10">
-        <v>504.487888565988</v>
+        <v>491.5988218430523</v>
       </c>
       <c r="P10">
-        <v>3531.415219961916</v>
+        <v>3441.191752901366</v>
       </c>
       <c r="Q10">
-        <v>4449.415219961916</v>
+        <v>4359.191752901366</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1065787476988515</v>
+        <v>0.1071690618761908</v>
       </c>
       <c r="T10">
-        <v>1.184690920074217</v>
+        <v>1.196197242141759</v>
       </c>
       <c r="U10">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05051953957971732</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.18911569938162</v>
+        <v>6.207549645468822</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1022044798695081</v>
+        <v>0.1021959486896956</v>
       </c>
       <c r="C11">
-        <v>128792.5000446896</v>
+        <v>127402.0410931836</v>
       </c>
       <c r="D11">
-        <v>141025.6308384976</v>
+        <v>141046.9641974146</v>
       </c>
       <c r="E11">
-        <v>2681.899751497585</v>
+        <v>4093.692061920689</v>
       </c>
       <c r="F11">
-        <v>12706.13079380793</v>
+        <v>14117.92310423103</v>
       </c>
       <c r="G11">
         <v>473</v>
@@ -2445,28 +2445,28 @@
         <v>4688</v>
       </c>
       <c r="M11">
-        <v>755.2094252555819</v>
+        <v>839.1215836173131</v>
       </c>
       <c r="N11">
-        <v>3932.790574744418</v>
+        <v>3848.878416382687</v>
       </c>
       <c r="O11">
-        <v>491.5988218430523</v>
+        <v>481.1098020478358</v>
       </c>
       <c r="P11">
-        <v>3441.191752901366</v>
+        <v>3367.768614334851</v>
       </c>
       <c r="Q11">
-        <v>4359.191752901366</v>
+        <v>4285.768614334851</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1071690618761908</v>
+        <v>0.1077724941463598</v>
       </c>
       <c r="T11">
-        <v>1.196197242141759</v>
+        <v>1.207959260255248</v>
       </c>
       <c r="U11">
         <v>0.05943661666253409</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>6.207549645468822</v>
+        <v>5.58679468092194</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2491,22 +2491,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1021959486896956</v>
+        <v>0.102264417509883</v>
       </c>
       <c r="C12">
-        <v>127402.0410931836</v>
+        <v>125819.2150653238</v>
       </c>
       <c r="D12">
-        <v>141046.9641974146</v>
+        <v>140875.9304799779</v>
       </c>
       <c r="E12">
-        <v>4093.69206192069</v>
+        <v>5505.484372343792</v>
       </c>
       <c r="F12">
-        <v>14117.92310423103</v>
+        <v>15529.71541465414</v>
       </c>
       <c r="G12">
         <v>473</v>
@@ -2527,45 +2527,45 @@
         <v>4688</v>
       </c>
       <c r="M12">
-        <v>839.1215836173133</v>
+        <v>935.4575143107678</v>
       </c>
       <c r="N12">
-        <v>3848.878416382687</v>
+        <v>3752.542485689232</v>
       </c>
       <c r="O12">
-        <v>481.1098020478358</v>
+        <v>469.067810711154</v>
       </c>
       <c r="P12">
-        <v>3367.768614334851</v>
+        <v>3283.474674978078</v>
       </c>
       <c r="Q12">
-        <v>4285.768614334851</v>
+        <v>4201.474674978079</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1077724941463598</v>
+        <v>0.108389486692263</v>
       </c>
       <c r="T12">
-        <v>1.207959260255248</v>
+        <v>1.219985593382523</v>
       </c>
       <c r="U12">
-        <v>0.05943661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.58679468092194</v>
+        <v>5.011451539254622</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.102264417509883</v>
+        <v>0.1022628863300703</v>
       </c>
       <c r="C13">
-        <v>125819.2150653238</v>
+        <v>124411.2430764404</v>
       </c>
       <c r="D13">
-        <v>140875.9304799779</v>
+        <v>140879.7508015176</v>
       </c>
       <c r="E13">
-        <v>5505.484372343792</v>
+        <v>6917.276682766897</v>
       </c>
       <c r="F13">
-        <v>15529.71541465414</v>
+        <v>16941.50772507724</v>
       </c>
       <c r="G13">
         <v>473</v>
@@ -2609,28 +2609,28 @@
         <v>4688</v>
       </c>
       <c r="M13">
-        <v>935.4575143107678</v>
+        <v>1020.499106520838</v>
       </c>
       <c r="N13">
-        <v>3752.542485689232</v>
+        <v>3667.500893479162</v>
       </c>
       <c r="O13">
-        <v>469.067810711154</v>
+        <v>458.4376116848953</v>
       </c>
       <c r="P13">
-        <v>3283.474674978078</v>
+        <v>3209.063281794267</v>
       </c>
       <c r="Q13">
-        <v>4201.474674978079</v>
+        <v>4127.063281794267</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.108389486692263</v>
+        <v>0.1090205017960276</v>
       </c>
       <c r="T13">
-        <v>1.219985593382523</v>
+        <v>1.23228525226269</v>
       </c>
       <c r="U13">
         <v>0.06023661666253409</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.011451539254622</v>
+        <v>4.59383057765007</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1022628863300703</v>
+        <v>0.1023751051502577</v>
       </c>
       <c r="C14">
-        <v>124411.2430764404</v>
+        <v>122720.0105532018</v>
       </c>
       <c r="D14">
-        <v>140879.7508015176</v>
+        <v>140600.3105887022</v>
       </c>
       <c r="E14">
-        <v>6917.276682766897</v>
+        <v>8329.068993189998</v>
       </c>
       <c r="F14">
-        <v>16941.50772507724</v>
+        <v>18353.30003550034</v>
       </c>
       <c r="G14">
         <v>473</v>
@@ -2691,45 +2691,45 @@
         <v>4688</v>
       </c>
       <c r="M14">
-        <v>1020.499106520838</v>
+        <v>1123.893998766408</v>
       </c>
       <c r="N14">
-        <v>3667.500893479162</v>
+        <v>3564.106001233592</v>
       </c>
       <c r="O14">
-        <v>458.4376116848953</v>
+        <v>445.513250154199</v>
       </c>
       <c r="P14">
-        <v>3209.063281794267</v>
+        <v>3118.592751079393</v>
       </c>
       <c r="Q14">
-        <v>4127.063281794267</v>
+        <v>4036.592751079393</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1090205017960276</v>
+        <v>0.1096660229941316</v>
       </c>
       <c r="T14">
-        <v>1.23228525226269</v>
+        <v>1.244867661921711</v>
       </c>
       <c r="U14">
-        <v>0.06023661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.59383057765007</v>
+        <v>4.171211880431406</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2737,22 +2737,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1023751051502577</v>
+        <v>0.1023823239704452</v>
       </c>
       <c r="C15">
-        <v>122720.0105532018</v>
+        <v>121290.2803376307</v>
       </c>
       <c r="D15">
-        <v>140600.3105887022</v>
+        <v>140582.3726835542</v>
       </c>
       <c r="E15">
-        <v>8329.068993189998</v>
+        <v>9740.861303613103</v>
       </c>
       <c r="F15">
-        <v>18353.30003550034</v>
+        <v>19765.09234592345</v>
       </c>
       <c r="G15">
         <v>473</v>
@@ -2773,28 +2773,28 @@
         <v>4688</v>
       </c>
       <c r="M15">
-        <v>1123.893998766408</v>
+        <v>1210.347383286901</v>
       </c>
       <c r="N15">
-        <v>3564.106001233592</v>
+        <v>3477.652616713099</v>
       </c>
       <c r="O15">
-        <v>445.513250154199</v>
+        <v>434.7065770891374</v>
       </c>
       <c r="P15">
-        <v>3118.592751079393</v>
+        <v>3042.946039623962</v>
       </c>
       <c r="Q15">
-        <v>4036.592751079393</v>
+        <v>3960.946039623962</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1096660229941316</v>
+        <v>0.1103265563131218</v>
       </c>
       <c r="T15">
-        <v>1.244867661921711</v>
+        <v>1.25774268575885</v>
       </c>
       <c r="U15">
         <v>0.06123661666253409</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.171211880431406</v>
+        <v>3.873268174686305</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1023823239704452</v>
+        <v>0.1023895427906325</v>
       </c>
       <c r="C16">
-        <v>121290.2803376307</v>
+        <v>119860.5546985417</v>
       </c>
       <c r="D16">
-        <v>140582.3726835542</v>
+        <v>140564.4393548883</v>
       </c>
       <c r="E16">
-        <v>9740.861303613103</v>
+        <v>11152.65361403621</v>
       </c>
       <c r="F16">
-        <v>19765.09234592345</v>
+        <v>21176.88465634655</v>
       </c>
       <c r="G16">
         <v>473</v>
@@ -2855,28 +2855,28 @@
         <v>4688</v>
       </c>
       <c r="M16">
-        <v>1210.347383286901</v>
+        <v>1296.800767807394</v>
       </c>
       <c r="N16">
-        <v>3477.652616713099</v>
+        <v>3391.199232192606</v>
       </c>
       <c r="O16">
-        <v>434.7065770891374</v>
+        <v>423.8999040240758</v>
       </c>
       <c r="P16">
-        <v>3042.946039623962</v>
+        <v>2967.29932816853</v>
       </c>
       <c r="Q16">
-        <v>3960.946039623962</v>
+        <v>3885.29932816853</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1103265563131218</v>
+        <v>0.1110026315925587</v>
       </c>
       <c r="T16">
-        <v>1.25774268575885</v>
+        <v>1.270920651333332</v>
       </c>
       <c r="U16">
         <v>0.06123661666253409</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>3.873268174686305</v>
+        <v>3.615050296373885</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1023895427906325</v>
+        <v>0.1023967616108199</v>
       </c>
       <c r="C17">
-        <v>119860.5546985417</v>
+        <v>118430.8336341835</v>
       </c>
       <c r="D17">
-        <v>140564.4393548883</v>
+        <v>140546.5106009531</v>
       </c>
       <c r="E17">
-        <v>11152.6536140362</v>
+        <v>12564.44592445931</v>
       </c>
       <c r="F17">
-        <v>21176.88465634655</v>
+        <v>22588.67696676965</v>
       </c>
       <c r="G17">
         <v>473</v>
@@ -2937,28 +2937,28 @@
         <v>4688</v>
       </c>
       <c r="M17">
-        <v>1296.800767807394</v>
+        <v>1383.254152327887</v>
       </c>
       <c r="N17">
-        <v>3391.199232192606</v>
+        <v>3304.745847672113</v>
       </c>
       <c r="O17">
-        <v>423.8999040240758</v>
+        <v>413.0932309590141</v>
       </c>
       <c r="P17">
-        <v>2967.29932816853</v>
+        <v>2891.652616713099</v>
       </c>
       <c r="Q17">
-        <v>3885.29932816853</v>
+        <v>3809.652616713099</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1110026315925587</v>
+        <v>0.1116948039024585</v>
       </c>
       <c r="T17">
-        <v>1.270920651333332</v>
+        <v>1.284412377992922</v>
       </c>
       <c r="U17">
         <v>0.06123661666253409</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.615050296373885</v>
+        <v>3.389109652850517</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2983,22 +2983,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1023967616108199</v>
+        <v>0.1024039804310073</v>
       </c>
       <c r="C18">
-        <v>118430.8336341835</v>
+        <v>117001.1171428059</v>
       </c>
       <c r="D18">
-        <v>140546.5106009531</v>
+        <v>140528.5864199986</v>
       </c>
       <c r="E18">
-        <v>12564.44592445931</v>
+        <v>13976.23823488241</v>
       </c>
       <c r="F18">
-        <v>22588.67696676965</v>
+        <v>24000.46927719276</v>
       </c>
       <c r="G18">
         <v>473</v>
@@ -3019,28 +3019,28 @@
         <v>4688</v>
       </c>
       <c r="M18">
-        <v>1383.254152327887</v>
+        <v>1469.70753684838</v>
       </c>
       <c r="N18">
-        <v>3304.745847672113</v>
+        <v>3218.292463151621</v>
       </c>
       <c r="O18">
-        <v>413.0932309590141</v>
+        <v>402.2865578939526</v>
       </c>
       <c r="P18">
-        <v>2891.652616713099</v>
+        <v>2816.005905257668</v>
       </c>
       <c r="Q18">
-        <v>3809.652616713099</v>
+        <v>3734.005905257668</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1116948039024585</v>
+        <v>0.1124036550631992</v>
       </c>
       <c r="T18">
-        <v>1.284412377992922</v>
+        <v>1.29822920649973</v>
       </c>
       <c r="U18">
         <v>0.06123661666253409</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.389109652850517</v>
+        <v>3.189750261506369</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3065,22 +3065,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1024039804310073</v>
+        <v>0.1024111992511947</v>
       </c>
       <c r="C19">
-        <v>117001.1171428059</v>
+        <v>115571.4052226594</v>
       </c>
       <c r="D19">
-        <v>140528.5864199986</v>
+        <v>140510.6668102752</v>
       </c>
       <c r="E19">
-        <v>13976.23823488241</v>
+        <v>15388.03054530552</v>
       </c>
       <c r="F19">
-        <v>24000.46927719276</v>
+        <v>25412.26158761586</v>
       </c>
       <c r="G19">
         <v>473</v>
@@ -3101,28 +3101,28 @@
         <v>4688</v>
       </c>
       <c r="M19">
-        <v>1469.70753684838</v>
+        <v>1556.160921368873</v>
       </c>
       <c r="N19">
-        <v>3218.292463151621</v>
+        <v>3131.839078631127</v>
       </c>
       <c r="O19">
-        <v>402.2865578939526</v>
+        <v>391.4798848288909</v>
       </c>
       <c r="P19">
-        <v>2816.005905257668</v>
+        <v>2740.359193802236</v>
       </c>
       <c r="Q19">
-        <v>3734.005905257668</v>
+        <v>3658.359193802236</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1124036550631992</v>
+        <v>0.113129795276641</v>
       </c>
       <c r="T19">
-        <v>1.29822920649973</v>
+        <v>1.312383030823778</v>
       </c>
       <c r="U19">
         <v>0.06123661666253409</v>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.189750261506369</v>
+        <v>3.012541913644904</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1024111992511947</v>
+        <v>0.1028340430713821</v>
       </c>
       <c r="C20">
-        <v>115571.4052226594</v>
+        <v>113117.8830272134</v>
       </c>
       <c r="D20">
-        <v>140510.6668102752</v>
+        <v>139468.9369252524</v>
       </c>
       <c r="E20">
-        <v>15388.03054530552</v>
+        <v>16799.82285572862</v>
       </c>
       <c r="F20">
-        <v>25412.26158761586</v>
+        <v>26824.05389803896</v>
       </c>
       <c r="G20">
         <v>473</v>
@@ -3183,45 +3183,45 @@
         <v>4688</v>
       </c>
       <c r="M20">
-        <v>1556.160921368872</v>
+        <v>1709.674440634463</v>
       </c>
       <c r="N20">
-        <v>3131.839078631127</v>
+        <v>2978.325559365537</v>
       </c>
       <c r="O20">
-        <v>391.4798848288909</v>
+        <v>372.2906949206921</v>
       </c>
       <c r="P20">
-        <v>2740.359193802236</v>
+        <v>2606.034864444845</v>
       </c>
       <c r="Q20">
-        <v>3658.359193802236</v>
+        <v>3524.034864444845</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.113129795276641</v>
+        <v>0.1138738648780689</v>
       </c>
       <c r="T20">
-        <v>1.312383030823778</v>
+        <v>1.326886332291629</v>
       </c>
       <c r="U20">
-        <v>0.06123661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.012541913644904</v>
+        <v>2.742042513228586</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3229,22 +3229,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1028340430713821</v>
+        <v>0.1028631368915695</v>
       </c>
       <c r="C21">
-        <v>113117.8830272134</v>
+        <v>111634.9820397413</v>
       </c>
       <c r="D21">
-        <v>139468.9369252524</v>
+        <v>139397.8282482033</v>
       </c>
       <c r="E21">
-        <v>16799.82285572862</v>
+        <v>18211.61516615173</v>
       </c>
       <c r="F21">
-        <v>26824.05389803896</v>
+        <v>28235.84620846207</v>
       </c>
       <c r="G21">
         <v>473</v>
@@ -3265,28 +3265,28 @@
         <v>4688</v>
       </c>
       <c r="M21">
-        <v>1709.674440634463</v>
+        <v>1799.657305931014</v>
       </c>
       <c r="N21">
-        <v>2978.325559365537</v>
+        <v>2888.342694068986</v>
       </c>
       <c r="O21">
-        <v>372.2906949206921</v>
+        <v>361.0428367586233</v>
       </c>
       <c r="P21">
-        <v>2606.034864444845</v>
+        <v>2527.299857310363</v>
       </c>
       <c r="Q21">
-        <v>3524.034864444845</v>
+        <v>3445.299857310363</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1138738648780689</v>
+        <v>0.1146365362195326</v>
       </c>
       <c r="T21">
-        <v>1.326886332291629</v>
+        <v>1.341752216296177</v>
       </c>
       <c r="U21">
         <v>0.06373661666253409</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.742042513228586</v>
+        <v>2.604940387567157</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3311,22 +3311,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1028631368915695</v>
+        <v>0.1035353557117569</v>
       </c>
       <c r="C22">
-        <v>111634.9820397413</v>
+        <v>108600.1661506722</v>
       </c>
       <c r="D22">
-        <v>139397.8282482033</v>
+        <v>137774.8046695573</v>
       </c>
       <c r="E22">
-        <v>18211.61516615173</v>
+        <v>19623.40747657483</v>
       </c>
       <c r="F22">
-        <v>28235.84620846207</v>
+        <v>29647.63851888517</v>
       </c>
       <c r="G22">
         <v>473</v>
@@ -3347,45 +3347,45 @@
         <v>4688</v>
       </c>
       <c r="M22">
-        <v>1799.657305931014</v>
+        <v>1993.406906043662</v>
       </c>
       <c r="N22">
-        <v>2888.342694068986</v>
+        <v>2694.593093956338</v>
       </c>
       <c r="O22">
-        <v>361.0428367586233</v>
+        <v>336.8241367445422</v>
       </c>
       <c r="P22">
-        <v>2527.299857310363</v>
+        <v>2357.768957211796</v>
       </c>
       <c r="Q22">
-        <v>3445.299857310363</v>
+        <v>3275.768957211796</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1146365362195326</v>
+        <v>0.1154185156962231</v>
       </c>
       <c r="T22">
-        <v>1.341752216296177</v>
+        <v>1.356994451794511</v>
       </c>
       <c r="U22">
-        <v>0.06373661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.604940387567157</v>
+        <v>2.351752663135058</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3393,22 +3393,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1035353557117569</v>
+        <v>0.1041340745319443</v>
       </c>
       <c r="C23">
-        <v>108600.1661506722</v>
+        <v>105774.3054905723</v>
       </c>
       <c r="D23">
-        <v>137774.8046695574</v>
+        <v>136360.7363198806</v>
       </c>
       <c r="E23">
-        <v>19623.40747657482</v>
+        <v>21035.19978699793</v>
       </c>
       <c r="F23">
-        <v>29647.63851888517</v>
+        <v>31059.43082930827</v>
       </c>
       <c r="G23">
         <v>473</v>
@@ -3429,45 +3429,45 @@
         <v>4688</v>
       </c>
       <c r="M23">
-        <v>1993.406906043662</v>
+        <v>2175.297450748757</v>
       </c>
       <c r="N23">
-        <v>2694.593093956338</v>
+        <v>2512.702549251243</v>
       </c>
       <c r="O23">
-        <v>336.8241367445423</v>
+        <v>314.0878186564054</v>
       </c>
       <c r="P23">
-        <v>2357.768957211796</v>
+        <v>2198.614730594838</v>
       </c>
       <c r="Q23">
-        <v>3275.768957211796</v>
+        <v>3116.614730594838</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1154185156962231</v>
+        <v>0.1162205459287263</v>
       </c>
       <c r="T23">
-        <v>1.356994451794511</v>
+        <v>1.372627513844084</v>
       </c>
       <c r="U23">
-        <v>0.06723661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05883203957971732</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.351752663135059</v>
+        <v>2.15510756857015</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3475,22 +3475,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1041340745319443</v>
+        <v>0.1042182933521317</v>
       </c>
       <c r="C24">
-        <v>105774.3054905723</v>
+        <v>104165.928520212</v>
       </c>
       <c r="D24">
-        <v>136360.7363198806</v>
+        <v>136164.1516599434</v>
       </c>
       <c r="E24">
-        <v>21035.19978699793</v>
+        <v>22446.99209742103</v>
       </c>
       <c r="F24">
-        <v>31059.43082930827</v>
+        <v>32471.22313973138</v>
       </c>
       <c r="G24">
         <v>473</v>
@@ -3511,28 +3511,28 @@
         <v>4688</v>
       </c>
       <c r="M24">
-        <v>2175.297450748757</v>
+        <v>2274.174607600973</v>
       </c>
       <c r="N24">
-        <v>2512.702549251243</v>
+        <v>2413.825392399027</v>
       </c>
       <c r="O24">
-        <v>314.0878186564054</v>
+        <v>301.7281740498784</v>
       </c>
       <c r="P24">
-        <v>2198.614730594838</v>
+        <v>2112.097218349149</v>
       </c>
       <c r="Q24">
-        <v>3116.614730594838</v>
+        <v>3030.097218349149</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1162205459287263</v>
+        <v>0.1170434081153204</v>
       </c>
       <c r="T24">
-        <v>1.372627513844084</v>
+        <v>1.388666629453386</v>
       </c>
       <c r="U24">
         <v>0.07003661666253409</v>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.15510756857015</v>
+        <v>2.061407239501883</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1042182933521317</v>
+        <v>0.1059405121723191</v>
       </c>
       <c r="C25">
-        <v>104165.928520212</v>
+        <v>98854.86006209519</v>
       </c>
       <c r="D25">
-        <v>136164.1516599434</v>
+        <v>132264.8755122497</v>
       </c>
       <c r="E25">
-        <v>22446.99209742103</v>
+        <v>23858.78440784414</v>
       </c>
       <c r="F25">
-        <v>32471.22313973138</v>
+        <v>33883.01545015448</v>
       </c>
       <c r="G25">
         <v>473</v>
@@ -3593,45 +3593,45 @@
         <v>4688</v>
       </c>
       <c r="M25">
-        <v>2274.174607600973</v>
+        <v>2637.339284964394</v>
       </c>
       <c r="N25">
-        <v>2413.825392399027</v>
+        <v>2050.660715035606</v>
       </c>
       <c r="O25">
-        <v>301.7281740498784</v>
+        <v>256.3325893794507</v>
       </c>
       <c r="P25">
-        <v>2112.097218349149</v>
+        <v>1794.328125656155</v>
       </c>
       <c r="Q25">
-        <v>3030.097218349149</v>
+        <v>2712.328125656155</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1170434081153204</v>
+        <v>0.1178879245699828</v>
       </c>
       <c r="T25">
-        <v>1.388666629453386</v>
+        <v>1.405127827052407</v>
       </c>
       <c r="U25">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971732</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.061407239501883</v>
+        <v>1.777549072554497</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1059405121723191</v>
+        <v>0.1069461059925065</v>
       </c>
       <c r="C26">
-        <v>98854.86006209522</v>
+        <v>95267.87213971815</v>
       </c>
       <c r="D26">
-        <v>132264.8755122497</v>
+        <v>130089.6799002957</v>
       </c>
       <c r="E26">
-        <v>23858.78440784414</v>
+        <v>25270.57671826724</v>
       </c>
       <c r="F26">
-        <v>33883.01545015448</v>
+        <v>35294.80776057758</v>
       </c>
       <c r="G26">
         <v>473</v>
@@ -3675,45 +3675,45 @@
         <v>4688</v>
       </c>
       <c r="M26">
-        <v>2637.339284964394</v>
+        <v>2884.878172104163</v>
       </c>
       <c r="N26">
-        <v>2050.660715035606</v>
+        <v>1803.121827895837</v>
       </c>
       <c r="O26">
-        <v>256.3325893794507</v>
+        <v>225.3902284869796</v>
       </c>
       <c r="P26">
-        <v>1794.328125656155</v>
+        <v>1577.731599408857</v>
       </c>
       <c r="Q26">
-        <v>2712.328125656155</v>
+        <v>2495.731599408857</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1178879245699828</v>
+        <v>0.1187549614634362</v>
       </c>
       <c r="T26">
-        <v>1.405127827052407</v>
+        <v>1.422027989920735</v>
       </c>
       <c r="U26">
-        <v>0.07783661666253408</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.06810703957971732</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.777549072554497</v>
+        <v>1.62502529407704</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1069461059925065</v>
+        <v>0.1071326998126939</v>
       </c>
       <c r="C27">
-        <v>95267.87213971815</v>
+        <v>93460.30513792019</v>
       </c>
       <c r="D27">
-        <v>130089.6799002957</v>
+        <v>129693.9052089209</v>
       </c>
       <c r="E27">
-        <v>25270.57671826724</v>
+        <v>26682.36902869034</v>
       </c>
       <c r="F27">
-        <v>35294.80776057758</v>
+        <v>36706.60007100068</v>
       </c>
       <c r="G27">
         <v>473</v>
@@ -3757,28 +3757,28 @@
         <v>4688</v>
       </c>
       <c r="M27">
-        <v>2884.878172104163</v>
+        <v>3000.27329898833</v>
       </c>
       <c r="N27">
-        <v>1803.121827895837</v>
+        <v>1687.72670101167</v>
       </c>
       <c r="O27">
-        <v>225.3902284869796</v>
+        <v>210.9658376264588</v>
       </c>
       <c r="P27">
-        <v>1577.731599408857</v>
+        <v>1476.760863385211</v>
       </c>
       <c r="Q27">
-        <v>2495.731599408857</v>
+        <v>2394.760863385211</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1187549614634362</v>
+        <v>0.1196454317864424</v>
       </c>
       <c r="T27">
-        <v>1.422027989920735</v>
+        <v>1.439384913947666</v>
       </c>
       <c r="U27">
         <v>0.0817366166625341</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.62502529407704</v>
+        <v>1.562524321227923</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1071326998126939</v>
+        <v>0.1073192936328813</v>
       </c>
       <c r="C28">
-        <v>93460.30513792019</v>
+        <v>91655.13898006038</v>
       </c>
       <c r="D28">
-        <v>129693.9052089209</v>
+        <v>129300.5313614842</v>
       </c>
       <c r="E28">
-        <v>26682.36902869034</v>
+        <v>28094.16133911345</v>
       </c>
       <c r="F28">
-        <v>36706.60007100068</v>
+        <v>38118.39238142379</v>
       </c>
       <c r="G28">
         <v>473</v>
@@ -3839,28 +3839,28 @@
         <v>4688</v>
       </c>
       <c r="M28">
-        <v>3000.27329898833</v>
+        <v>3115.668425872497</v>
       </c>
       <c r="N28">
-        <v>1687.72670101167</v>
+        <v>1572.331574127503</v>
       </c>
       <c r="O28">
-        <v>210.9658376264588</v>
+        <v>196.5414467659379</v>
       </c>
       <c r="P28">
-        <v>1476.760863385211</v>
+        <v>1375.790127361565</v>
       </c>
       <c r="Q28">
-        <v>2394.760863385211</v>
+        <v>2293.790127361565</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1196454317864424</v>
+        <v>0.1205602985566543</v>
       </c>
       <c r="T28">
-        <v>1.439384913947666</v>
+        <v>1.457217370139719</v>
       </c>
       <c r="U28">
         <v>0.0817366166625341</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.562524321227923</v>
+        <v>1.504653050071333</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1073192936328813</v>
+        <v>0.1182942647238389</v>
       </c>
       <c r="C29">
-        <v>91655.13898006038</v>
+        <v>70668.42444449876</v>
       </c>
       <c r="D29">
-        <v>129300.5313614842</v>
+        <v>109725.6091363457</v>
       </c>
       <c r="E29">
-        <v>28094.16133911345</v>
+        <v>29505.95364953655</v>
       </c>
       <c r="F29">
-        <v>38118.39238142379</v>
+        <v>39530.18469184689</v>
       </c>
       <c r="G29">
         <v>473</v>
@@ -3921,45 +3921,45 @@
         <v>4688</v>
       </c>
       <c r="M29">
-        <v>3115.668425872497</v>
+        <v>4922.95545756771</v>
       </c>
       <c r="N29">
-        <v>1572.331574127503</v>
+        <v>-234.9554575677103</v>
       </c>
       <c r="O29">
-        <v>196.5414467659379</v>
+        <v>-29.36943219596378</v>
       </c>
       <c r="P29">
-        <v>1375.790127361565</v>
+        <v>-205.5860253717465</v>
       </c>
       <c r="Q29">
-        <v>2293.790127361565</v>
+        <v>712.4139746282535</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1205602985566543</v>
+        <v>0.1216316169876492</v>
       </c>
       <c r="T29">
-        <v>1.457217370139719</v>
+        <v>1.478099360403758</v>
       </c>
       <c r="U29">
-        <v>0.0817366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V29">
-        <v>0.125</v>
+        <v>0.1190341868925878</v>
       </c>
       <c r="W29">
-        <v>0.07151953957971734</v>
+        <v>0.1097125017597554</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.504653050071333</v>
+        <v>0.9522734951407026</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1182942647238389</v>
+        <v>0.1190816308904643</v>
       </c>
       <c r="C30">
-        <v>70668.42444449876</v>
+        <v>68077.69777908767</v>
       </c>
       <c r="D30">
-        <v>109725.6091363457</v>
+        <v>108546.6747813577</v>
       </c>
       <c r="E30">
-        <v>29505.95364953655</v>
+        <v>30917.74595995966</v>
       </c>
       <c r="F30">
-        <v>39530.18469184689</v>
+        <v>40941.97700227</v>
       </c>
       <c r="G30">
         <v>473</v>
@@ -4003,37 +4003,37 @@
         <v>4688</v>
       </c>
       <c r="M30">
-        <v>4922.95545756771</v>
+        <v>5098.775295337987</v>
       </c>
       <c r="N30">
-        <v>-234.9554575677103</v>
+        <v>-410.7752953379868</v>
       </c>
       <c r="O30">
-        <v>-29.36943219596378</v>
+        <v>-51.34691191724835</v>
       </c>
       <c r="P30">
-        <v>-205.5860253717465</v>
+        <v>-359.4283834207384</v>
       </c>
       <c r="Q30">
-        <v>712.4139746282535</v>
+        <v>558.5716165792616</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1216316169876492</v>
+        <v>0.1226996679311372</v>
       </c>
       <c r="T30">
-        <v>1.478099360403758</v>
+        <v>1.498917661254515</v>
       </c>
       <c r="U30">
         <v>0.1245366166625341</v>
       </c>
       <c r="V30">
-        <v>0.1190341868925878</v>
+        <v>0.1149295597583606</v>
       </c>
       <c r="W30">
-        <v>0.1097125017597554</v>
+        <v>0.1102236781357133</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.9522734951407026</v>
+        <v>0.919436478066885</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4049,22 +4049,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1190816308904643</v>
+        <v>0.1198689970570896</v>
       </c>
       <c r="C31">
-        <v>68077.6977790877</v>
+        <v>65512.0356632364</v>
       </c>
       <c r="D31">
-        <v>108546.6747813577</v>
+        <v>107392.8049759295</v>
       </c>
       <c r="E31">
-        <v>30917.74595995965</v>
+        <v>32329.53827038275</v>
       </c>
       <c r="F31">
-        <v>40941.97700227</v>
+        <v>42353.7693126931</v>
       </c>
       <c r="G31">
         <v>473</v>
@@ -4085,37 +4085,37 @@
         <v>4688</v>
       </c>
       <c r="M31">
-        <v>5098.775295337986</v>
+        <v>5274.595133108261</v>
       </c>
       <c r="N31">
-        <v>-410.7752953379859</v>
+        <v>-586.5951331082606</v>
       </c>
       <c r="O31">
-        <v>-51.34691191724824</v>
+        <v>-73.32439163853257</v>
       </c>
       <c r="P31">
-        <v>-359.4283834207376</v>
+        <v>-513.270741469728</v>
       </c>
       <c r="Q31">
-        <v>558.5716165792624</v>
+        <v>404.729258530272</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1226996679311372</v>
+        <v>0.1237982346158678</v>
       </c>
       <c r="T31">
-        <v>1.498917661254515</v>
+        <v>1.520330770701008</v>
       </c>
       <c r="U31">
         <v>0.1245366166625341</v>
       </c>
       <c r="V31">
-        <v>0.1149295597583607</v>
+        <v>0.111098574433082</v>
       </c>
       <c r="W31">
-        <v>0.1102236781357133</v>
+        <v>0.1107007760866073</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9194364780668851</v>
+        <v>0.8887885954646557</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1198689970570896</v>
+        <v>0.120656363223715</v>
       </c>
       <c r="C32">
-        <v>65512.0356632364</v>
+        <v>62970.64718308846</v>
       </c>
       <c r="D32">
-        <v>107392.8049759295</v>
+        <v>106263.2088062047</v>
       </c>
       <c r="E32">
-        <v>32329.53827038275</v>
+        <v>33741.33058080586</v>
       </c>
       <c r="F32">
-        <v>42353.7693126931</v>
+        <v>43765.56162311621</v>
       </c>
       <c r="G32">
         <v>473</v>
@@ -4167,37 +4167,37 @@
         <v>4688</v>
       </c>
       <c r="M32">
-        <v>5274.595133108261</v>
+        <v>5450.414970878536</v>
       </c>
       <c r="N32">
-        <v>-586.5951331082606</v>
+        <v>-762.4149708785362</v>
       </c>
       <c r="O32">
-        <v>-73.32439163853257</v>
+        <v>-95.30187135981703</v>
       </c>
       <c r="P32">
-        <v>-513.270741469728</v>
+        <v>-667.1130995187192</v>
       </c>
       <c r="Q32">
-        <v>404.729258530272</v>
+        <v>250.8869004812808</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1237982346158678</v>
+        <v>0.1249286438131992</v>
       </c>
       <c r="T32">
-        <v>1.520330770701008</v>
+        <v>1.542364549986529</v>
       </c>
       <c r="U32">
         <v>0.1245366166625341</v>
       </c>
       <c r="V32">
-        <v>0.111098574433082</v>
+        <v>0.1075147494513696</v>
       </c>
       <c r="W32">
-        <v>0.1107007760866073</v>
+        <v>0.1111470935245405</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8887885954646557</v>
+        <v>0.8601179956109571</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.120656363223715</v>
+        <v>0.1214437293903403</v>
       </c>
       <c r="C33">
-        <v>62970.64718308846</v>
+        <v>60452.7743548831</v>
       </c>
       <c r="D33">
-        <v>106263.2088062047</v>
+        <v>105157.1282884224</v>
       </c>
       <c r="E33">
-        <v>33741.33058080586</v>
+        <v>35153.12289122897</v>
       </c>
       <c r="F33">
-        <v>43765.56162311621</v>
+        <v>45177.35393353931</v>
       </c>
       <c r="G33">
         <v>473</v>
@@ -4249,37 +4249,37 @@
         <v>4688</v>
       </c>
       <c r="M33">
-        <v>5450.414970878536</v>
+        <v>5626.234808648812</v>
       </c>
       <c r="N33">
-        <v>-762.4149708785362</v>
+        <v>-938.2348086488118</v>
       </c>
       <c r="O33">
-        <v>-95.30187135981703</v>
+        <v>-117.2793510811015</v>
       </c>
       <c r="P33">
-        <v>-667.1130995187192</v>
+        <v>-820.9554575677104</v>
       </c>
       <c r="Q33">
-        <v>250.8869004812808</v>
+        <v>97.04454243228963</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1249286438131992</v>
+        <v>0.1260923003398638</v>
       </c>
       <c r="T33">
-        <v>1.542364549986529</v>
+        <v>1.565046381603978</v>
       </c>
       <c r="U33">
         <v>0.1245366166625341</v>
       </c>
       <c r="V33">
-        <v>0.1075147494513696</v>
+        <v>0.1041549135310143</v>
       </c>
       <c r="W33">
-        <v>0.1111470935245405</v>
+        <v>0.1115655161226028</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8601179956109571</v>
+        <v>0.8332393082481147</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1214437293903403</v>
+        <v>0.1222310955569657</v>
       </c>
       <c r="C34">
-        <v>60452.7743548831</v>
+        <v>57957.69042878406</v>
       </c>
       <c r="D34">
-        <v>105157.1282884224</v>
+        <v>104073.8366727465</v>
       </c>
       <c r="E34">
-        <v>35153.12289122897</v>
+        <v>36564.91520165207</v>
       </c>
       <c r="F34">
-        <v>45177.35393353931</v>
+        <v>46589.14624396242</v>
       </c>
       <c r="G34">
         <v>473</v>
@@ -4331,37 +4331,37 @@
         <v>4688</v>
       </c>
       <c r="M34">
-        <v>5626.234808648812</v>
+        <v>5802.054646419087</v>
       </c>
       <c r="N34">
-        <v>-938.2348086488118</v>
+        <v>-1114.054646419087</v>
       </c>
       <c r="O34">
-        <v>-117.2793510811015</v>
+        <v>-139.2568308023859</v>
       </c>
       <c r="P34">
-        <v>-820.9554575677104</v>
+        <v>-974.7978156167015</v>
       </c>
       <c r="Q34">
-        <v>97.04454243228963</v>
+        <v>-56.79781561670154</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1260923003398638</v>
+        <v>0.1272906928822499</v>
       </c>
       <c r="T34">
-        <v>1.565046381603978</v>
+        <v>1.588405282821949</v>
       </c>
       <c r="U34">
         <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.1041549135310143</v>
+        <v>0.1009987040300745</v>
       </c>
       <c r="W34">
-        <v>0.1115655161226028</v>
+        <v>0.111958579775328</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8332393082481147</v>
+        <v>0.8079896322405961</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4377,22 +4377,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1222310955569657</v>
+        <v>0.1517149560870955</v>
       </c>
       <c r="C35">
-        <v>57957.69042878406</v>
+        <v>27574.55546141365</v>
       </c>
       <c r="D35">
-        <v>104073.8366727465</v>
+        <v>75102.49401579917</v>
       </c>
       <c r="E35">
-        <v>36564.91520165207</v>
+        <v>37976.70751207517</v>
       </c>
       <c r="F35">
-        <v>46589.14624396242</v>
+        <v>48000.93855438552</v>
       </c>
       <c r="G35">
         <v>473</v>
@@ -4413,45 +4413,45 @@
         <v>4688</v>
       </c>
       <c r="M35">
-        <v>5802.054646419087</v>
+        <v>9923.551633359852</v>
       </c>
       <c r="N35">
-        <v>-1114.054646419087</v>
+        <v>-5235.551633359852</v>
       </c>
       <c r="O35">
-        <v>-139.2568308023859</v>
+        <v>-654.4439541699815</v>
       </c>
       <c r="P35">
-        <v>-974.7978156167015</v>
+        <v>-4581.10767918987</v>
       </c>
       <c r="Q35">
-        <v>-56.79781561670154</v>
+        <v>-3663.10767918987</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1272906928822499</v>
+        <v>0.129659482719109</v>
       </c>
       <c r="T35">
-        <v>1.588405282821949</v>
+        <v>1.634577405768538</v>
       </c>
       <c r="U35">
-        <v>0.1245366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V35">
-        <v>0.1009987040300745</v>
+        <v>0.05905143860289423</v>
       </c>
       <c r="W35">
-        <v>0.111958579775328</v>
+        <v>0.1945285220367164</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8079896322405961</v>
+        <v>0.4724115088231539</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4459,22 +4459,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1517149560870955</v>
+        <v>0.1533243222537209</v>
       </c>
       <c r="C36">
-        <v>27574.55546141365</v>
+        <v>25038.6694541895</v>
       </c>
       <c r="D36">
-        <v>75102.49401579917</v>
+        <v>73978.40031899812</v>
       </c>
       <c r="E36">
-        <v>37976.70751207517</v>
+        <v>39388.49982249827</v>
       </c>
       <c r="F36">
-        <v>48000.93855438552</v>
+        <v>49412.73086480862</v>
       </c>
       <c r="G36">
         <v>473</v>
@@ -4495,37 +4495,37 @@
         <v>4688</v>
       </c>
       <c r="M36">
-        <v>9923.551633359852</v>
+        <v>10215.42079904691</v>
       </c>
       <c r="N36">
-        <v>-5235.551633359852</v>
+        <v>-5527.420799046906</v>
       </c>
       <c r="O36">
-        <v>-654.4439541699815</v>
+        <v>-690.9275998808632</v>
       </c>
       <c r="P36">
-        <v>-4581.10767918987</v>
+        <v>-4836.493199166042</v>
       </c>
       <c r="Q36">
-        <v>-3663.10767918987</v>
+        <v>-3918.493199166042</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.129659482719109</v>
+        <v>0.1309496286070953</v>
       </c>
       <c r="T36">
-        <v>1.634577405768538</v>
+        <v>1.659724750472669</v>
       </c>
       <c r="U36">
         <v>0.2067366166625341</v>
       </c>
       <c r="V36">
-        <v>0.05905143860289423</v>
+        <v>0.05736425464281154</v>
       </c>
       <c r="W36">
-        <v>0.1945285220367164</v>
+        <v>0.1948773247403112</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4724115088231539</v>
+        <v>0.4589140371424922</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1533243222537209</v>
+        <v>0.1549336884203462</v>
       </c>
       <c r="C37">
-        <v>25038.6694541895</v>
+        <v>22535.93688271805</v>
       </c>
       <c r="D37">
-        <v>73978.40031899812</v>
+        <v>72887.46005794978</v>
       </c>
       <c r="E37">
-        <v>39388.49982249827</v>
+        <v>40800.29213292139</v>
       </c>
       <c r="F37">
-        <v>49412.73086480862</v>
+        <v>50824.52317523173</v>
       </c>
       <c r="G37">
         <v>473</v>
@@ -4577,37 +4577,37 @@
         <v>4688</v>
       </c>
       <c r="M37">
-        <v>10215.42079904691</v>
+        <v>10507.28996473396</v>
       </c>
       <c r="N37">
-        <v>-5527.420799046906</v>
+        <v>-5819.289964733962</v>
       </c>
       <c r="O37">
-        <v>-690.9275998808632</v>
+        <v>-727.4112455917452</v>
       </c>
       <c r="P37">
-        <v>-4836.493199166042</v>
+        <v>-5091.878719142216</v>
       </c>
       <c r="Q37">
-        <v>-3918.493199166042</v>
+        <v>-4173.878719142216</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1309496286070953</v>
+        <v>0.1322800915540812</v>
       </c>
       <c r="T37">
-        <v>1.659724750472669</v>
+        <v>1.685657949698805</v>
       </c>
       <c r="U37">
         <v>0.2067366166625341</v>
       </c>
       <c r="V37">
-        <v>0.05736425464281154</v>
+        <v>0.05577080312495565</v>
       </c>
       <c r="W37">
-        <v>0.1948773247403112</v>
+        <v>0.1952067495159285</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4589140371424922</v>
+        <v>0.4461664249996452</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4623,22 +4623,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1549336884203462</v>
+        <v>0.1565430545869715</v>
       </c>
       <c r="C38">
-        <v>22535.93688271806</v>
+        <v>20064.91234661713</v>
       </c>
       <c r="D38">
-        <v>72887.46005794978</v>
+        <v>71828.22783227195</v>
       </c>
       <c r="E38">
-        <v>40800.29213292137</v>
+        <v>42212.08444334447</v>
       </c>
       <c r="F38">
-        <v>50824.52317523172</v>
+        <v>52236.31548565482</v>
       </c>
       <c r="G38">
         <v>473</v>
@@ -4659,37 +4659,37 @@
         <v>4688</v>
       </c>
       <c r="M38">
-        <v>10507.28996473396</v>
+        <v>10799.15913042101</v>
       </c>
       <c r="N38">
-        <v>-5819.28996473396</v>
+        <v>-6111.159130421014</v>
       </c>
       <c r="O38">
-        <v>-727.411245591745</v>
+        <v>-763.8948913026268</v>
       </c>
       <c r="P38">
-        <v>-5091.878719142215</v>
+        <v>-5347.264239118387</v>
       </c>
       <c r="Q38">
-        <v>-4173.878719142215</v>
+        <v>-4429.264239118387</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1322800915540812</v>
+        <v>0.133652791420019</v>
       </c>
       <c r="T38">
-        <v>1.685657949698804</v>
+        <v>1.712414425090849</v>
       </c>
       <c r="U38">
         <v>0.2067366166625341</v>
       </c>
       <c r="V38">
-        <v>0.05577080312495566</v>
+        <v>0.05426348412157848</v>
       </c>
       <c r="W38">
-        <v>0.1952067495159285</v>
+        <v>0.1955183675469178</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4461664249996453</v>
+        <v>0.4341078729726279</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1565430545869715</v>
+        <v>0.1581524207535969</v>
       </c>
       <c r="C39">
-        <v>20064.91234661713</v>
+        <v>17624.23326271331</v>
       </c>
       <c r="D39">
-        <v>71828.22783227195</v>
+        <v>70799.34105879124</v>
       </c>
       <c r="E39">
-        <v>42212.08444334447</v>
+        <v>43623.87675376759</v>
       </c>
       <c r="F39">
-        <v>52236.31548565482</v>
+        <v>53648.10779607793</v>
       </c>
       <c r="G39">
         <v>473</v>
@@ -4741,37 +4741,37 @@
         <v>4688</v>
       </c>
       <c r="M39">
-        <v>10799.15913042101</v>
+        <v>11091.02829610807</v>
       </c>
       <c r="N39">
-        <v>-6111.159130421014</v>
+        <v>-6403.02829610807</v>
       </c>
       <c r="O39">
-        <v>-763.8948913026268</v>
+        <v>-800.3785370135088</v>
       </c>
       <c r="P39">
-        <v>-5347.264239118387</v>
+        <v>-5602.649759094562</v>
       </c>
       <c r="Q39">
-        <v>-4429.264239118387</v>
+        <v>-4684.649759094562</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.133652791420019</v>
+        <v>0.1350697719267935</v>
       </c>
       <c r="T39">
-        <v>1.712414425090849</v>
+        <v>1.740034012592314</v>
       </c>
       <c r="U39">
         <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.05426348412157848</v>
+        <v>0.05283549769732641</v>
       </c>
       <c r="W39">
-        <v>0.1955183675469178</v>
+        <v>0.1958135846289077</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4341078729726279</v>
+        <v>0.4226839815786113</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4787,22 +4787,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1581524207535969</v>
+        <v>0.1597617869202222</v>
       </c>
       <c r="C40">
-        <v>17624.23326271331</v>
+        <v>15212.6140173269</v>
       </c>
       <c r="D40">
-        <v>70799.34105879124</v>
+        <v>69799.51412382793</v>
       </c>
       <c r="E40">
-        <v>43623.87675376759</v>
+        <v>45035.66906419069</v>
       </c>
       <c r="F40">
-        <v>53648.10779607793</v>
+        <v>55059.90010650103</v>
       </c>
       <c r="G40">
         <v>473</v>
@@ -4823,37 +4823,37 @@
         <v>4688</v>
       </c>
       <c r="M40">
-        <v>11091.02829610807</v>
+        <v>11382.89746179512</v>
       </c>
       <c r="N40">
-        <v>-6403.02829610807</v>
+        <v>-6694.897461795124</v>
       </c>
       <c r="O40">
-        <v>-800.3785370135088</v>
+        <v>-836.8621827243905</v>
       </c>
       <c r="P40">
-        <v>-5602.649759094562</v>
+        <v>-5858.035279070734</v>
       </c>
       <c r="Q40">
-        <v>-4684.649759094562</v>
+        <v>-4940.035279070734</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1350697719267935</v>
+        <v>0.1365332108108393</v>
       </c>
       <c r="T40">
-        <v>1.740034012592314</v>
+        <v>1.768559160339729</v>
       </c>
       <c r="U40">
         <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.05283549769732641</v>
+        <v>0.05148074134611291</v>
       </c>
       <c r="W40">
-        <v>0.1958135846289077</v>
+        <v>0.1960936623733597</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4226839815786113</v>
+        <v>0.4118459307689033</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1597617869202222</v>
+        <v>0.1613711530868476</v>
       </c>
       <c r="C41">
-        <v>15212.6140173269</v>
+        <v>12828.84060714474</v>
       </c>
       <c r="D41">
-        <v>69799.51412382793</v>
+        <v>68827.53302406888</v>
       </c>
       <c r="E41">
-        <v>45035.66906419069</v>
+        <v>46447.46137461379</v>
       </c>
       <c r="F41">
-        <v>55059.90010650103</v>
+        <v>56471.69241692414</v>
       </c>
       <c r="G41">
         <v>473</v>
@@ -4905,37 +4905,37 @@
         <v>4688</v>
       </c>
       <c r="M41">
-        <v>11382.89746179512</v>
+        <v>11674.76662748218</v>
       </c>
       <c r="N41">
-        <v>-6694.897461795124</v>
+        <v>-6986.766627482179</v>
       </c>
       <c r="O41">
-        <v>-836.8621827243905</v>
+        <v>-873.3458284352723</v>
       </c>
       <c r="P41">
-        <v>-5858.035279070734</v>
+        <v>-6113.420799046906</v>
       </c>
       <c r="Q41">
-        <v>-4940.035279070734</v>
+        <v>-5195.420799046906</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1365332108108393</v>
+        <v>0.1380454309910199</v>
       </c>
       <c r="T41">
-        <v>1.768559160339729</v>
+        <v>1.798035146345392</v>
       </c>
       <c r="U41">
         <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.05148074134611291</v>
+        <v>0.0501937228124601</v>
       </c>
       <c r="W41">
-        <v>0.1960936623733597</v>
+        <v>0.1963597362305891</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4118459307689033</v>
+        <v>0.4015497824996808</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4951,22 +4951,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1613711530868476</v>
+        <v>0.1629805192534729</v>
       </c>
       <c r="C42">
-        <v>12828.84060714474</v>
+        <v>10471.76572170915</v>
       </c>
       <c r="D42">
-        <v>68827.53302406888</v>
+        <v>67882.25044905639</v>
       </c>
       <c r="E42">
-        <v>46447.46137461379</v>
+        <v>47859.25368503689</v>
       </c>
       <c r="F42">
-        <v>56471.69241692414</v>
+        <v>57883.48472734724</v>
       </c>
       <c r="G42">
         <v>473</v>
@@ -4987,37 +4987,37 @@
         <v>4688</v>
       </c>
       <c r="M42">
-        <v>11674.76662748218</v>
+        <v>11966.63579316923</v>
       </c>
       <c r="N42">
-        <v>-6986.766627482179</v>
+        <v>-7278.635793169233</v>
       </c>
       <c r="O42">
-        <v>-873.3458284352723</v>
+        <v>-909.8294741461541</v>
       </c>
       <c r="P42">
-        <v>-6113.420799046906</v>
+        <v>-6368.806319023079</v>
       </c>
       <c r="Q42">
-        <v>-5195.420799046906</v>
+        <v>-5450.806319023079</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1380454309910199</v>
+        <v>0.1396089128722237</v>
       </c>
       <c r="T42">
-        <v>1.798035146345392</v>
+        <v>1.828510318317347</v>
       </c>
       <c r="U42">
         <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.0501937228124601</v>
+        <v>0.04896948567069277</v>
       </c>
       <c r="W42">
-        <v>0.1963597362305891</v>
+        <v>0.1966128308752706</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4015497824996808</v>
+        <v>0.3917558853655422</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5033,22 +5033,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1629805192534729</v>
+        <v>0.1645898854200983</v>
       </c>
       <c r="C43">
-        <v>10471.76572170915</v>
+        <v>8140.304225641572</v>
       </c>
       <c r="D43">
-        <v>67882.25044905639</v>
+        <v>66962.58126341192</v>
       </c>
       <c r="E43">
-        <v>47859.25368503689</v>
+        <v>49271.04599546001</v>
       </c>
       <c r="F43">
-        <v>57883.48472734724</v>
+        <v>59295.27703777035</v>
       </c>
       <c r="G43">
         <v>473</v>
@@ -5069,37 +5069,37 @@
         <v>4688</v>
       </c>
       <c r="M43">
-        <v>11966.63579316923</v>
+        <v>12258.50495885629</v>
       </c>
       <c r="N43">
-        <v>-7278.635793169233</v>
+        <v>-7570.504958856289</v>
       </c>
       <c r="O43">
-        <v>-909.8294741461541</v>
+        <v>-946.3131198570361</v>
       </c>
       <c r="P43">
-        <v>-6368.806319023079</v>
+        <v>-6624.191838999252</v>
       </c>
       <c r="Q43">
-        <v>-5450.806319023079</v>
+        <v>-5706.191838999252</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1396089128722237</v>
+        <v>0.1412263079217448</v>
       </c>
       <c r="T43">
-        <v>1.828510318317347</v>
+        <v>1.860036358288336</v>
       </c>
       <c r="U43">
         <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.04896948567069277</v>
+        <v>0.04780354553567627</v>
       </c>
       <c r="W43">
-        <v>0.1966128308752706</v>
+        <v>0.196853873394015</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3917558853655422</v>
+        <v>0.3824283642854102</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5115,22 +5115,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1645898854200983</v>
+        <v>0.1661992515867236</v>
       </c>
       <c r="C44">
-        <v>8140.304225641601</v>
+        <v>5833.429003198791</v>
       </c>
       <c r="D44">
-        <v>66962.58126341194</v>
+        <v>66067.49835139223</v>
       </c>
       <c r="E44">
-        <v>49271.04599545999</v>
+        <v>50682.8383058831</v>
       </c>
       <c r="F44">
-        <v>59295.27703777033</v>
+        <v>60707.06934819344</v>
       </c>
       <c r="G44">
         <v>473</v>
@@ -5151,37 +5151,37 @@
         <v>4688</v>
       </c>
       <c r="M44">
-        <v>12258.50495885629</v>
+        <v>12550.37412454334</v>
       </c>
       <c r="N44">
-        <v>-7570.504958856285</v>
+        <v>-7862.374124543341</v>
       </c>
       <c r="O44">
-        <v>-946.3131198570356</v>
+        <v>-982.7967655679176</v>
       </c>
       <c r="P44">
-        <v>-6624.19183899925</v>
+        <v>-6879.577358975424</v>
       </c>
       <c r="Q44">
-        <v>-5706.19183899925</v>
+        <v>-5961.577358975424</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1412263079217447</v>
+        <v>0.1429004536747578</v>
       </c>
       <c r="T44">
-        <v>1.860036358288336</v>
+        <v>1.892668575100412</v>
       </c>
       <c r="U44">
         <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.04780354553567628</v>
+        <v>0.04669183517438148</v>
       </c>
       <c r="W44">
-        <v>0.196853873394015</v>
+        <v>0.1970837046328178</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3824283642854103</v>
+        <v>0.3735346813950519</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1661992515867236</v>
+        <v>0.1678086177533489</v>
       </c>
       <c r="C45">
-        <v>5833.429003198791</v>
+        <v>3550.167131705399</v>
       </c>
       <c r="D45">
-        <v>66067.49835139223</v>
+        <v>65196.02879032194</v>
       </c>
       <c r="E45">
-        <v>50682.8383058831</v>
+        <v>52094.6306163062</v>
       </c>
       <c r="F45">
-        <v>60707.06934819344</v>
+        <v>62118.86165861654</v>
       </c>
       <c r="G45">
         <v>473</v>
@@ -5233,37 +5233,37 @@
         <v>4688</v>
       </c>
       <c r="M45">
-        <v>12550.37412454334</v>
+        <v>12842.2432902304</v>
       </c>
       <c r="N45">
-        <v>-7862.374124543341</v>
+        <v>-8154.243290230395</v>
       </c>
       <c r="O45">
-        <v>-982.7967655679176</v>
+        <v>-1019.280411278799</v>
       </c>
       <c r="P45">
-        <v>-6879.577358975424</v>
+        <v>-7134.962878951595</v>
       </c>
       <c r="Q45">
-        <v>-5961.577358975424</v>
+        <v>-6216.962878951595</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1429004536747578</v>
+        <v>0.1446343903475213</v>
       </c>
       <c r="T45">
-        <v>1.892668575100412</v>
+        <v>1.926466228227205</v>
       </c>
       <c r="U45">
         <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.04669183517438148</v>
+        <v>0.04563065710223645</v>
       </c>
       <c r="W45">
-        <v>0.1970837046328178</v>
+        <v>0.1973030889971295</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3735346813950519</v>
+        <v>0.3650452568178916</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1678086177533489</v>
+        <v>0.1694179839199743</v>
       </c>
       <c r="C46">
-        <v>3550.167131705399</v>
+        <v>1289.596353891975</v>
       </c>
       <c r="D46">
-        <v>65196.02879032194</v>
+        <v>64347.25032293163</v>
       </c>
       <c r="E46">
-        <v>52094.6306163062</v>
+        <v>53506.42292672931</v>
       </c>
       <c r="F46">
-        <v>62118.86165861654</v>
+        <v>63530.65396903965</v>
       </c>
       <c r="G46">
         <v>473</v>
@@ -5315,37 +5315,37 @@
         <v>4688</v>
       </c>
       <c r="M46">
-        <v>12842.2432902304</v>
+        <v>13134.11245591745</v>
       </c>
       <c r="N46">
-        <v>-8154.243290230395</v>
+        <v>-8446.112455917451</v>
       </c>
       <c r="O46">
-        <v>-1019.280411278799</v>
+        <v>-1055.764056989681</v>
       </c>
       <c r="P46">
-        <v>-7134.962878951595</v>
+        <v>-7390.34839892777</v>
       </c>
       <c r="Q46">
-        <v>-6216.962878951595</v>
+        <v>-6472.34839892777</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1446343903475213</v>
+        <v>0.1464313792629308</v>
       </c>
       <c r="T46">
-        <v>1.926466228227205</v>
+        <v>1.961492886922245</v>
       </c>
       <c r="U46">
         <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.04563065710223645</v>
+        <v>0.04461664249996453</v>
       </c>
       <c r="W46">
-        <v>0.1973030889971295</v>
+        <v>0.1975127229452496</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3650452568178916</v>
+        <v>0.3569331399997162</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5361,22 +5361,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1694179839199743</v>
+        <v>0.1710273500865996</v>
       </c>
       <c r="C47">
-        <v>1289.596353891975</v>
+        <v>-949.158177751051</v>
       </c>
       <c r="D47">
-        <v>64347.25032293163</v>
+        <v>63520.2881017117</v>
       </c>
       <c r="E47">
-        <v>53506.42292672931</v>
+        <v>54918.21523715241</v>
       </c>
       <c r="F47">
-        <v>63530.65396903965</v>
+        <v>64942.44627946275</v>
       </c>
       <c r="G47">
         <v>473</v>
@@ -5397,37 +5397,37 @@
         <v>4688</v>
       </c>
       <c r="M47">
-        <v>13134.11245591745</v>
+        <v>13425.98162160451</v>
       </c>
       <c r="N47">
-        <v>-8446.112455917451</v>
+        <v>-8737.981621604506</v>
       </c>
       <c r="O47">
-        <v>-1055.764056989681</v>
+        <v>-1092.247702700563</v>
       </c>
       <c r="P47">
-        <v>-7390.34839892777</v>
+        <v>-7645.733918903942</v>
       </c>
       <c r="Q47">
-        <v>-6472.34839892777</v>
+        <v>-6727.733918903942</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1464313792629308</v>
+        <v>0.1482949233233555</v>
       </c>
       <c r="T47">
-        <v>1.961492886922245</v>
+        <v>1.997816829272657</v>
       </c>
       <c r="U47">
         <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.04461664249996453</v>
+        <v>0.04364671548909573</v>
       </c>
       <c r="W47">
-        <v>0.1975127229452496</v>
+        <v>0.1977132423738862</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3569331399997162</v>
+        <v>0.3491737239127658</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1710273500865996</v>
+        <v>0.172636716253225</v>
       </c>
       <c r="C48">
-        <v>-949.158177751051</v>
+        <v>-3166.926908764348</v>
       </c>
       <c r="D48">
-        <v>63520.2881017117</v>
+        <v>62714.31168112151</v>
       </c>
       <c r="E48">
-        <v>54918.21523715241</v>
+        <v>56330.00754757551</v>
       </c>
       <c r="F48">
-        <v>64942.44627946275</v>
+        <v>66354.23858988586</v>
       </c>
       <c r="G48">
         <v>473</v>
@@ -5479,37 +5479,37 @@
         <v>4688</v>
       </c>
       <c r="M48">
-        <v>13425.98162160451</v>
+        <v>13717.85078729156</v>
       </c>
       <c r="N48">
-        <v>-8737.981621604506</v>
+        <v>-9029.85078729156</v>
       </c>
       <c r="O48">
-        <v>-1092.247702700563</v>
+        <v>-1128.731348411445</v>
       </c>
       <c r="P48">
-        <v>-7645.733918903942</v>
+        <v>-7901.119438880115</v>
       </c>
       <c r="Q48">
-        <v>-6727.733918903942</v>
+        <v>-6983.119438880115</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1482949233233555</v>
+        <v>0.1502287898011546</v>
       </c>
       <c r="T48">
-        <v>1.997816829272657</v>
+        <v>2.035511486428745</v>
       </c>
       <c r="U48">
         <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.04364671548909573</v>
+        <v>0.04271806196805114</v>
       </c>
       <c r="W48">
-        <v>0.1977132423738862</v>
+        <v>0.1979052290608787</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3491737239127658</v>
+        <v>0.3417444957444091</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5525,22 +5525,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.172636716253225</v>
+        <v>0.1742460824198503</v>
       </c>
       <c r="C49">
-        <v>-3166.926908764348</v>
+        <v>-5364.498664393752</v>
       </c>
       <c r="D49">
-        <v>62714.31168112151</v>
+        <v>61928.53223591521</v>
       </c>
       <c r="E49">
-        <v>56330.00754757551</v>
+        <v>57741.79985799862</v>
       </c>
       <c r="F49">
-        <v>66354.23858988586</v>
+        <v>67766.03090030896</v>
       </c>
       <c r="G49">
         <v>473</v>
@@ -5561,37 +5561,37 @@
         <v>4688</v>
       </c>
       <c r="M49">
-        <v>13717.85078729156</v>
+        <v>14009.71995297861</v>
       </c>
       <c r="N49">
-        <v>-9029.85078729156</v>
+        <v>-9321.719952978614</v>
       </c>
       <c r="O49">
-        <v>-1128.731348411445</v>
+        <v>-1165.214994122327</v>
       </c>
       <c r="P49">
-        <v>-7901.119438880115</v>
+        <v>-8156.504958856287</v>
       </c>
       <c r="Q49">
-        <v>-6983.119438880115</v>
+        <v>-7238.504958856287</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1502287898011546</v>
+        <v>0.1522370357588692</v>
       </c>
       <c r="T49">
-        <v>2.035511486428745</v>
+        <v>2.074655938090836</v>
       </c>
       <c r="U49">
         <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.04271806196805114</v>
+        <v>0.04182810234371674</v>
       </c>
       <c r="W49">
-        <v>0.1979052290608787</v>
+        <v>0.1980892163025799</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3417444957444091</v>
+        <v>0.3346248187497339</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5607,22 +5607,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1742460824198503</v>
+        <v>0.1758554485864756</v>
       </c>
       <c r="C50">
-        <v>-5364.498664393737</v>
+        <v>-7542.623224733914</v>
       </c>
       <c r="D50">
-        <v>61928.53223591523</v>
+        <v>61162.19998599815</v>
       </c>
       <c r="E50">
-        <v>57741.79985799862</v>
+        <v>59153.59216842172</v>
       </c>
       <c r="F50">
-        <v>67766.03090030896</v>
+        <v>69177.82321073207</v>
       </c>
       <c r="G50">
         <v>473</v>
@@ -5643,37 +5643,37 @@
         <v>4688</v>
       </c>
       <c r="M50">
-        <v>14009.71995297861</v>
+        <v>14301.58911866567</v>
       </c>
       <c r="N50">
-        <v>-9321.719952978614</v>
+        <v>-9613.589118665668</v>
       </c>
       <c r="O50">
-        <v>-1165.214994122327</v>
+        <v>-1201.698639833209</v>
       </c>
       <c r="P50">
-        <v>-8156.504958856287</v>
+        <v>-8411.89047883246</v>
       </c>
       <c r="Q50">
-        <v>-7238.504958856287</v>
+        <v>-7493.89047883246</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1522370357588692</v>
+        <v>0.1543240364600234</v>
       </c>
       <c r="T50">
-        <v>2.074655938090836</v>
+        <v>2.115335466288696</v>
       </c>
       <c r="U50">
         <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.04182810234371674</v>
+        <v>0.04097446760200824</v>
       </c>
       <c r="W50">
-        <v>0.1980892163025799</v>
+        <v>0.1982656938609463</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3346248187497339</v>
+        <v>0.3277957408160659</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1758554485864756</v>
+        <v>0.177464814753101</v>
       </c>
       <c r="C51">
-        <v>-7542.623224733914</v>
+        <v>-9702.013711013045</v>
       </c>
       <c r="D51">
-        <v>61162.19998599815</v>
+        <v>60414.60181014212</v>
       </c>
       <c r="E51">
-        <v>59153.59216842172</v>
+        <v>60565.38447884482</v>
       </c>
       <c r="F51">
-        <v>69177.82321073207</v>
+        <v>70589.61552115517</v>
       </c>
       <c r="G51">
         <v>473</v>
@@ -5725,37 +5725,37 @@
         <v>4688</v>
       </c>
       <c r="M51">
-        <v>14301.58911866567</v>
+        <v>14593.45828435272</v>
       </c>
       <c r="N51">
-        <v>-9613.589118665668</v>
+        <v>-9905.458284352722</v>
       </c>
       <c r="O51">
-        <v>-1201.698639833209</v>
+        <v>-1238.18228554409</v>
       </c>
       <c r="P51">
-        <v>-8411.89047883246</v>
+        <v>-8667.275998808633</v>
       </c>
       <c r="Q51">
-        <v>-7493.89047883246</v>
+        <v>-7749.275998808633</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1543240364600234</v>
+        <v>0.1564945171892239</v>
       </c>
       <c r="T51">
-        <v>2.115335466288696</v>
+        <v>2.15764217561447</v>
       </c>
       <c r="U51">
         <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.04097446760200824</v>
+        <v>0.04015497824996807</v>
       </c>
       <c r="W51">
-        <v>0.1982656938609463</v>
+        <v>0.1984351123169781</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3277957408160659</v>
+        <v>0.3212398259997447</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5771,22 +5771,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.177464814753101</v>
+        <v>0.1790741809197263</v>
       </c>
       <c r="C52">
-        <v>-9702.013711013045</v>
+        <v>-11843.34879898244</v>
       </c>
       <c r="D52">
-        <v>60414.60181014212</v>
+        <v>59685.05903259583</v>
       </c>
       <c r="E52">
-        <v>60565.38447884482</v>
+        <v>61977.17678926792</v>
       </c>
       <c r="F52">
-        <v>70589.61552115517</v>
+        <v>72001.40783157827</v>
       </c>
       <c r="G52">
         <v>473</v>
@@ -5807,37 +5807,37 @@
         <v>4688</v>
       </c>
       <c r="M52">
-        <v>14593.45828435272</v>
+        <v>14885.32745003978</v>
       </c>
       <c r="N52">
-        <v>-9905.458284352722</v>
+        <v>-10197.32745003978</v>
       </c>
       <c r="O52">
-        <v>-1238.18228554409</v>
+        <v>-1274.665931254972</v>
       </c>
       <c r="P52">
-        <v>-8667.275998808633</v>
+        <v>-8922.661518784804</v>
       </c>
       <c r="Q52">
-        <v>-7749.275998808633</v>
+        <v>-8004.661518784804</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1564945171892239</v>
+        <v>0.1587535889685958</v>
       </c>
       <c r="T52">
-        <v>2.15764217561447</v>
+        <v>2.20167568940252</v>
       </c>
       <c r="U52">
         <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.04015497824996807</v>
+        <v>0.03936762573526282</v>
       </c>
       <c r="W52">
-        <v>0.1984351123169781</v>
+        <v>0.1985978869119889</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3212398259997447</v>
+        <v>0.3149410058821026</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5853,22 +5853,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1790741809197263</v>
+        <v>0.1806835470863516</v>
       </c>
       <c r="C53">
-        <v>-11843.34879898244</v>
+        <v>-13967.27477385166</v>
       </c>
       <c r="D53">
-        <v>59685.05903259583</v>
+        <v>58972.92536814971</v>
       </c>
       <c r="E53">
-        <v>61977.17678926792</v>
+        <v>63388.96909969102</v>
       </c>
       <c r="F53">
-        <v>72001.40783157827</v>
+        <v>73413.20014200137</v>
       </c>
       <c r="G53">
         <v>473</v>
@@ -5889,37 +5889,37 @@
         <v>4688</v>
       </c>
       <c r="M53">
-        <v>14885.32745003978</v>
+        <v>15177.19661572683</v>
       </c>
       <c r="N53">
-        <v>-10197.32745003978</v>
+        <v>-10489.19661572683</v>
       </c>
       <c r="O53">
-        <v>-1274.665931254972</v>
+        <v>-1311.149576965854</v>
       </c>
       <c r="P53">
-        <v>-8922.661518784804</v>
+        <v>-9178.047038760977</v>
       </c>
       <c r="Q53">
-        <v>-8004.661518784804</v>
+        <v>-8260.047038760977</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1587535889685958</v>
+        <v>0.1611067887387749</v>
       </c>
       <c r="T53">
-        <v>2.20167568940252</v>
+        <v>2.247543932931739</v>
       </c>
       <c r="U53">
         <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.03936762573526282</v>
+        <v>0.03861055600958469</v>
       </c>
       <c r="W53">
-        <v>0.1985978869119889</v>
+        <v>0.1987544009456533</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3149410058821026</v>
+        <v>0.3088844480766775</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5935,22 +5935,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1806835470863516</v>
+        <v>0.182292913252977</v>
       </c>
       <c r="C54">
-        <v>-13967.27477385166</v>
+        <v>-16074.40743984705</v>
       </c>
       <c r="D54">
-        <v>58972.92536814971</v>
+        <v>58277.58501257743</v>
       </c>
       <c r="E54">
-        <v>63388.96909969102</v>
+        <v>64800.76141011414</v>
       </c>
       <c r="F54">
-        <v>73413.20014200137</v>
+        <v>74824.99245242449</v>
       </c>
       <c r="G54">
         <v>473</v>
@@ -5971,37 +5971,37 @@
         <v>4688</v>
       </c>
       <c r="M54">
-        <v>15177.19661572683</v>
+        <v>15469.06578141389</v>
       </c>
       <c r="N54">
-        <v>-10489.19661572683</v>
+        <v>-10781.06578141389</v>
       </c>
       <c r="O54">
-        <v>-1311.149576965854</v>
+        <v>-1347.633222676736</v>
       </c>
       <c r="P54">
-        <v>-9178.047038760977</v>
+        <v>-9433.432558737153</v>
       </c>
       <c r="Q54">
-        <v>-8260.047038760977</v>
+        <v>-8515.432558737153</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1611067887387749</v>
+        <v>0.1635601246693871</v>
       </c>
       <c r="T54">
-        <v>2.247543932931739</v>
+        <v>2.295364016611138</v>
       </c>
       <c r="U54">
         <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.03861055600958469</v>
+        <v>0.03788205495280007</v>
       </c>
       <c r="W54">
-        <v>0.1987544009456533</v>
+        <v>0.198905008789368</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3088844480766775</v>
+        <v>0.3030564396224005</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6017,22 +6017,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.182292913252977</v>
+        <v>0.1839022794196024</v>
       </c>
       <c r="C55">
-        <v>-16074.40743984705</v>
+        <v>-18165.33389625271</v>
       </c>
       <c r="D55">
-        <v>58277.58501257743</v>
+        <v>57598.45086659487</v>
       </c>
       <c r="E55">
-        <v>64800.76141011414</v>
+        <v>66212.55372053724</v>
       </c>
       <c r="F55">
-        <v>74824.99245242449</v>
+        <v>76236.78476284759</v>
       </c>
       <c r="G55">
         <v>473</v>
@@ -6053,37 +6053,37 @@
         <v>4688</v>
       </c>
       <c r="M55">
-        <v>15469.06578141389</v>
+        <v>15760.93494710094</v>
       </c>
       <c r="N55">
-        <v>-10781.06578141389</v>
+        <v>-11072.93494710094</v>
       </c>
       <c r="O55">
-        <v>-1347.633222676736</v>
+        <v>-1384.116868387618</v>
       </c>
       <c r="P55">
-        <v>-9433.432558737153</v>
+        <v>-9688.818078713324</v>
       </c>
       <c r="Q55">
-        <v>-8515.432558737153</v>
+        <v>-8770.818078713324</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1635601246693871</v>
+        <v>0.1661201273795912</v>
       </c>
       <c r="T55">
-        <v>2.295364016611138</v>
+        <v>2.345263234363554</v>
       </c>
       <c r="U55">
         <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.03788205495280007</v>
+        <v>0.03718053541663711</v>
       </c>
       <c r="W55">
-        <v>0.198905008789368</v>
+        <v>0.199050038564797</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3030564396224005</v>
+        <v>0.2974442833330968</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1839022794196024</v>
+        <v>0.1855116455862277</v>
       </c>
       <c r="C56">
-        <v>-18165.33389625271</v>
+        <v>-20240.61419070016</v>
       </c>
       <c r="D56">
-        <v>57598.45086659487</v>
+        <v>56934.96288257053</v>
       </c>
       <c r="E56">
-        <v>66212.55372053724</v>
+        <v>67624.34603096034</v>
       </c>
       <c r="F56">
-        <v>76236.78476284759</v>
+        <v>77648.57707327069</v>
       </c>
       <c r="G56">
         <v>473</v>
@@ -6135,37 +6135,37 @@
         <v>4688</v>
       </c>
       <c r="M56">
-        <v>15760.93494710094</v>
+        <v>16052.804112788</v>
       </c>
       <c r="N56">
-        <v>-11072.93494710094</v>
+        <v>-11364.804112788</v>
       </c>
       <c r="O56">
-        <v>-1384.116868387618</v>
+        <v>-1420.600514098499</v>
       </c>
       <c r="P56">
-        <v>-9688.818078713324</v>
+        <v>-9944.203598689495</v>
       </c>
       <c r="Q56">
-        <v>-8770.818078713324</v>
+        <v>-9026.203598689495</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1661201273795912</v>
+        <v>0.1687939079880266</v>
       </c>
       <c r="T56">
-        <v>2.345263234363554</v>
+        <v>2.397380195127189</v>
       </c>
       <c r="U56">
         <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.03718053541663711</v>
+        <v>0.03650452568178916</v>
       </c>
       <c r="W56">
-        <v>0.199050038564797</v>
+        <v>0.1991897945302104</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2974442833330968</v>
+        <v>0.2920362054543133</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6181,22 +6181,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1855116455862277</v>
+        <v>0.1871210117528531</v>
       </c>
       <c r="C57">
-        <v>-20240.61419070016</v>
+        <v>-22300.78285949187</v>
       </c>
       <c r="D57">
-        <v>56934.96288257053</v>
+        <v>56286.58652420192</v>
       </c>
       <c r="E57">
-        <v>67624.34603096034</v>
+        <v>69036.13834138344</v>
       </c>
       <c r="F57">
-        <v>77648.57707327069</v>
+        <v>79060.36938369379</v>
       </c>
       <c r="G57">
         <v>473</v>
@@ -6217,37 +6217,37 @@
         <v>4688</v>
       </c>
       <c r="M57">
-        <v>16052.804112788</v>
+        <v>16344.67327847505</v>
       </c>
       <c r="N57">
-        <v>-11364.804112788</v>
+        <v>-11656.67327847505</v>
       </c>
       <c r="O57">
-        <v>-1420.600514098499</v>
+        <v>-1457.084159809381</v>
       </c>
       <c r="P57">
-        <v>-9944.203598689495</v>
+        <v>-10199.58911866567</v>
       </c>
       <c r="Q57">
-        <v>-9026.203598689495</v>
+        <v>-9281.589118665668</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1687939079880266</v>
+        <v>0.1715892240786636</v>
       </c>
       <c r="T57">
-        <v>2.397380195127189</v>
+        <v>2.451866108652807</v>
       </c>
       <c r="U57">
         <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.03650452568178916</v>
+        <v>0.03585265915175721</v>
       </c>
       <c r="W57">
-        <v>0.1991897945302104</v>
+        <v>0.1993245592111448</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2920362054543133</v>
+        <v>0.2868212732140577</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6263,22 +6263,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1871210117528531</v>
+        <v>0.1887303779194784</v>
       </c>
       <c r="C58">
-        <v>-22300.78285949187</v>
+        <v>-24346.35036386228</v>
       </c>
       <c r="D58">
-        <v>56286.58652420192</v>
+        <v>55652.81133025463</v>
       </c>
       <c r="E58">
-        <v>69036.13834138344</v>
+        <v>70447.93065180656</v>
       </c>
       <c r="F58">
-        <v>79060.36938369379</v>
+        <v>80472.1616941169</v>
       </c>
       <c r="G58">
         <v>473</v>
@@ -6299,37 +6299,37 @@
         <v>4688</v>
       </c>
       <c r="M58">
-        <v>16344.67327847505</v>
+        <v>16636.54244416211</v>
       </c>
       <c r="N58">
-        <v>-11656.67327847505</v>
+        <v>-11948.54244416211</v>
       </c>
       <c r="O58">
-        <v>-1457.084159809381</v>
+        <v>-1493.567805520263</v>
       </c>
       <c r="P58">
-        <v>-10199.58911866567</v>
+        <v>-10454.97463864184</v>
       </c>
       <c r="Q58">
-        <v>-9281.589118665668</v>
+        <v>-9536.974638641845</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1715892240786636</v>
+        <v>0.1745145548711906</v>
       </c>
       <c r="T58">
-        <v>2.451866108652807</v>
+        <v>2.5088862507145</v>
       </c>
       <c r="U58">
         <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.03585265915175721</v>
+        <v>0.03522366513155094</v>
       </c>
       <c r="W58">
-        <v>0.1993245592111448</v>
+        <v>0.1994545953067832</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2868212732140577</v>
+        <v>0.2817893210524075</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1887303779194784</v>
+        <v>0.1903397440861037</v>
       </c>
       <c r="C59">
-        <v>-24346.35036386228</v>
+        <v>-26377.80443028753</v>
       </c>
       <c r="D59">
-        <v>55652.81133025463</v>
+        <v>55033.14957425248</v>
       </c>
       <c r="E59">
-        <v>70447.93065180656</v>
+        <v>71859.72296222966</v>
       </c>
       <c r="F59">
-        <v>80472.1616941169</v>
+        <v>81883.95400454001</v>
       </c>
       <c r="G59">
         <v>473</v>
@@ -6381,37 +6381,37 @@
         <v>4688</v>
       </c>
       <c r="M59">
-        <v>16636.54244416211</v>
+        <v>16928.41160984916</v>
       </c>
       <c r="N59">
-        <v>-11948.54244416211</v>
+        <v>-12240.41160984916</v>
       </c>
       <c r="O59">
-        <v>-1493.567805520263</v>
+        <v>-1530.051451231145</v>
       </c>
       <c r="P59">
-        <v>-10454.97463864184</v>
+        <v>-10710.36015861802</v>
       </c>
       <c r="Q59">
-        <v>-9536.974638641845</v>
+        <v>-9792.360158618016</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1745145548711906</v>
+        <v>0.1775791871300285</v>
       </c>
       <c r="T59">
-        <v>2.5088862507145</v>
+        <v>2.568621637636274</v>
       </c>
       <c r="U59">
         <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.03522366513155094</v>
+        <v>0.0346163605603173</v>
       </c>
       <c r="W59">
-        <v>0.1994545953067832</v>
+        <v>0.1995801473991237</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2817893210524075</v>
+        <v>0.2769308844825384</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6427,22 +6427,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1903397440861037</v>
+        <v>0.191949110252729</v>
       </c>
       <c r="C60">
-        <v>-26377.80443028748</v>
+        <v>-28395.61130223941</v>
       </c>
       <c r="D60">
-        <v>55033.14957425251</v>
+        <v>54427.13501272369</v>
       </c>
       <c r="E60">
-        <v>71859.72296222964</v>
+        <v>73271.51527265274</v>
       </c>
       <c r="F60">
-        <v>81883.95400453999</v>
+        <v>83295.74631496309</v>
       </c>
       <c r="G60">
         <v>473</v>
@@ -6463,37 +6463,37 @@
         <v>4688</v>
       </c>
       <c r="M60">
-        <v>16928.41160984916</v>
+        <v>17220.28077553621</v>
       </c>
       <c r="N60">
-        <v>-12240.41160984916</v>
+        <v>-12532.28077553621</v>
       </c>
       <c r="O60">
-        <v>-1530.051451231145</v>
+        <v>-1566.535096942026</v>
       </c>
       <c r="P60">
-        <v>-10710.36015861801</v>
+        <v>-10965.74567859418</v>
       </c>
       <c r="Q60">
-        <v>-9792.360158618012</v>
+        <v>-10047.74567859418</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1775791871300284</v>
+        <v>0.180793313645395</v>
       </c>
       <c r="T60">
-        <v>2.568621637636273</v>
+        <v>2.631270945871304</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.03461636056031731</v>
+        <v>0.03402964258471871</v>
       </c>
       <c r="W60">
-        <v>0.1995801473991237</v>
+        <v>0.199701443488334</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2769308844825384</v>
+        <v>0.2722371406777496</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.191949110252729</v>
+        <v>0.1935584764193544</v>
       </c>
       <c r="C61">
-        <v>-28395.61130223941</v>
+        <v>-30400.2169101361</v>
       </c>
       <c r="D61">
-        <v>54427.13501272369</v>
+        <v>53834.32171525009</v>
       </c>
       <c r="E61">
-        <v>73271.51527265274</v>
+        <v>74683.30758307585</v>
       </c>
       <c r="F61">
-        <v>83295.74631496309</v>
+        <v>84707.53862538619</v>
       </c>
       <c r="G61">
         <v>473</v>
@@ -6545,37 +6545,37 @@
         <v>4688</v>
       </c>
       <c r="M61">
-        <v>17220.28077553621</v>
+        <v>17512.14994122327</v>
       </c>
       <c r="N61">
-        <v>-12532.28077553621</v>
+        <v>-12824.14994122327</v>
       </c>
       <c r="O61">
-        <v>-1566.535096942026</v>
+        <v>-1603.018742652908</v>
       </c>
       <c r="P61">
-        <v>-10965.74567859418</v>
+        <v>-11221.13119857036</v>
       </c>
       <c r="Q61">
-        <v>-10047.74567859418</v>
+        <v>-10303.13119857036</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.180793313645395</v>
+        <v>0.1841681464865299</v>
       </c>
       <c r="T61">
-        <v>2.631270945871304</v>
+        <v>2.697052719518087</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.03402964258471871</v>
+        <v>0.0334624818749734</v>
       </c>
       <c r="W61">
-        <v>0.199701443488334</v>
+        <v>0.1998186963745707</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2722371406777496</v>
+        <v>0.2676998549997872</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6591,22 +6591,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1935584764193544</v>
+        <v>0.1951678425859797</v>
       </c>
       <c r="C62">
-        <v>-30400.2169101361</v>
+        <v>-32392.04796565838</v>
       </c>
       <c r="D62">
-        <v>53834.32171525009</v>
+        <v>53254.28297015091</v>
       </c>
       <c r="E62">
-        <v>74683.30758307585</v>
+        <v>76095.09989349895</v>
       </c>
       <c r="F62">
-        <v>84707.53862538619</v>
+        <v>86119.3309358093</v>
       </c>
       <c r="G62">
         <v>473</v>
@@ -6627,37 +6627,37 @@
         <v>4688</v>
       </c>
       <c r="M62">
-        <v>17512.14994122327</v>
+        <v>17804.01910691032</v>
       </c>
       <c r="N62">
-        <v>-12824.14994122327</v>
+        <v>-13116.01910691032</v>
       </c>
       <c r="O62">
-        <v>-1603.018742652908</v>
+        <v>-1639.50238836379</v>
       </c>
       <c r="P62">
-        <v>-11221.13119857036</v>
+        <v>-11476.51671854653</v>
       </c>
       <c r="Q62">
-        <v>-10303.13119857036</v>
+        <v>-10558.51671854653</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1841681464865299</v>
+        <v>0.1877160476784922</v>
       </c>
       <c r="T62">
-        <v>2.697052719518087</v>
+        <v>2.766207917454448</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.0334624818749734</v>
+        <v>0.03291391659833449</v>
       </c>
       <c r="W62">
-        <v>0.1998186963745707</v>
+        <v>0.1999321049038816</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2676998549997872</v>
+        <v>0.263311332786676</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6673,22 +6673,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1951678425859797</v>
+        <v>0.1967772087526051</v>
       </c>
       <c r="C63">
-        <v>-32392.04796565838</v>
+        <v>-34371.51298607638</v>
       </c>
       <c r="D63">
-        <v>53254.28297015091</v>
+        <v>52686.61026015603</v>
       </c>
       <c r="E63">
-        <v>76095.09989349895</v>
+        <v>77506.89220392206</v>
       </c>
       <c r="F63">
-        <v>86119.3309358093</v>
+        <v>87531.12324623241</v>
       </c>
       <c r="G63">
         <v>473</v>
@@ -6709,37 +6709,37 @@
         <v>4688</v>
       </c>
       <c r="M63">
-        <v>17804.01910691032</v>
+        <v>18095.88827259738</v>
       </c>
       <c r="N63">
-        <v>-13116.01910691032</v>
+        <v>-13407.88827259738</v>
       </c>
       <c r="O63">
-        <v>-1639.50238836379</v>
+        <v>-1675.986034074672</v>
       </c>
       <c r="P63">
-        <v>-11476.51671854653</v>
+        <v>-11731.90223852271</v>
       </c>
       <c r="Q63">
-        <v>-10558.51671854653</v>
+        <v>-10813.90223852271</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1877160476784922</v>
+        <v>0.1914506805121367</v>
       </c>
       <c r="T63">
-        <v>2.766207917454448</v>
+        <v>2.839002862650618</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.03291391659833449</v>
+        <v>0.0323830469757807</v>
       </c>
       <c r="W63">
-        <v>0.1999321049038816</v>
+        <v>0.2000418550935373</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.263311332786676</v>
+        <v>0.2590643758062456</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6755,22 +6755,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1967772087526051</v>
+        <v>0.1983865749192304</v>
       </c>
       <c r="C64">
-        <v>-34371.51298607638</v>
+        <v>-36339.00325375263</v>
       </c>
       <c r="D64">
-        <v>52686.61026015603</v>
+        <v>52130.91230290289</v>
       </c>
       <c r="E64">
-        <v>77506.89220392206</v>
+        <v>78918.68451434516</v>
       </c>
       <c r="F64">
-        <v>87531.12324623241</v>
+        <v>88942.91555665551</v>
       </c>
       <c r="G64">
         <v>473</v>
@@ -6791,37 +6791,37 @@
         <v>4688</v>
       </c>
       <c r="M64">
-        <v>18095.88827259738</v>
+        <v>18387.75743828443</v>
       </c>
       <c r="N64">
-        <v>-13407.88827259738</v>
+        <v>-13699.75743828443</v>
       </c>
       <c r="O64">
-        <v>-1675.986034074672</v>
+        <v>-1712.469679785554</v>
       </c>
       <c r="P64">
-        <v>-11731.90223852271</v>
+        <v>-11987.28775849888</v>
       </c>
       <c r="Q64">
-        <v>-10813.90223852271</v>
+        <v>-11069.28775849888</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1914506805121367</v>
+        <v>0.1953871853908431</v>
       </c>
       <c r="T64">
-        <v>2.839002862650618</v>
+        <v>2.915732669749283</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.0323830469757807</v>
+        <v>0.03186903035711752</v>
       </c>
       <c r="W64">
-        <v>0.2000418550935373</v>
+        <v>0.200148121150188</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2590643758062456</v>
+        <v>0.2549522428569402</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6837,22 +6837,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1983865749192304</v>
+        <v>0.1999959410858557</v>
       </c>
       <c r="C65">
-        <v>-36339.00325375263</v>
+        <v>-38294.89371555892</v>
       </c>
       <c r="D65">
-        <v>52130.91230290289</v>
+        <v>51586.8141515197</v>
       </c>
       <c r="E65">
-        <v>78918.68451434516</v>
+        <v>80330.47682476827</v>
       </c>
       <c r="F65">
-        <v>88942.91555665551</v>
+        <v>90354.70786707861</v>
       </c>
       <c r="G65">
         <v>473</v>
@@ -6873,37 +6873,37 @@
         <v>4688</v>
       </c>
       <c r="M65">
-        <v>18387.75743828443</v>
+        <v>18679.62660397149</v>
       </c>
       <c r="N65">
-        <v>-13699.75743828443</v>
+        <v>-13991.62660397149</v>
       </c>
       <c r="O65">
-        <v>-1712.469679785554</v>
+        <v>-1748.953325496436</v>
       </c>
       <c r="P65">
-        <v>-11987.28775849888</v>
+        <v>-12242.67327847505</v>
       </c>
       <c r="Q65">
-        <v>-11069.28775849888</v>
+        <v>-11324.67327847505</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1953871853908431</v>
+        <v>0.1995423849850332</v>
       </c>
       <c r="T65">
-        <v>2.915732669749283</v>
+        <v>2.996725243908986</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.03186903035711752</v>
+        <v>0.03137107675778756</v>
       </c>
       <c r="W65">
-        <v>0.200148121150188</v>
+        <v>0.2002510663925684</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2549522428569402</v>
+        <v>0.2509686140623004</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1999959410858557</v>
+        <v>0.2016053072524811</v>
       </c>
       <c r="C66">
-        <v>-38294.89371555892</v>
+        <v>-40239.54382655044</v>
       </c>
       <c r="D66">
-        <v>51586.8141515197</v>
+        <v>51053.95635095127</v>
       </c>
       <c r="E66">
-        <v>80330.47682476827</v>
+        <v>81742.26913519137</v>
       </c>
       <c r="F66">
-        <v>90354.70786707861</v>
+        <v>91766.50017750172</v>
       </c>
       <c r="G66">
         <v>473</v>
@@ -6955,37 +6955,37 @@
         <v>4688</v>
       </c>
       <c r="M66">
-        <v>18679.62660397149</v>
+        <v>18971.49576965854</v>
       </c>
       <c r="N66">
-        <v>-13991.62660397149</v>
+        <v>-14283.49576965854</v>
       </c>
       <c r="O66">
-        <v>-1748.953325496436</v>
+        <v>-1785.436971207318</v>
       </c>
       <c r="P66">
-        <v>-12242.67327847505</v>
+        <v>-12498.05879845122</v>
       </c>
       <c r="Q66">
-        <v>-11324.67327847505</v>
+        <v>-11580.05879845122</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1995423849850332</v>
+        <v>0.2039350245560342</v>
       </c>
       <c r="T66">
-        <v>2.996725243908986</v>
+        <v>3.082345965163529</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.03137107675778756</v>
+        <v>0.03088844480766775</v>
       </c>
       <c r="W66">
-        <v>0.2002510663925684</v>
+        <v>0.2003508440890295</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2509686140623004</v>
+        <v>0.247107558461342</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7001,22 +7001,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2016053072524811</v>
+        <v>0.2032146734191064</v>
       </c>
       <c r="C67">
-        <v>-40239.54382655044</v>
+        <v>-42173.29834188714</v>
       </c>
       <c r="D67">
-        <v>51053.95635095127</v>
+        <v>50531.99414603769</v>
       </c>
       <c r="E67">
-        <v>81742.26913519137</v>
+        <v>83154.06144561448</v>
       </c>
       <c r="F67">
-        <v>91766.50017750172</v>
+        <v>93178.29248792483</v>
       </c>
       <c r="G67">
         <v>473</v>
@@ -7037,37 +7037,37 @@
         <v>4688</v>
       </c>
       <c r="M67">
-        <v>18971.49576965854</v>
+        <v>19263.36493534559</v>
       </c>
       <c r="N67">
-        <v>-14283.49576965854</v>
+        <v>-14575.36493534559</v>
       </c>
       <c r="O67">
-        <v>-1785.436971207318</v>
+        <v>-1821.920616918199</v>
       </c>
       <c r="P67">
-        <v>-12498.05879845122</v>
+        <v>-12753.4443184274</v>
       </c>
       <c r="Q67">
-        <v>-11580.05879845122</v>
+        <v>-11835.4443184274</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2039350245560342</v>
+        <v>0.2085860546900352</v>
       </c>
       <c r="T67">
-        <v>3.082345965163529</v>
+        <v>3.173003199433044</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.03088844480766775</v>
+        <v>0.03042043806815763</v>
       </c>
       <c r="W67">
-        <v>0.2003508440890295</v>
+        <v>0.200447598218931</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.247107558461342</v>
+        <v>0.243363504545261</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7083,22 +7083,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2032146734191064</v>
+        <v>0.2048240395857318</v>
       </c>
       <c r="C68">
-        <v>-42173.29834188714</v>
+        <v>-44096.48806066813</v>
       </c>
       <c r="D68">
-        <v>50531.99414603769</v>
+        <v>50020.59673767981</v>
       </c>
       <c r="E68">
-        <v>83154.06144561448</v>
+        <v>84565.85375603758</v>
       </c>
       <c r="F68">
-        <v>93178.29248792483</v>
+        <v>94590.08479834793</v>
       </c>
       <c r="G68">
         <v>473</v>
@@ -7119,37 +7119,37 @@
         <v>4688</v>
       </c>
       <c r="M68">
-        <v>19263.36493534559</v>
+        <v>19555.23410103265</v>
       </c>
       <c r="N68">
-        <v>-14575.36493534559</v>
+        <v>-14867.23410103265</v>
       </c>
       <c r="O68">
-        <v>-1821.920616918199</v>
+        <v>-1858.404262629081</v>
       </c>
       <c r="P68">
-        <v>-12753.4443184274</v>
+        <v>-13008.82983840357</v>
       </c>
       <c r="Q68">
-        <v>-11835.4443184274</v>
+        <v>-12090.82983840357</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2085860546900352</v>
+        <v>0.2135189654382181</v>
       </c>
       <c r="T68">
-        <v>3.173003199433044</v>
+        <v>3.269154811537076</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.03042043806815763</v>
+        <v>0.02996640167908065</v>
       </c>
       <c r="W68">
-        <v>0.200447598218931</v>
+        <v>0.2005414641658505</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.243363504545261</v>
+        <v>0.2397312134326453</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2048240395857318</v>
+        <v>0.2064334057523571</v>
       </c>
       <c r="C69">
-        <v>-44096.48806066813</v>
+        <v>-46009.43052505196</v>
       </c>
       <c r="D69">
-        <v>50020.59673767981</v>
+        <v>49519.44658371907</v>
       </c>
       <c r="E69">
-        <v>84565.85375603758</v>
+        <v>85977.64606646069</v>
       </c>
       <c r="F69">
-        <v>94590.08479834793</v>
+        <v>96001.87710877103</v>
       </c>
       <c r="G69">
         <v>473</v>
@@ -7201,37 +7201,37 @@
         <v>4688</v>
       </c>
       <c r="M69">
-        <v>19555.23410103265</v>
+        <v>19847.1032667197</v>
       </c>
       <c r="N69">
-        <v>-14867.23410103265</v>
+        <v>-15159.1032667197</v>
       </c>
       <c r="O69">
-        <v>-1858.404262629081</v>
+        <v>-1894.887908339963</v>
       </c>
       <c r="P69">
-        <v>-13008.82983840357</v>
+        <v>-13264.21535837974</v>
       </c>
       <c r="Q69">
-        <v>-12090.82983840357</v>
+        <v>-12346.21535837974</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2135189654382181</v>
+        <v>0.2187601831081624</v>
       </c>
       <c r="T69">
-        <v>3.269154811537076</v>
+        <v>3.371315899397609</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.02996640167908065</v>
+        <v>0.02952571930144711</v>
       </c>
       <c r="W69">
-        <v>0.2005414641658505</v>
+        <v>0.2006325693496253</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2397312134326453</v>
+        <v>0.2362057544115769</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7247,22 +7247,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2064334057523571</v>
+        <v>0.2080427719189825</v>
       </c>
       <c r="C70">
-        <v>-46009.43052505196</v>
+        <v>-47912.43067776738</v>
       </c>
       <c r="D70">
-        <v>49519.44658371907</v>
+        <v>49028.23874142676</v>
       </c>
       <c r="E70">
-        <v>85977.64606646069</v>
+        <v>87389.43837688379</v>
       </c>
       <c r="F70">
-        <v>96001.87710877103</v>
+        <v>97413.66941919414</v>
       </c>
       <c r="G70">
         <v>473</v>
@@ -7283,37 +7283,37 @@
         <v>4688</v>
       </c>
       <c r="M70">
-        <v>19847.1032667197</v>
+        <v>20138.97243240676</v>
       </c>
       <c r="N70">
-        <v>-15159.1032667197</v>
+        <v>-15450.97243240676</v>
       </c>
       <c r="O70">
-        <v>-1894.887908339963</v>
+        <v>-1931.371554050845</v>
       </c>
       <c r="P70">
-        <v>-13264.21535837974</v>
+        <v>-13519.60087835591</v>
       </c>
       <c r="Q70">
-        <v>-12346.21535837974</v>
+        <v>-12601.60087835591</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2187601831081624</v>
+        <v>0.224339543853587</v>
       </c>
       <c r="T70">
-        <v>3.371315899397609</v>
+        <v>3.48006802518463</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.02952571930144711</v>
+        <v>0.02909781032606382</v>
       </c>
       <c r="W70">
-        <v>0.2006325693496253</v>
+        <v>0.2007210338034355</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2362057544115769</v>
+        <v>0.2327824826085105</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7329,22 +7329,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2080427719189825</v>
+        <v>0.2096521380856078</v>
       </c>
       <c r="C71">
-        <v>-47912.43067776738</v>
+        <v>-49805.78148087525</v>
       </c>
       <c r="D71">
-        <v>49028.23874142676</v>
+        <v>48546.68024874198</v>
       </c>
       <c r="E71">
-        <v>87389.43837688379</v>
+        <v>88801.23068730689</v>
       </c>
       <c r="F71">
-        <v>97413.66941919414</v>
+        <v>98825.46172961724</v>
       </c>
       <c r="G71">
         <v>473</v>
@@ -7365,37 +7365,37 @@
         <v>4688</v>
       </c>
       <c r="M71">
-        <v>20138.97243240676</v>
+        <v>20430.84159809381</v>
       </c>
       <c r="N71">
-        <v>-15450.97243240676</v>
+        <v>-15742.84159809381</v>
       </c>
       <c r="O71">
-        <v>-1931.371554050845</v>
+        <v>-1967.855199761726</v>
       </c>
       <c r="P71">
-        <v>-13519.60087835591</v>
+        <v>-13774.98639833208</v>
       </c>
       <c r="Q71">
-        <v>-12601.60087835591</v>
+        <v>-12856.98639833208</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.224339543853587</v>
+        <v>0.2302908619820399</v>
       </c>
       <c r="T71">
-        <v>3.48006802518463</v>
+        <v>3.596070292690784</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.02909781032606382</v>
+        <v>0.02868212732140577</v>
       </c>
       <c r="W71">
-        <v>0.2007210338034355</v>
+        <v>0.2008069707014226</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2327824826085105</v>
+        <v>0.2294570185712461</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7411,22 +7411,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2096521380856078</v>
+        <v>0.2112615042522332</v>
       </c>
       <c r="C72">
-        <v>-49805.78148087525</v>
+        <v>-51689.76449842021</v>
       </c>
       <c r="D72">
-        <v>48546.68024874198</v>
+        <v>48074.48954162014</v>
       </c>
       <c r="E72">
-        <v>88801.23068730689</v>
+        <v>90213.02299773</v>
       </c>
       <c r="F72">
-        <v>98825.46172961724</v>
+        <v>100237.2540400404</v>
       </c>
       <c r="G72">
         <v>473</v>
@@ -7447,37 +7447,37 @@
         <v>4688</v>
       </c>
       <c r="M72">
-        <v>20430.84159809381</v>
+        <v>20722.71076378087</v>
       </c>
       <c r="N72">
-        <v>-15742.84159809381</v>
+        <v>-16034.71076378087</v>
       </c>
       <c r="O72">
-        <v>-1967.855199761726</v>
+        <v>-2004.338845472609</v>
       </c>
       <c r="P72">
-        <v>-13774.98639833208</v>
+        <v>-14030.37191830826</v>
       </c>
       <c r="Q72">
-        <v>-12856.98639833208</v>
+        <v>-13112.37191830826</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2302908619820399</v>
+        <v>0.2366526158434896</v>
       </c>
       <c r="T72">
-        <v>3.596070292690784</v>
+        <v>3.720072716576673</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.02868212732140577</v>
+        <v>0.02827815369716061</v>
       </c>
       <c r="W72">
-        <v>0.2008069707014226</v>
+        <v>0.20089048684172</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2294570185712461</v>
+        <v>0.2262252295772849</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7493,22 +7493,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2112615042522331</v>
+        <v>0.2128708704188585</v>
       </c>
       <c r="C73">
-        <v>-51689.76449842016</v>
+        <v>-53564.65044540659</v>
       </c>
       <c r="D73">
-        <v>48074.48954162018</v>
+        <v>47611.39590505685</v>
       </c>
       <c r="E73">
-        <v>90213.02299772999</v>
+        <v>91624.81530815309</v>
       </c>
       <c r="F73">
-        <v>100237.2540400403</v>
+        <v>101649.0463504634</v>
       </c>
       <c r="G73">
         <v>473</v>
@@ -7529,37 +7529,37 @@
         <v>4688</v>
       </c>
       <c r="M73">
-        <v>20722.71076378087</v>
+        <v>21014.57992946792</v>
       </c>
       <c r="N73">
-        <v>-16034.71076378087</v>
+        <v>-16326.57992946792</v>
       </c>
       <c r="O73">
-        <v>-2004.338845472608</v>
+        <v>-2040.82249118349</v>
       </c>
       <c r="P73">
-        <v>-14030.37191830826</v>
+        <v>-14285.75743828443</v>
       </c>
       <c r="Q73">
-        <v>-13112.37191830826</v>
+        <v>-13367.75743828443</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2366526158434895</v>
+        <v>0.2434687806950427</v>
       </c>
       <c r="T73">
-        <v>3.720072716576671</v>
+        <v>3.85293245645441</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.02827815369716062</v>
+        <v>0.02788540156247783</v>
       </c>
       <c r="W73">
-        <v>0.20089048684172</v>
+        <v>0.2009716830892313</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.226225229577285</v>
+        <v>0.2230832124998227</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7575,22 +7575,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2128708704188585</v>
+        <v>0.2144802365854838</v>
       </c>
       <c r="C74">
-        <v>-53564.65044540659</v>
+        <v>-55430.69970534833</v>
       </c>
       <c r="D74">
-        <v>47611.39590505685</v>
+        <v>47157.13895553821</v>
       </c>
       <c r="E74">
-        <v>91624.81530815309</v>
+        <v>93036.60761857619</v>
       </c>
       <c r="F74">
-        <v>101649.0463504634</v>
+        <v>103060.8386608865</v>
       </c>
       <c r="G74">
         <v>473</v>
@@ -7611,37 +7611,37 @@
         <v>4688</v>
       </c>
       <c r="M74">
-        <v>21014.57992946792</v>
+        <v>21306.44909515497</v>
       </c>
       <c r="N74">
-        <v>-16326.57992946792</v>
+        <v>-16618.44909515497</v>
       </c>
       <c r="O74">
-        <v>-2040.82249118349</v>
+        <v>-2077.306136894372</v>
       </c>
       <c r="P74">
-        <v>-14285.75743828443</v>
+        <v>-14541.1429582606</v>
       </c>
       <c r="Q74">
-        <v>-13367.75743828443</v>
+        <v>-13623.1429582606</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2434687806950427</v>
+        <v>0.2507898466467109</v>
       </c>
       <c r="T74">
-        <v>3.85293245645441</v>
+        <v>3.995633658545314</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.02788540156247783</v>
+        <v>0.02750340976025211</v>
       </c>
       <c r="W74">
-        <v>0.2009716830892313</v>
+        <v>0.2010506547820163</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2230832124998227</v>
+        <v>0.2200272780820168</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7657,22 +7657,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2144802365854838</v>
+        <v>0.2160896027521091</v>
       </c>
       <c r="C75">
-        <v>-55430.69970534833</v>
+        <v>-57288.16281847082</v>
       </c>
       <c r="D75">
-        <v>47157.13895553821</v>
+        <v>46711.46815283882</v>
       </c>
       <c r="E75">
-        <v>93036.60761857619</v>
+        <v>94448.39992899929</v>
       </c>
       <c r="F75">
-        <v>103060.8386608865</v>
+        <v>104472.6309713096</v>
       </c>
       <c r="G75">
         <v>473</v>
@@ -7693,37 +7693,37 @@
         <v>4688</v>
       </c>
       <c r="M75">
-        <v>21306.44909515497</v>
+        <v>21598.31826084203</v>
       </c>
       <c r="N75">
-        <v>-16618.44909515497</v>
+        <v>-16910.31826084203</v>
       </c>
       <c r="O75">
-        <v>-2077.306136894372</v>
+        <v>-2113.789782605254</v>
       </c>
       <c r="P75">
-        <v>-14541.1429582606</v>
+        <v>-14796.52847823677</v>
       </c>
       <c r="Q75">
-        <v>-13623.1429582606</v>
+        <v>-13878.52847823677</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2507898466467109</v>
+        <v>0.2586740715177382</v>
       </c>
       <c r="T75">
-        <v>3.995633658545314</v>
+        <v>4.149311876181672</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.02750340976025211</v>
+        <v>0.02713174206078924</v>
       </c>
       <c r="W75">
-        <v>0.2010506547820163</v>
+        <v>0.2011274921047259</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2200272780820168</v>
+        <v>0.2170539364863139</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2160896027521091</v>
+        <v>0.2176989689187345</v>
       </c>
       <c r="C76">
-        <v>-57288.16281847082</v>
+        <v>-59137.2809424892</v>
       </c>
       <c r="D76">
-        <v>46711.46815283882</v>
+        <v>46274.14233924354</v>
       </c>
       <c r="E76">
-        <v>94448.39992899929</v>
+        <v>95860.19223942239</v>
       </c>
       <c r="F76">
-        <v>104472.6309713096</v>
+        <v>105884.4232817327</v>
       </c>
       <c r="G76">
         <v>473</v>
@@ -7775,37 +7775,37 @@
         <v>4688</v>
       </c>
       <c r="M76">
-        <v>21598.31826084203</v>
+        <v>21890.18742652908</v>
       </c>
       <c r="N76">
-        <v>-16910.31826084203</v>
+        <v>-17202.18742652908</v>
       </c>
       <c r="O76">
-        <v>-2113.789782605254</v>
+        <v>-2150.273428316135</v>
       </c>
       <c r="P76">
-        <v>-14796.52847823677</v>
+        <v>-15051.91399821295</v>
       </c>
       <c r="Q76">
-        <v>-13878.52847823677</v>
+        <v>-14133.91399821295</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2586740715177382</v>
+        <v>0.2671890343784478</v>
       </c>
       <c r="T76">
-        <v>4.149311876181672</v>
+        <v>4.315284351228939</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.02713174206078924</v>
+        <v>0.02676998549997872</v>
       </c>
       <c r="W76">
-        <v>0.2011274921047259</v>
+        <v>0.2012022804321634</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2170539364863139</v>
+        <v>0.2141598839998298</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7821,22 +7821,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2176989689187345</v>
+        <v>0.2193083350853599</v>
       </c>
       <c r="C77">
-        <v>-59137.2809424892</v>
+        <v>-60978.28628774288</v>
       </c>
       <c r="D77">
-        <v>46274.14233924354</v>
+        <v>45844.92930441298</v>
       </c>
       <c r="E77">
-        <v>95860.19223942239</v>
+        <v>97271.98454984551</v>
       </c>
       <c r="F77">
-        <v>105884.4232817327</v>
+        <v>107296.2155921559</v>
       </c>
       <c r="G77">
         <v>473</v>
@@ -7857,37 +7857,37 @@
         <v>4688</v>
       </c>
       <c r="M77">
-        <v>21890.18742652908</v>
+        <v>22182.05659221614</v>
       </c>
       <c r="N77">
-        <v>-17202.18742652908</v>
+        <v>-17494.05659221614</v>
       </c>
       <c r="O77">
-        <v>-2150.273428316135</v>
+        <v>-2186.757074027018</v>
       </c>
       <c r="P77">
-        <v>-15051.91399821295</v>
+        <v>-15307.29951818912</v>
       </c>
       <c r="Q77">
-        <v>-14133.91399821295</v>
+        <v>-14389.29951818912</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2671890343784478</v>
+        <v>0.2764135774775498</v>
       </c>
       <c r="T77">
-        <v>4.315284351228939</v>
+        <v>4.495087865863479</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.02676998549997872</v>
+        <v>0.0264177488486632</v>
       </c>
       <c r="W77">
-        <v>0.2012022804321634</v>
+        <v>0.2012751006457209</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2141598839998298</v>
+        <v>0.2113419907893056</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7903,22 +7903,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2193083350853599</v>
+        <v>0.2209177012519852</v>
       </c>
       <c r="C78">
-        <v>-60978.28628774288</v>
+        <v>-62811.40252833615</v>
       </c>
       <c r="D78">
-        <v>45844.92930441298</v>
+        <v>45423.60537424281</v>
       </c>
       <c r="E78">
-        <v>97271.98454984551</v>
+        <v>98683.77686026861</v>
       </c>
       <c r="F78">
-        <v>107296.2155921559</v>
+        <v>108708.007902579</v>
       </c>
       <c r="G78">
         <v>473</v>
@@ -7939,37 +7939,37 @@
         <v>4688</v>
       </c>
       <c r="M78">
-        <v>22182.05659221614</v>
+        <v>22473.92575790319</v>
       </c>
       <c r="N78">
-        <v>-17494.05659221614</v>
+        <v>-17785.92575790319</v>
       </c>
       <c r="O78">
-        <v>-2186.757074027018</v>
+        <v>-2223.240719737899</v>
       </c>
       <c r="P78">
-        <v>-15307.29951818912</v>
+        <v>-15562.68503816529</v>
       </c>
       <c r="Q78">
-        <v>-14389.29951818912</v>
+        <v>-14644.68503816529</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2764135774775498</v>
+        <v>0.2864402547591824</v>
       </c>
       <c r="T78">
-        <v>4.495087865863479</v>
+        <v>4.690526468727109</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.0264177488486632</v>
+        <v>0.02607466120127797</v>
       </c>
       <c r="W78">
-        <v>0.2012751006457209</v>
+        <v>0.20134602942516</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2113419907893056</v>
+        <v>0.2085972896102237</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7985,22 +7985,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2209177012519852</v>
+        <v>0.2225270674186105</v>
       </c>
       <c r="C79">
-        <v>-62811.40252833615</v>
+        <v>-64636.84519081477</v>
       </c>
       <c r="D79">
-        <v>45423.60537424281</v>
+        <v>45009.95502218729</v>
       </c>
       <c r="E79">
-        <v>98683.77686026861</v>
+        <v>100095.5691706917</v>
       </c>
       <c r="F79">
-        <v>108708.007902579</v>
+        <v>110119.8002130021</v>
       </c>
       <c r="G79">
         <v>473</v>
@@ -8021,37 +8021,37 @@
         <v>4688</v>
       </c>
       <c r="M79">
-        <v>22473.92575790319</v>
+        <v>22765.79492359025</v>
       </c>
       <c r="N79">
-        <v>-17785.92575790319</v>
+        <v>-18077.79492359025</v>
       </c>
       <c r="O79">
-        <v>-2223.240719737899</v>
+        <v>-2259.724365448781</v>
       </c>
       <c r="P79">
-        <v>-15562.68503816529</v>
+        <v>-15818.07055814147</v>
       </c>
       <c r="Q79">
-        <v>-14644.68503816529</v>
+        <v>-14900.07055814147</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2864402547591824</v>
+        <v>0.2973784481573271</v>
       </c>
       <c r="T79">
-        <v>4.690526468727109</v>
+        <v>4.903732217305614</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.02607466120127797</v>
+        <v>0.02574037067305646</v>
       </c>
       <c r="W79">
-        <v>0.20134602942516</v>
+        <v>0.2014151395179469</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2085972896102237</v>
+        <v>0.2059229653844517</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8067,22 +8067,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2225270674186105</v>
+        <v>0.2241364335852359</v>
       </c>
       <c r="C80">
-        <v>-64636.84519081477</v>
+        <v>-66454.82202179695</v>
       </c>
       <c r="D80">
-        <v>45009.95502218729</v>
+        <v>44603.77050162821</v>
       </c>
       <c r="E80">
-        <v>100095.5691706917</v>
+        <v>101507.3614811148</v>
       </c>
       <c r="F80">
-        <v>110119.8002130021</v>
+        <v>111531.5925234252</v>
       </c>
       <c r="G80">
         <v>473</v>
@@ -8103,37 +8103,37 @@
         <v>4688</v>
       </c>
       <c r="M80">
-        <v>22765.79492359025</v>
+        <v>23057.6640892773</v>
       </c>
       <c r="N80">
-        <v>-18077.79492359025</v>
+        <v>-18369.6640892773</v>
       </c>
       <c r="O80">
-        <v>-2259.724365448781</v>
+        <v>-2296.208011159663</v>
       </c>
       <c r="P80">
-        <v>-15818.07055814147</v>
+        <v>-16073.45607811764</v>
       </c>
       <c r="Q80">
-        <v>-14900.07055814147</v>
+        <v>-15155.45607811764</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2973784481573271</v>
+        <v>0.309358374260057</v>
       </c>
       <c r="T80">
-        <v>4.903732217305614</v>
+        <v>5.137243275272548</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.02574037067305646</v>
+        <v>0.02541454319618233</v>
       </c>
       <c r="W80">
-        <v>0.2014151395179469</v>
+        <v>0.2014824999881315</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2059229653844517</v>
+        <v>0.2033163455694585</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2241364335852359</v>
+        <v>0.2257457997518612</v>
       </c>
       <c r="C81">
-        <v>-66454.82202179695</v>
+        <v>-68265.53333587688</v>
       </c>
       <c r="D81">
-        <v>44603.77050162821</v>
+        <v>44204.85149797139</v>
       </c>
       <c r="E81">
-        <v>101507.3614811148</v>
+        <v>102919.1537915379</v>
       </c>
       <c r="F81">
-        <v>111531.5925234252</v>
+        <v>112943.3848338483</v>
       </c>
       <c r="G81">
         <v>473</v>
@@ -8185,37 +8185,37 @@
         <v>4688</v>
       </c>
       <c r="M81">
-        <v>23057.6640892773</v>
+        <v>23349.53325496436</v>
       </c>
       <c r="N81">
-        <v>-18369.6640892773</v>
+        <v>-18661.53325496436</v>
       </c>
       <c r="O81">
-        <v>-2296.208011159663</v>
+        <v>-2332.691656870545</v>
       </c>
       <c r="P81">
-        <v>-16073.45607811764</v>
+        <v>-16328.84159809381</v>
       </c>
       <c r="Q81">
-        <v>-15155.45607811764</v>
+        <v>-15410.84159809381</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.309358374260057</v>
+        <v>0.3225362929730598</v>
       </c>
       <c r="T81">
-        <v>5.137243275272548</v>
+        <v>5.394105439036175</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.02541454319618233</v>
+        <v>0.02509686140623005</v>
       </c>
       <c r="W81">
-        <v>0.2014824999881315</v>
+        <v>0.2015481764465616</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2033163455694585</v>
+        <v>0.2007748912498404</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8231,22 +8231,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2257457997518612</v>
+        <v>0.2558693531517254</v>
       </c>
       <c r="C82">
-        <v>-68265.53333587688</v>
+        <v>-76016.21889585667</v>
       </c>
       <c r="D82">
-        <v>44204.85149797139</v>
+        <v>37865.95824841471</v>
       </c>
       <c r="E82">
-        <v>102919.1537915379</v>
+        <v>104330.946101961</v>
       </c>
       <c r="F82">
-        <v>112943.3848338483</v>
+        <v>114355.1771442714</v>
       </c>
       <c r="G82">
         <v>473</v>
@@ -8267,45 +8267,45 @@
         <v>4688</v>
       </c>
       <c r="M82">
-        <v>23349.53325496436</v>
+        <v>27643.83362070091</v>
       </c>
       <c r="N82">
-        <v>-18661.53325496436</v>
+        <v>-22955.83362070091</v>
       </c>
       <c r="O82">
-        <v>-2332.691656870545</v>
+        <v>-2869.479202587614</v>
       </c>
       <c r="P82">
-        <v>-16328.84159809381</v>
+        <v>-20086.3544181133</v>
       </c>
       <c r="Q82">
-        <v>-15410.84159809381</v>
+        <v>-19168.3544181133</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3225362929730598</v>
+        <v>0.3379655043571095</v>
       </c>
       <c r="T82">
-        <v>5.394105439036175</v>
+        <v>5.69484948728735</v>
       </c>
       <c r="U82">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V82">
-        <v>0.02509686140623005</v>
+        <v>0.02119821758589871</v>
       </c>
       <c r="W82">
-        <v>0.2015481764465616</v>
+        <v>0.2366122312640427</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.2007748912498404</v>
+        <v>0.1695857406871897</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2558693531517254</v>
+        <v>0.2578287193183507</v>
       </c>
       <c r="C83">
-        <v>-76016.21889585667</v>
+        <v>-77777.93209292811</v>
       </c>
       <c r="D83">
-        <v>37865.95824841471</v>
+        <v>37516.03736176637</v>
       </c>
       <c r="E83">
-        <v>104330.946101961</v>
+        <v>105742.7384123841</v>
       </c>
       <c r="F83">
-        <v>114355.1771442714</v>
+        <v>115766.9694546945</v>
       </c>
       <c r="G83">
         <v>473</v>
@@ -8349,37 +8349,37 @@
         <v>4688</v>
       </c>
       <c r="M83">
-        <v>27643.83362070091</v>
+        <v>27985.11551725277</v>
       </c>
       <c r="N83">
-        <v>-22955.83362070091</v>
+        <v>-23297.11551725277</v>
       </c>
       <c r="O83">
-        <v>-2869.479202587614</v>
+        <v>-2912.139439656597</v>
       </c>
       <c r="P83">
-        <v>-20086.3544181133</v>
+        <v>-20384.97607759618</v>
       </c>
       <c r="Q83">
-        <v>-19168.3544181133</v>
+        <v>-19466.97607759618</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3379655043571095</v>
+        <v>0.3541969212658378</v>
       </c>
       <c r="T83">
-        <v>5.69484948728735</v>
+        <v>6.011230014358869</v>
       </c>
       <c r="U83">
         <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.02119821758589871</v>
+        <v>0.02093970273729019</v>
       </c>
       <c r="W83">
-        <v>0.2366122312640427</v>
+        <v>0.2366747237689024</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1695857406871897</v>
+        <v>0.1675176218983215</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8395,22 +8395,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2578287193183507</v>
+        <v>0.2597880854849761</v>
       </c>
       <c r="C84">
-        <v>-77777.93209292811</v>
+        <v>-79533.23724027343</v>
       </c>
       <c r="D84">
-        <v>37516.03736176637</v>
+        <v>37172.52452484415</v>
       </c>
       <c r="E84">
-        <v>105742.7384123841</v>
+        <v>107154.5307228072</v>
       </c>
       <c r="F84">
-        <v>115766.9694546945</v>
+        <v>117178.7617651176</v>
       </c>
       <c r="G84">
         <v>473</v>
@@ -8431,37 +8431,37 @@
         <v>4688</v>
       </c>
       <c r="M84">
-        <v>27985.11551725277</v>
+        <v>28326.39741380464</v>
       </c>
       <c r="N84">
-        <v>-23297.11551725277</v>
+        <v>-23638.39741380464</v>
       </c>
       <c r="O84">
-        <v>-2912.139439656597</v>
+        <v>-2954.79967672558</v>
       </c>
       <c r="P84">
-        <v>-20384.97607759618</v>
+        <v>-20683.59773707906</v>
       </c>
       <c r="Q84">
-        <v>-19466.97607759618</v>
+        <v>-19765.59773707906</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3541969212658378</v>
+        <v>0.3723379166344165</v>
       </c>
       <c r="T84">
-        <v>6.011230014358869</v>
+        <v>6.364831779909391</v>
       </c>
       <c r="U84">
         <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.02093970273729019</v>
+        <v>0.02068741716214211</v>
       </c>
       <c r="W84">
-        <v>0.2366747237689024</v>
+        <v>0.2367357104302714</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1675176218983215</v>
+        <v>0.165499337297137</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8477,22 +8477,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2597880854849761</v>
+        <v>0.2617474516516015</v>
       </c>
       <c r="C85">
-        <v>-79533.23724027343</v>
+        <v>-81282.30876526926</v>
       </c>
       <c r="D85">
-        <v>37172.52452484415</v>
+        <v>36835.24531027144</v>
       </c>
       <c r="E85">
-        <v>107154.5307228072</v>
+        <v>108566.3230332304</v>
       </c>
       <c r="F85">
-        <v>117178.7617651176</v>
+        <v>118590.5540755407</v>
       </c>
       <c r="G85">
         <v>473</v>
@@ -8513,37 +8513,37 @@
         <v>4688</v>
       </c>
       <c r="M85">
-        <v>28326.39741380464</v>
+        <v>28667.6793103565</v>
       </c>
       <c r="N85">
-        <v>-23638.39741380464</v>
+        <v>-23979.6793103565</v>
       </c>
       <c r="O85">
-        <v>-2954.79967672558</v>
+        <v>-2997.459913794563</v>
       </c>
       <c r="P85">
-        <v>-20683.59773707906</v>
+        <v>-20982.21939656194</v>
       </c>
       <c r="Q85">
-        <v>-19765.59773707906</v>
+        <v>-20064.21939656194</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3723379166344165</v>
+        <v>0.3927465364240676</v>
       </c>
       <c r="T85">
-        <v>6.364831779909391</v>
+        <v>6.762633766153731</v>
       </c>
       <c r="U85">
         <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.02068741716214211</v>
+        <v>0.02044113838640232</v>
       </c>
       <c r="W85">
-        <v>0.2367357104302714</v>
+        <v>0.2367952450282746</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.165499337297137</v>
+        <v>0.1635291070912186</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8559,22 +8559,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2617474516516014</v>
+        <v>0.2637068178182267</v>
       </c>
       <c r="C86">
-        <v>-81282.30876526923</v>
+        <v>-83025.31482165461</v>
       </c>
       <c r="D86">
-        <v>36835.24531027144</v>
+        <v>36504.03156430918</v>
       </c>
       <c r="E86">
-        <v>108566.3230332303</v>
+        <v>109978.1153436534</v>
       </c>
       <c r="F86">
-        <v>118590.5540755407</v>
+        <v>120002.3463859638</v>
       </c>
       <c r="G86">
         <v>473</v>
@@ -8595,37 +8595,37 @@
         <v>4688</v>
       </c>
       <c r="M86">
-        <v>28667.6793103565</v>
+        <v>29008.96120690836</v>
       </c>
       <c r="N86">
-        <v>-23979.6793103565</v>
+        <v>-24320.96120690836</v>
       </c>
       <c r="O86">
-        <v>-2997.459913794562</v>
+        <v>-3040.120150863545</v>
       </c>
       <c r="P86">
-        <v>-20982.21939656193</v>
+        <v>-21280.84105604482</v>
       </c>
       <c r="Q86">
-        <v>-20064.21939656193</v>
+        <v>-20362.84105604482</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3927465364240673</v>
+        <v>0.4158763055190052</v>
       </c>
       <c r="T86">
-        <v>6.762633766153725</v>
+        <v>7.21347601723064</v>
       </c>
       <c r="U86">
         <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.02044113838640233</v>
+        <v>0.02020065440538583</v>
       </c>
       <c r="W86">
-        <v>0.2367952450282745</v>
+        <v>0.236853378812207</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1635291070912186</v>
+        <v>0.1616052352430867</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8641,22 +8641,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2637068178182267</v>
+        <v>0.2656661839848521</v>
       </c>
       <c r="C87">
-        <v>-83025.31482165461</v>
+        <v>-84762.41756907268</v>
       </c>
       <c r="D87">
-        <v>36504.03156430918</v>
+        <v>36178.7211273142</v>
       </c>
       <c r="E87">
-        <v>109978.1153436534</v>
+        <v>111389.9076540765</v>
       </c>
       <c r="F87">
-        <v>120002.3463859638</v>
+        <v>121414.1386963869</v>
       </c>
       <c r="G87">
         <v>473</v>
@@ -8677,37 +8677,37 @@
         <v>4688</v>
       </c>
       <c r="M87">
-        <v>29008.96120690836</v>
+        <v>29350.24310346022</v>
       </c>
       <c r="N87">
-        <v>-24320.96120690836</v>
+        <v>-24662.24310346022</v>
       </c>
       <c r="O87">
-        <v>-3040.120150863545</v>
+        <v>-3082.780387932528</v>
       </c>
       <c r="P87">
-        <v>-21280.84105604482</v>
+        <v>-21579.46271552769</v>
       </c>
       <c r="Q87">
-        <v>-20362.84105604482</v>
+        <v>-20661.46271552769</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4158763055190052</v>
+        <v>0.4423103273417913</v>
       </c>
       <c r="T87">
-        <v>7.21347601723064</v>
+        <v>7.728724304175686</v>
       </c>
       <c r="U87">
         <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.02020065440538583</v>
+        <v>0.01996576307509065</v>
       </c>
       <c r="W87">
-        <v>0.236853378812207</v>
+        <v>0.2369101606476759</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1616052352430867</v>
+        <v>0.1597261046007251</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8723,22 +8723,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2656661839848521</v>
+        <v>0.2676255501514774</v>
       </c>
       <c r="C88">
-        <v>-84762.41756907268</v>
+        <v>-86493.77343779747</v>
       </c>
       <c r="D88">
-        <v>36178.7211273142</v>
+        <v>35859.15756901252</v>
       </c>
       <c r="E88">
-        <v>111389.9076540765</v>
+        <v>112801.6999644996</v>
       </c>
       <c r="F88">
-        <v>121414.1386963869</v>
+        <v>122825.93100681</v>
       </c>
       <c r="G88">
         <v>473</v>
@@ -8759,37 +8759,37 @@
         <v>4688</v>
       </c>
       <c r="M88">
-        <v>29350.24310346022</v>
+        <v>29691.52500001209</v>
       </c>
       <c r="N88">
-        <v>-24662.24310346022</v>
+        <v>-25003.52500001209</v>
       </c>
       <c r="O88">
-        <v>-3082.780387932528</v>
+        <v>-3125.440625001511</v>
       </c>
       <c r="P88">
-        <v>-21579.46271552769</v>
+        <v>-21878.08437501058</v>
       </c>
       <c r="Q88">
-        <v>-20661.46271552769</v>
+        <v>-20960.08437501058</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4423103273417913</v>
+        <v>0.4728111217526983</v>
       </c>
       <c r="T88">
-        <v>7.728724304175686</v>
+        <v>8.323241558343046</v>
       </c>
       <c r="U88">
         <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.01996576307509065</v>
+        <v>0.0197362715454919</v>
       </c>
       <c r="W88">
-        <v>0.2369101606476759</v>
+        <v>0.2369656371535939</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1597261046007251</v>
+        <v>0.1578901723639352</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8805,22 +8805,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2676255501514774</v>
+        <v>0.2695849163181028</v>
       </c>
       <c r="C89">
-        <v>-86493.77343779747</v>
+        <v>-88219.53337955338</v>
       </c>
       <c r="D89">
-        <v>35859.15756901252</v>
+        <v>35545.1899376797</v>
       </c>
       <c r="E89">
-        <v>112801.6999644996</v>
+        <v>114213.4922749227</v>
       </c>
       <c r="F89">
-        <v>122825.93100681</v>
+        <v>124237.7233172331</v>
       </c>
       <c r="G89">
         <v>473</v>
@@ -8841,37 +8841,37 @@
         <v>4688</v>
       </c>
       <c r="M89">
-        <v>29691.52500001209</v>
+        <v>30032.80689656395</v>
       </c>
       <c r="N89">
-        <v>-25003.52500001209</v>
+        <v>-25344.80689656395</v>
       </c>
       <c r="O89">
-        <v>-3125.440625001511</v>
+        <v>-3168.100862070494</v>
       </c>
       <c r="P89">
-        <v>-21878.08437501058</v>
+        <v>-22176.70603449346</v>
       </c>
       <c r="Q89">
-        <v>-20960.08437501058</v>
+        <v>-21258.70603449346</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4728111217526983</v>
+        <v>0.5083953818987565</v>
       </c>
       <c r="T89">
-        <v>8.323241558343046</v>
+        <v>9.016845021538302</v>
       </c>
       <c r="U89">
         <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.0197362715454919</v>
+        <v>0.01951199573247495</v>
       </c>
       <c r="W89">
-        <v>0.2369656371535939</v>
+        <v>0.2370198528298318</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1578901723639352</v>
+        <v>0.1560959658597996</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8887,22 +8887,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2695849163181028</v>
+        <v>0.2715442824847281</v>
       </c>
       <c r="C90">
-        <v>-88219.53337955338</v>
+        <v>-89939.84310527304</v>
       </c>
       <c r="D90">
-        <v>35545.1899376797</v>
+        <v>35236.67252238316</v>
       </c>
       <c r="E90">
-        <v>114213.4922749227</v>
+        <v>115625.2845853459</v>
       </c>
       <c r="F90">
-        <v>124237.7233172331</v>
+        <v>125649.5156276562</v>
       </c>
       <c r="G90">
         <v>473</v>
@@ -8923,37 +8923,37 @@
         <v>4688</v>
       </c>
       <c r="M90">
-        <v>30032.80689656395</v>
+        <v>30374.08879311581</v>
       </c>
       <c r="N90">
-        <v>-25344.80689656395</v>
+        <v>-25686.08879311581</v>
       </c>
       <c r="O90">
-        <v>-3168.100862070494</v>
+        <v>-3210.761099139477</v>
       </c>
       <c r="P90">
-        <v>-22176.70603449346</v>
+        <v>-22475.32769397634</v>
       </c>
       <c r="Q90">
-        <v>-21258.70603449346</v>
+        <v>-21557.32769397634</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5083953818987565</v>
+        <v>0.5504495075259161</v>
       </c>
       <c r="T90">
-        <v>9.016845021538302</v>
+        <v>9.83655820531451</v>
       </c>
       <c r="U90">
         <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.01951199573247495</v>
+        <v>0.01929275982536849</v>
       </c>
       <c r="W90">
-        <v>0.2370198528298318</v>
+        <v>0.2370728501762667</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1560959658597996</v>
+        <v>0.1543420786029479</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8969,22 +8969,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2715442824847281</v>
+        <v>0.2735036486513535</v>
       </c>
       <c r="C91">
-        <v>-89939.84310527304</v>
+        <v>-91654.84331057941</v>
       </c>
       <c r="D91">
-        <v>35236.67252238316</v>
+        <v>34933.4646274999</v>
       </c>
       <c r="E91">
-        <v>115625.2845853459</v>
+        <v>117037.076895769</v>
       </c>
       <c r="F91">
-        <v>125649.5156276562</v>
+        <v>127061.3079380793</v>
       </c>
       <c r="G91">
         <v>473</v>
@@ -9005,37 +9005,37 @@
         <v>4688</v>
       </c>
       <c r="M91">
-        <v>30374.08879311581</v>
+        <v>30715.37068966768</v>
       </c>
       <c r="N91">
-        <v>-25686.08879311581</v>
+        <v>-26027.37068966768</v>
       </c>
       <c r="O91">
-        <v>-3210.761099139477</v>
+        <v>-3253.42133620846</v>
       </c>
       <c r="P91">
-        <v>-22475.32769397634</v>
+        <v>-22773.94935345922</v>
       </c>
       <c r="Q91">
-        <v>-21557.32769397634</v>
+        <v>-21855.94935345922</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5504495075259161</v>
+        <v>0.6009144582785079</v>
       </c>
       <c r="T91">
-        <v>9.83655820531451</v>
+        <v>10.82021402584596</v>
       </c>
       <c r="U91">
         <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.01929275982536849</v>
+        <v>0.01907839582730884</v>
       </c>
       <c r="W91">
-        <v>0.2370728501762667</v>
+        <v>0.2371246698038919</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1543420786029479</v>
+        <v>0.1526271666184708</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9051,22 +9051,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2735036486513535</v>
+        <v>0.2754630148179788</v>
       </c>
       <c r="C92">
-        <v>-91654.84331057941</v>
+        <v>-93364.66988972609</v>
       </c>
       <c r="D92">
-        <v>34933.4646274999</v>
+        <v>34635.43035877632</v>
       </c>
       <c r="E92">
-        <v>117037.076895769</v>
+        <v>118448.8692061921</v>
       </c>
       <c r="F92">
-        <v>127061.3079380793</v>
+        <v>128473.1002485024</v>
       </c>
       <c r="G92">
         <v>473</v>
@@ -9087,37 +9087,37 @@
         <v>4688</v>
       </c>
       <c r="M92">
-        <v>30715.37068966768</v>
+        <v>31056.65258621954</v>
       </c>
       <c r="N92">
-        <v>-26027.37068966768</v>
+        <v>-26368.65258621954</v>
       </c>
       <c r="O92">
-        <v>-3253.42133620846</v>
+        <v>-3296.081573277443</v>
       </c>
       <c r="P92">
-        <v>-22773.94935345922</v>
+        <v>-23072.5710129421</v>
       </c>
       <c r="Q92">
-        <v>-21855.94935345922</v>
+        <v>-22154.5710129421</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6009144582785079</v>
+        <v>0.6625938425316755</v>
       </c>
       <c r="T92">
-        <v>10.82021402584596</v>
+        <v>12.02246002871774</v>
       </c>
       <c r="U92">
         <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.01907839582730884</v>
+        <v>0.01886874312590984</v>
       </c>
       <c r="W92">
-        <v>0.2371246698038919</v>
+        <v>0.2371753505386022</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1526271666184708</v>
+        <v>0.1509499450072788</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9133,22 +9133,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2754630148179788</v>
+        <v>0.2774223809846041</v>
       </c>
       <c r="C93">
-        <v>-93364.66988972609</v>
+        <v>-95069.45413867867</v>
       </c>
       <c r="D93">
-        <v>34635.43035877632</v>
+        <v>34342.43842024683</v>
       </c>
       <c r="E93">
-        <v>118448.8692061921</v>
+        <v>119860.6615166152</v>
       </c>
       <c r="F93">
-        <v>128473.1002485024</v>
+        <v>129884.8925589255</v>
       </c>
       <c r="G93">
         <v>473</v>
@@ -9169,37 +9169,37 @@
         <v>4688</v>
       </c>
       <c r="M93">
-        <v>31056.65258621954</v>
+        <v>31397.9344827714</v>
       </c>
       <c r="N93">
-        <v>-26368.65258621954</v>
+        <v>-26709.9344827714</v>
       </c>
       <c r="O93">
-        <v>-3296.081573277443</v>
+        <v>-3338.741810346426</v>
       </c>
       <c r="P93">
-        <v>-23072.5710129421</v>
+        <v>-23371.19267242498</v>
       </c>
       <c r="Q93">
-        <v>-22154.5710129421</v>
+        <v>-22453.19267242498</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6625938425316755</v>
+        <v>0.7396930728481351</v>
       </c>
       <c r="T93">
-        <v>12.02246002871774</v>
+        <v>13.52526753230746</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.01886874312590984</v>
+        <v>0.01866364809193256</v>
       </c>
       <c r="W93">
-        <v>0.2371753505386022</v>
+        <v>0.2372249295182102</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1509499450072788</v>
+        <v>0.1493091847354605</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9215,22 +9215,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2774223809846041</v>
+        <v>0.2793817471512295</v>
       </c>
       <c r="C94">
-        <v>-95069.45413867867</v>
+        <v>-96769.32294797513</v>
       </c>
       <c r="D94">
-        <v>34342.43842024683</v>
+        <v>34054.36192137349</v>
       </c>
       <c r="E94">
-        <v>119860.6615166152</v>
+        <v>121272.4538270383</v>
       </c>
       <c r="F94">
-        <v>129884.8925589255</v>
+        <v>131296.6848693486</v>
       </c>
       <c r="G94">
         <v>473</v>
@@ -9251,37 +9251,37 @@
         <v>4688</v>
       </c>
       <c r="M94">
-        <v>31397.9344827714</v>
+        <v>31739.21637932327</v>
       </c>
       <c r="N94">
-        <v>-26709.9344827714</v>
+        <v>-27051.21637932327</v>
       </c>
       <c r="O94">
-        <v>-3338.741810346426</v>
+        <v>-3381.402047415409</v>
       </c>
       <c r="P94">
-        <v>-23371.19267242498</v>
+        <v>-23669.81433190786</v>
       </c>
       <c r="Q94">
-        <v>-22453.19267242498</v>
+        <v>-22751.81433190786</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7396930728481351</v>
+        <v>0.8388206546835831</v>
       </c>
       <c r="T94">
-        <v>13.52526753230746</v>
+        <v>15.45744860835138</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.01866364809193256</v>
+        <v>0.01846296370384726</v>
       </c>
       <c r="W94">
-        <v>0.2372249295182102</v>
+        <v>0.2372734422832029</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1493091847354605</v>
+        <v>0.1477037096307781</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2793817471512295</v>
+        <v>0.2813411133178548</v>
       </c>
       <c r="C95">
-        <v>-96769.32294797513</v>
+        <v>-98464.3989859601</v>
       </c>
       <c r="D95">
-        <v>34054.36192137349</v>
+        <v>33771.07819381163</v>
       </c>
       <c r="E95">
-        <v>121272.4538270383</v>
+        <v>122684.2461374614</v>
       </c>
       <c r="F95">
-        <v>131296.6848693486</v>
+        <v>132708.4771797717</v>
       </c>
       <c r="G95">
         <v>473</v>
@@ -9333,37 +9333,37 @@
         <v>4688</v>
       </c>
       <c r="M95">
-        <v>31739.21637932327</v>
+        <v>32080.49827587513</v>
       </c>
       <c r="N95">
-        <v>-27051.21637932327</v>
+        <v>-27392.49827587513</v>
       </c>
       <c r="O95">
-        <v>-3381.402047415409</v>
+        <v>-3424.062284484392</v>
       </c>
       <c r="P95">
-        <v>-23669.81433190786</v>
+        <v>-23968.43599139074</v>
       </c>
       <c r="Q95">
-        <v>-22751.81433190786</v>
+        <v>-23050.43599139074</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8388206546835831</v>
+        <v>0.9709907637975138</v>
       </c>
       <c r="T95">
-        <v>15.45744860835138</v>
+        <v>18.03369004307662</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.01846296370384726</v>
+        <v>0.01826654919635953</v>
       </c>
       <c r="W95">
-        <v>0.2372734422832029</v>
+        <v>0.2373209228617064</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1477037096307781</v>
+        <v>0.1461323935708762</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9379,22 +9379,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2813411133178548</v>
+        <v>0.2833004794844802</v>
       </c>
       <c r="C96">
-        <v>-98464.3989859601</v>
+        <v>-100154.8008729493</v>
       </c>
       <c r="D96">
-        <v>33771.07819381163</v>
+        <v>33492.46861724553</v>
       </c>
       <c r="E96">
-        <v>122684.2461374614</v>
+        <v>124096.0384478845</v>
       </c>
       <c r="F96">
-        <v>132708.4771797717</v>
+        <v>134120.2694901948</v>
       </c>
       <c r="G96">
         <v>473</v>
@@ -9415,37 +9415,37 @@
         <v>4688</v>
       </c>
       <c r="M96">
-        <v>32080.49827587513</v>
+        <v>32421.780172427</v>
       </c>
       <c r="N96">
-        <v>-27392.49827587513</v>
+        <v>-27733.780172427</v>
       </c>
       <c r="O96">
-        <v>-3424.062284484392</v>
+        <v>-3466.722521553374</v>
       </c>
       <c r="P96">
-        <v>-23968.43599139074</v>
+        <v>-24267.05765087362</v>
       </c>
       <c r="Q96">
-        <v>-23050.43599139074</v>
+        <v>-23349.05765087362</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9709907637975138</v>
+        <v>1.156028916557017</v>
       </c>
       <c r="T96">
-        <v>18.03369004307662</v>
+        <v>21.64042805169195</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.01826654919635953</v>
+        <v>0.01807426973113469</v>
       </c>
       <c r="W96">
-        <v>0.2373209228617064</v>
+        <v>0.2373674038490836</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1461323935708762</v>
+        <v>0.1445941578490775</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9461,22 +9461,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2833004794844802</v>
+        <v>0.2852598456511055</v>
       </c>
       <c r="C97">
-        <v>-100154.8008729493</v>
+        <v>-101840.6433468433</v>
       </c>
       <c r="D97">
-        <v>33492.46861724553</v>
+        <v>33218.41845377467</v>
       </c>
       <c r="E97">
-        <v>124096.0384478845</v>
+        <v>125507.8307583076</v>
       </c>
       <c r="F97">
-        <v>134120.2694901948</v>
+        <v>135532.0618006179</v>
       </c>
       <c r="G97">
         <v>473</v>
@@ -9497,37 +9497,37 @@
         <v>4688</v>
       </c>
       <c r="M97">
-        <v>32421.780172427</v>
+        <v>32763.06206897886</v>
       </c>
       <c r="N97">
-        <v>-27733.780172427</v>
+        <v>-28075.06206897886</v>
       </c>
       <c r="O97">
-        <v>-3466.722521553374</v>
+        <v>-3509.382758622357</v>
       </c>
       <c r="P97">
-        <v>-24267.05765087362</v>
+        <v>-24565.6793103565</v>
       </c>
       <c r="Q97">
-        <v>-23349.05765087362</v>
+        <v>-23647.6793103565</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.156028916557017</v>
+        <v>1.433586145696272</v>
       </c>
       <c r="T97">
-        <v>21.64042805169195</v>
+        <v>27.05053506461496</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.01807426973113469</v>
+        <v>0.01788599608810204</v>
       </c>
       <c r="W97">
-        <v>0.2373674038490836</v>
+        <v>0.237412916482557</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1445941578490775</v>
+        <v>0.1430879687048163</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9543,22 +9543,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2852598456511055</v>
+        <v>0.2872192118177308</v>
       </c>
       <c r="C98">
-        <v>-101840.6433468433</v>
+        <v>-103522.0374206764</v>
       </c>
       <c r="D98">
-        <v>33218.41845377467</v>
+        <v>32948.81669036461</v>
       </c>
       <c r="E98">
-        <v>125507.8307583076</v>
+        <v>126919.6230687307</v>
       </c>
       <c r="F98">
-        <v>135532.0618006179</v>
+        <v>136943.854111041</v>
       </c>
       <c r="G98">
         <v>473</v>
@@ -9579,37 +9579,37 @@
         <v>4688</v>
       </c>
       <c r="M98">
-        <v>32763.06206897886</v>
+        <v>33104.34396553072</v>
       </c>
       <c r="N98">
-        <v>-28075.06206897886</v>
+        <v>-28416.34396553072</v>
       </c>
       <c r="O98">
-        <v>-3509.382758622357</v>
+        <v>-3552.04299569134</v>
       </c>
       <c r="P98">
-        <v>-24565.6793103565</v>
+        <v>-24864.30096983938</v>
       </c>
       <c r="Q98">
-        <v>-23647.6793103565</v>
+        <v>-23946.30096983938</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.433586145696268</v>
+        <v>1.896181527595024</v>
       </c>
       <c r="T98">
-        <v>27.05053506461488</v>
+        <v>36.06738008615317</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.01788599608810204</v>
+        <v>0.01770160437585356</v>
       </c>
       <c r="W98">
-        <v>0.237412916482557</v>
+        <v>0.2374574907112166</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1430879687048163</v>
+        <v>0.1416128350068284</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9625,22 +9625,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2872192118177308</v>
+        <v>0.2891785779843562</v>
       </c>
       <c r="C99">
-        <v>-103522.0374206764</v>
+        <v>-105199.0905325559</v>
       </c>
       <c r="D99">
-        <v>32948.81669036461</v>
+        <v>32683.55588890824</v>
       </c>
       <c r="E99">
-        <v>126919.6230687307</v>
+        <v>128331.4153791538</v>
       </c>
       <c r="F99">
-        <v>136943.854111041</v>
+        <v>138355.6464214641</v>
       </c>
       <c r="G99">
         <v>473</v>
@@ -9661,37 +9661,37 @@
         <v>4688</v>
       </c>
       <c r="M99">
-        <v>33104.34396553072</v>
+        <v>33445.62586208258</v>
       </c>
       <c r="N99">
-        <v>-28416.34396553072</v>
+        <v>-28757.62586208258</v>
       </c>
       <c r="O99">
-        <v>-3552.04299569134</v>
+        <v>-3594.703232760323</v>
       </c>
       <c r="P99">
-        <v>-24864.30096983938</v>
+        <v>-25162.92262932226</v>
       </c>
       <c r="Q99">
-        <v>-23946.30096983938</v>
+        <v>-24244.92262932226</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.896181527595024</v>
+        <v>2.821372291392537</v>
       </c>
       <c r="T99">
-        <v>36.06738008615317</v>
+        <v>54.10107012922977</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.01770160437585356</v>
+        <v>0.01752097575977342</v>
       </c>
       <c r="W99">
-        <v>0.2374574907112166</v>
+        <v>0.2375011552617402</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1416128350068284</v>
+        <v>0.1401678060781874</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9707,22 +9707,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2891785779843562</v>
+        <v>0.2911379441509815</v>
       </c>
       <c r="C100">
-        <v>-105199.0905325559</v>
+        <v>-106871.9066884153</v>
       </c>
       <c r="D100">
-        <v>32683.55588890824</v>
+        <v>32422.53204347191</v>
       </c>
       <c r="E100">
-        <v>128331.4153791538</v>
+        <v>129743.2076895769</v>
       </c>
       <c r="F100">
-        <v>138355.6464214641</v>
+        <v>139767.4387318872</v>
       </c>
       <c r="G100">
         <v>473</v>
@@ -9743,37 +9743,37 @@
         <v>4688</v>
       </c>
       <c r="M100">
-        <v>33445.62586208258</v>
+        <v>33786.90775863444</v>
       </c>
       <c r="N100">
-        <v>-28757.62586208258</v>
+        <v>-29098.90775863444</v>
       </c>
       <c r="O100">
-        <v>-3594.703232760323</v>
+        <v>-3637.363469829305</v>
       </c>
       <c r="P100">
-        <v>-25162.92262932226</v>
+        <v>-25461.54428880514</v>
       </c>
       <c r="Q100">
-        <v>-24244.92262932226</v>
+        <v>-24543.54428880514</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.821372291392537</v>
+        <v>5.596944582785073</v>
       </c>
       <c r="T100">
-        <v>54.10107012922977</v>
+        <v>108.2021402584595</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.01752097575977342</v>
+        <v>0.0173439962066444</v>
       </c>
       <c r="W100">
-        <v>0.2375011552617402</v>
+        <v>0.237543937700132</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9781,91 +9781,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1401678060781874</v>
+        <v>0.1387519696531552</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2911379441509815</v>
-      </c>
-      <c r="C101">
-        <v>-106871.9066884153</v>
-      </c>
-      <c r="D101">
-        <v>32422.53204347191</v>
-      </c>
-      <c r="E101">
-        <v>129743.2076895769</v>
-      </c>
-      <c r="F101">
-        <v>139767.4387318872</v>
-      </c>
-      <c r="G101">
-        <v>473</v>
-      </c>
-      <c r="H101">
-        <v>131155</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5606</v>
-      </c>
-      <c r="K101">
-        <v>918</v>
-      </c>
-      <c r="L101">
-        <v>4688</v>
-      </c>
-      <c r="M101">
-        <v>33786.90775863444</v>
-      </c>
-      <c r="N101">
-        <v>-29098.90775863444</v>
-      </c>
-      <c r="O101">
-        <v>-3637.363469829305</v>
-      </c>
-      <c r="P101">
-        <v>-25461.54428880514</v>
-      </c>
-      <c r="Q101">
-        <v>-24543.54428880514</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.596944582785073</v>
-      </c>
-      <c r="T101">
-        <v>108.2021402584595</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.0173439962066444</v>
-      </c>
-      <c r="W101">
-        <v>0.237543937700132</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1387519696531552</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
